--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE244"/>
+  <dimension ref="A1:AE245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -644,13 +644,13 @@
         <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -676,6 +676,7 @@
 Svartsnäppa
 Sädesärla
 Talltita
+Bergfink
 Nattskärra
 Spillkråka
 Stjärtmes
@@ -748,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -976,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1192,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1208,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1232,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1248,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1301,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1390,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1404,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1420,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1444,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1460,60 +1461,60 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S 602-2024</t>
+          <t>A 37754-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45351</v>
+        <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,22 +1526,17 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>68.40000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1555,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1564,548 +1560,590 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Orre</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S 602-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Skogsklocka
 Strandlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/S 602-2024 artfynd.xlsx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/S 602-2024 karta.png", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/S 602-2024 georefererad karta.tif", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/S 602-2024 FSC-klagomål.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/S 602-2024 FSC-klagomål mail.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/S 602-2024 tillsynsbegäran.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/S 602-2024 tillsynsbegäran mail.docx", "S 602-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 38064-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 36671-2025</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 55118-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45967</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>1.6</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Luddfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 31051-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46215</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38064-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 42774-2022</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr"/>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58883-2021</t>
+          <t>A 42774-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2119,10 +2157,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44489</v>
+        <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2135,7 +2173,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2178,7 +2216,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 64067-2021</t>
+          <t>A 58883-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2192,10 +2230,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44509</v>
+        <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2207,13 +2245,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2256,7 +2289,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 64067-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2270,10 +2303,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44571</v>
+        <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2285,8 +2318,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2346,7 +2384,7 @@
         <v>44535</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2419,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2492,7 +2530,7 @@
         <v>44733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2548,7 +2586,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54077-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2562,10 +2600,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44470</v>
+        <v>44571</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2578,7 +2616,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2621,7 +2659,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37425-2022</t>
+          <t>A 54077-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2635,10 +2673,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44809</v>
+        <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2694,7 +2732,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45804-2022</t>
+          <t>A 37425-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2708,10 +2746,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2724,7 +2762,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2767,7 +2805,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25845-2022</t>
+          <t>A 45804-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2781,10 +2819,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44733</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2797,7 +2835,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2840,7 +2878,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6190-2022</t>
+          <t>A 25845-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2854,10 +2892,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44600</v>
+        <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2870,7 +2908,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2913,7 +2951,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44061-2022</t>
+          <t>A 6190-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2927,10 +2965,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44839</v>
+        <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2943,7 +2981,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2986,7 +3024,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 68194-2021</t>
+          <t>A 44061-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3000,10 +3038,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44526</v>
+        <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3016,7 +3054,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3059,7 +3097,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 69666-2021</t>
+          <t>A 68194-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3073,10 +3111,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44532</v>
+        <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3089,7 +3127,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3132,7 +3170,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55581-2021</t>
+          <t>A 69666-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3146,10 +3184,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44475</v>
+        <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3162,7 +3200,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3205,7 +3243,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61207-2021</t>
+          <t>A 55581-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3215,14 +3253,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44498</v>
+        <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3235,7 +3273,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3278,7 +3316,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63214-2021</t>
+          <t>A 61207-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3288,14 +3326,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44505</v>
+        <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3308,7 +3346,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3351,7 +3389,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 63214-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3365,10 +3403,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44494</v>
+        <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3381,7 +3419,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3424,7 +3462,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3438,10 +3476,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44858</v>
+        <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3454,7 +3492,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3497,7 +3535,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3507,14 +3545,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44749</v>
+        <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3527,7 +3565,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3570,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3584,10 +3622,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45050</v>
+        <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3599,8 +3637,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3643,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3657,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45204</v>
+        <v>44705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3672,13 +3715,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3721,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3735,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45336</v>
+        <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3751,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3794,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3808,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45414</v>
+        <v>44868</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3824,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3867,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3881,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44868</v>
+        <v>45560</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3897,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3940,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3954,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44890</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3970,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4013,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4027,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44890</v>
+        <v>44958</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4043,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4086,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4100,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44813</v>
+        <v>45191</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4116,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4159,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4173,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44797</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4189,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4232,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4246,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45376</v>
+        <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4267,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4310,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4324,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44845</v>
+        <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4340,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4383,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4397,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44575</v>
+        <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4413,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4456,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4470,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44487</v>
+        <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4486,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4529,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4543,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45495</v>
+        <v>45680</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4559,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>11.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4602,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4616,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44582</v>
+        <v>46007</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4632,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4675,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4689,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45329</v>
+        <v>45369</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4704,13 +4742,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4753,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4767,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44536</v>
+        <v>46008</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4783,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4826,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4840,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45525</v>
+        <v>45328</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4856,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4899,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4913,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44974</v>
+        <v>45247</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4929,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4972,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4986,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45554</v>
+        <v>45707</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5002,7 +5035,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5045,7 +5078,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5055,14 +5088,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45820</v>
+        <v>45707</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5075,7 +5108,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5118,7 +5151,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5128,14 +5161,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45819</v>
+        <v>45586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5148,7 +5181,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5191,7 +5224,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5205,10 +5238,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45369</v>
+        <v>45811</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5221,7 +5254,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5264,7 +5297,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5278,10 +5311,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45826</v>
+        <v>45811</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5294,7 +5327,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5337,7 +5370,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5351,10 +5384,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>45350</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5366,8 +5399,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5410,7 +5448,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5424,10 +5462,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45113</v>
+        <v>45309</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5440,7 +5478,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5483,7 +5521,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5497,10 +5535,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45229</v>
+        <v>45811</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5513,7 +5551,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5573,7 +5611,7 @@
         <v>45803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5629,7 +5667,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5643,10 +5681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45588</v>
+        <v>45450</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5659,7 +5697,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5702,7 +5740,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5716,10 +5754,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45884</v>
+        <v>45629</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5731,13 +5769,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5780,7 +5813,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5794,10 +5827,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45893</v>
+        <v>45884</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5809,8 +5842,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5853,7 +5891,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5867,10 +5905,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45660</v>
+        <v>45126</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5883,7 +5921,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5926,7 +5964,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5940,10 +5978,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46072</v>
+        <v>46034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5956,7 +5994,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5999,7 +6037,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6013,10 +6051,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45082</v>
+        <v>46034</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6029,7 +6067,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6072,7 +6110,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6086,10 +6124,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44999</v>
+        <v>45893</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6102,7 +6140,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6145,7 +6183,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6159,10 +6197,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45903</v>
+        <v>45819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6174,13 +6212,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6223,7 +6256,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6237,10 +6270,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45113</v>
+        <v>44498</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6253,7 +6286,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6296,7 +6329,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6310,10 +6343,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45629</v>
+        <v>45567</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6326,7 +6359,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6369,7 +6402,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6379,14 +6412,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44496</v>
+        <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6399,7 +6432,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6442,7 +6475,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6456,10 +6489,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46072</v>
+        <v>45660</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6472,7 +6505,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6515,7 +6548,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6529,10 +6562,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46072</v>
+        <v>45109</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6545,7 +6578,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6588,7 +6621,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6602,10 +6635,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45910</v>
+        <v>46038</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6617,8 +6650,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6661,7 +6699,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6671,14 +6709,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45903</v>
+        <v>45826</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6691,7 +6729,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6734,7 +6772,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6744,14 +6782,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45782</v>
+        <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6763,8 +6801,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6807,7 +6850,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6821,10 +6864,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45271</v>
+        <v>45629</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6837,7 +6880,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6880,7 +6923,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6894,10 +6937,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45915</v>
+        <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6910,7 +6953,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6953,7 +6996,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6967,10 +7010,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45609</v>
+        <v>45551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6983,7 +7026,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7026,7 +7069,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7040,10 +7083,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45042</v>
+        <v>44897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7056,7 +7099,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7099,7 +7142,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7113,10 +7156,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45925</v>
+        <v>45915</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7128,13 +7171,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7177,7 +7215,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7191,10 +7229,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45019</v>
+        <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7206,8 +7244,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7250,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7260,14 +7303,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45019</v>
+        <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7280,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7323,7 +7366,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7337,10 +7380,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45932</v>
+        <v>44917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7353,7 +7396,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7396,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7410,10 +7453,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45674</v>
+        <v>44999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7426,7 +7469,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7469,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7483,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44749</v>
+        <v>45925</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7498,8 +7541,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7542,7 +7590,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7556,10 +7604,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45939</v>
+        <v>45674</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7572,7 +7620,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7615,7 +7663,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7629,10 +7677,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46090</v>
+        <v>45329</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7644,8 +7692,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7688,7 +7741,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7702,10 +7755,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46090</v>
+        <v>45082</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7718,7 +7771,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7761,7 +7814,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7775,10 +7828,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45224</v>
+        <v>45271</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7791,7 +7844,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7834,7 +7887,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7848,10 +7901,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45198</v>
+        <v>45099</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7864,7 +7917,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7907,7 +7960,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7921,10 +7974,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45953</v>
+        <v>45782</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7937,7 +7990,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7980,7 +8033,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7994,10 +8047,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45013</v>
+        <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8010,7 +8063,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8053,7 +8106,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8067,10 +8120,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45960</v>
+        <v>46072</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8083,7 +8136,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8126,7 +8179,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8140,10 +8193,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45042</v>
+        <v>46072</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8156,7 +8209,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8199,7 +8252,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8213,10 +8266,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44858</v>
+        <v>46072</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8229,7 +8282,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8272,7 +8325,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8286,10 +8339,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46108</v>
+        <v>45939</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8301,13 +8354,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8350,7 +8398,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8364,10 +8412,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45055</v>
+        <v>44603</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8380,7 +8428,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8423,7 +8471,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8437,10 +8485,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44819</v>
+        <v>46090</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8453,7 +8501,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8496,7 +8544,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8510,10 +8558,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44868</v>
+        <v>46090</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8526,7 +8574,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8569,7 +8617,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8583,10 +8631,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45967</v>
+        <v>45751</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8599,7 +8647,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8642,7 +8690,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8656,10 +8704,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45247</v>
+        <v>45113</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8672,7 +8720,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8715,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8729,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45246</v>
+        <v>45205</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8745,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8788,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8802,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45979</v>
+        <v>44890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8818,7 +8866,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8861,7 +8909,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8875,10 +8923,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45169</v>
+        <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8891,7 +8939,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8934,7 +8982,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8948,10 +8996,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46121</v>
+        <v>45953</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8963,13 +9011,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9012,7 +9055,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9026,10 +9069,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45113</v>
+        <v>46108</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9041,8 +9084,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9085,7 +9133,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9099,10 +9147,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45012</v>
+        <v>45960</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9158,7 +9206,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9172,10 +9220,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45986</v>
+        <v>45111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9187,13 +9235,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>11.2</v>
+        <v>6.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9236,7 +9279,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9250,10 +9293,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45986</v>
+        <v>44476</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9266,7 +9309,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9309,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9323,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44531</v>
+        <v>46121</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9338,8 +9381,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9382,7 +9430,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9396,10 +9444,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45098</v>
+        <v>45967</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9412,7 +9460,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9455,7 +9503,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9465,14 +9513,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44866</v>
+        <v>44749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9485,7 +9533,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9528,7 +9576,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9542,10 +9590,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44476</v>
+        <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9558,7 +9606,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9601,7 +9649,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9615,10 +9663,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44876</v>
+        <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9631,7 +9679,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9674,7 +9722,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9688,10 +9736,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46000</v>
+        <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9704,7 +9752,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9747,7 +9795,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9761,10 +9809,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45771</v>
+        <v>45119</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9777,7 +9825,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9820,7 +9868,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9834,10 +9882,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44603</v>
+        <v>44748</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9850,7 +9898,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9893,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9907,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46007</v>
+        <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9923,7 +9971,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9966,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9980,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46008</v>
+        <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9995,8 +10043,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>11.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10039,7 +10092,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10053,10 +10106,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44651</v>
+        <v>45621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10069,7 +10122,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10129,7 +10182,7 @@
         <v>45706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10185,7 +10238,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10199,10 +10252,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45109</v>
+        <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10215,7 +10268,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10258,7 +10311,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10272,10 +10325,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45065</v>
+        <v>45055</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10288,7 +10341,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10331,7 +10384,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10345,10 +10398,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44498</v>
+        <v>45800</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10361,7 +10414,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10404,7 +10457,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10418,10 +10471,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44901</v>
+        <v>45792</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10434,7 +10487,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10477,7 +10530,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10491,10 +10544,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45621</v>
+        <v>45800</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10507,7 +10560,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10550,7 +10603,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10564,10 +10617,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45119</v>
+        <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10580,7 +10633,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10623,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10637,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45792</v>
+        <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10653,7 +10706,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10696,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10710,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46034</v>
+        <v>45280</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10725,8 +10778,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10769,7 +10827,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10783,10 +10841,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46034</v>
+        <v>45804</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10799,7 +10857,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10842,7 +10900,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10856,10 +10914,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45575</v>
+        <v>45065</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10872,7 +10930,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10915,7 +10973,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10929,10 +10987,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46038</v>
+        <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10944,13 +11002,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10993,7 +11046,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11007,10 +11060,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45800</v>
+        <v>46085</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11023,7 +11076,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11066,7 +11119,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11080,10 +11133,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45800</v>
+        <v>44866</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11096,7 +11149,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11139,7 +11192,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11153,10 +11206,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45918</v>
+        <v>44749</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11169,7 +11222,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11212,7 +11265,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11226,10 +11279,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45588</v>
+        <v>45112</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11242,7 +11295,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11285,7 +11338,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11299,10 +11352,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45804</v>
+        <v>45098</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11315,7 +11368,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11358,7 +11411,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11372,10 +11425,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45938</v>
+        <v>45358</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11388,7 +11441,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11431,7 +11484,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11445,10 +11498,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45912</v>
+        <v>46141</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11460,8 +11513,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11504,7 +11562,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11518,10 +11576,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45825</v>
+        <v>45303</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11534,7 +11592,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11577,7 +11635,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11591,10 +11649,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45582</v>
+        <v>45019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11607,7 +11665,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11650,7 +11708,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11664,10 +11722,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45044</v>
+        <v>45376</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11679,8 +11737,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11723,7 +11786,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11737,10 +11800,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46085</v>
+        <v>45554</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11753,7 +11816,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11796,7 +11859,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11810,10 +11873,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45567</v>
+        <v>46153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11826,7 +11889,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11869,7 +11932,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11883,10 +11946,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46141</v>
+        <v>45140</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11898,13 +11961,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11947,7 +12005,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11961,10 +12019,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45616</v>
+        <v>44749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11977,7 +12035,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12020,7 +12078,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12034,10 +12092,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44995</v>
+        <v>44993</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12050,7 +12108,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12093,7 +12151,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12107,10 +12165,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45191</v>
+        <v>45594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12123,7 +12181,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12166,7 +12224,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12180,10 +12238,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44550</v>
+        <v>45791</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12196,7 +12254,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12239,7 +12297,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12253,10 +12311,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44536</v>
+        <v>45518</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12269,7 +12327,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12312,7 +12370,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12326,10 +12384,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45616</v>
+        <v>45588</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12342,7 +12400,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12385,7 +12443,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12399,10 +12457,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45588</v>
+        <v>46176</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12415,7 +12473,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12458,7 +12516,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12472,10 +12530,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45588</v>
+        <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12488,7 +12546,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12531,7 +12589,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12545,10 +12603,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12561,7 +12619,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12604,7 +12662,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12618,10 +12676,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45629</v>
+        <v>46239</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12634,7 +12692,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12677,7 +12735,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12691,10 +12749,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45791</v>
+        <v>45554</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12707,7 +12765,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12750,7 +12808,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12764,10 +12822,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45594</v>
+        <v>45169</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12780,7 +12838,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12823,7 +12881,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12837,10 +12895,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45629</v>
+        <v>46240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12853,7 +12911,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12896,7 +12954,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12910,10 +12968,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45229</v>
+        <v>46240</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12926,7 +12984,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12969,7 +13027,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12983,10 +13041,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45098</v>
+        <v>46240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12998,8 +13056,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13042,7 +13105,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13056,10 +13119,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45518</v>
+        <v>45229</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13072,7 +13135,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13115,7 +13178,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13129,10 +13192,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45248</v>
+        <v>46245</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13145,7 +13208,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13188,7 +13251,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13202,10 +13265,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44748</v>
+        <v>46204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13217,8 +13280,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13261,7 +13329,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13275,10 +13343,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46176</v>
+        <v>46246</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13290,8 +13358,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>13.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13334,7 +13407,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13348,10 +13421,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45303</v>
+        <v>44536</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13364,7 +13437,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13407,7 +13480,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13421,10 +13494,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46170</v>
+        <v>45414</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13437,7 +13510,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13480,7 +13553,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13494,10 +13567,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45450</v>
+        <v>45248</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13510,7 +13583,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13553,7 +13626,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13567,10 +13640,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44958</v>
+        <v>44550</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13583,7 +13656,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13626,7 +13699,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13640,10 +13713,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45300</v>
+        <v>46212</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13657,7 +13730,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -13704,7 +13777,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13718,10 +13791,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46168</v>
+        <v>46255</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13734,7 +13807,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13777,7 +13850,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13791,10 +13864,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45140</v>
+        <v>44797</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13807,7 +13880,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13850,7 +13923,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13864,10 +13937,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44866</v>
+        <v>44858</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13880,7 +13953,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13923,7 +13996,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13937,10 +14010,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45350</v>
+        <v>44496</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13952,13 +14025,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14001,7 +14069,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14015,10 +14083,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45680</v>
+        <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14031,7 +14099,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14074,7 +14142,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14088,10 +14156,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44879</v>
+        <v>46224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14104,7 +14172,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14147,7 +14215,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14161,10 +14229,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46240</v>
+        <v>46267</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14177,7 +14245,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14220,7 +14288,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14234,10 +14302,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44993</v>
+        <v>45113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14250,7 +14318,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14293,7 +14361,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14307,10 +14375,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44917</v>
+        <v>45012</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14323,7 +14391,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14366,7 +14434,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14380,10 +14448,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45620</v>
+        <v>44813</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14396,7 +14464,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14439,7 +14507,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14453,10 +14521,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46240</v>
+        <v>45042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14469,7 +14537,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14512,7 +14580,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14526,10 +14594,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46240</v>
+        <v>45616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14541,13 +14609,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14590,7 +14653,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14604,10 +14667,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46239</v>
+        <v>45588</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14620,7 +14683,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14663,7 +14726,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14677,10 +14740,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44858</v>
+        <v>45588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14693,7 +14756,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14736,7 +14799,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14750,10 +14813,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45554</v>
+        <v>44582</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14766,7 +14829,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14809,7 +14872,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14823,10 +14886,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46245</v>
+        <v>46234</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14839,7 +14902,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14882,7 +14945,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14896,10 +14959,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46246</v>
+        <v>46234</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14911,13 +14974,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>13.1</v>
+        <v>4.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14960,7 +15018,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14974,10 +15032,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44995</v>
+        <v>44487</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14990,7 +15048,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15033,7 +15091,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15047,10 +15105,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46204</v>
+        <v>45050</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15062,13 +15120,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15111,7 +15164,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15125,10 +15178,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45109</v>
+        <v>45229</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15141,7 +15194,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15184,7 +15237,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15198,10 +15251,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45560</v>
+        <v>45113</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15214,7 +15267,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15257,7 +15310,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15271,10 +15324,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44749</v>
+        <v>45336</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15287,7 +15340,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15330,7 +15383,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15344,10 +15397,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45111</v>
+        <v>44845</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15360,7 +15413,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15403,7 +15456,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15417,10 +15470,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45370</v>
+        <v>45771</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15433,7 +15486,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15476,7 +15529,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15490,10 +15543,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45280</v>
+        <v>45554</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15505,13 +15558,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15554,7 +15602,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15568,10 +15616,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46212</v>
+        <v>45013</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15583,13 +15631,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15632,7 +15675,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15646,10 +15689,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45099</v>
+        <v>44909</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15662,7 +15705,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15705,7 +15748,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15719,10 +15762,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46255</v>
+        <v>44901</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15735,7 +15778,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15778,7 +15821,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15788,14 +15831,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45358</v>
+        <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15808,7 +15851,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15851,7 +15894,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15865,10 +15908,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44909</v>
+        <v>45042</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15881,7 +15924,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15924,7 +15967,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15938,10 +15981,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45126</v>
+        <v>45044</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15954,7 +15997,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -15997,7 +16040,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16011,10 +16054,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44705</v>
+        <v>45109</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16027,7 +16070,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16070,7 +16113,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16080,14 +16123,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46224</v>
+        <v>44866</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16100,7 +16143,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16143,7 +16186,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16157,10 +16200,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45140</v>
+        <v>44876</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16173,7 +16216,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>8.1</v>
+        <v>4.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16216,7 +16259,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16230,10 +16273,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45229</v>
+        <v>45140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16246,7 +16289,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16289,7 +16332,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16303,10 +16346,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45236</v>
+        <v>45525</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16319,7 +16362,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16362,7 +16405,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16376,10 +16419,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45309</v>
+        <v>44858</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16392,7 +16435,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16435,7 +16478,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16449,10 +16492,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45751</v>
+        <v>45450</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16465,7 +16508,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16508,7 +16551,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16522,10 +16565,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45554</v>
+        <v>45019</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16538,7 +16581,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16581,7 +16624,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16595,10 +16638,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46267</v>
+        <v>45575</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16611,7 +16654,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16654,7 +16697,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16668,10 +16711,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45205</v>
+        <v>45229</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16684,7 +16727,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.1</v>
+        <v>9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16727,7 +16770,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16741,10 +16784,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44897</v>
+        <v>44868</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16757,7 +16800,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16800,7 +16843,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16814,10 +16857,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45534</v>
+        <v>45495</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16829,13 +16872,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>11.2</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16878,7 +16916,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16892,10 +16930,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45527</v>
+        <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16908,7 +16946,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16951,7 +16989,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16965,10 +17003,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45328</v>
+        <v>45098</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16981,7 +17019,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17024,7 +17062,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17038,10 +17076,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44858</v>
+        <v>44575</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17054,7 +17092,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17097,7 +17135,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17111,10 +17149,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45098</v>
+        <v>45236</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17127,7 +17165,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17170,7 +17208,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17184,10 +17222,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45551</v>
+        <v>44651</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17200,7 +17238,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17243,7 +17281,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17257,10 +17295,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46234</v>
+        <v>45224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17273,7 +17311,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17316,7 +17354,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17330,10 +17368,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45112</v>
+        <v>45527</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17346,7 +17384,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17389,7 +17427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17403,10 +17441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46234</v>
+        <v>45609</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17419,7 +17457,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17462,7 +17500,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17476,10 +17514,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45642</v>
+        <v>44819</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17492,7 +17530,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17535,7 +17573,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17549,10 +17587,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45777</v>
+        <v>45620</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17565,7 +17603,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17608,7 +17646,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17622,10 +17660,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45777</v>
+        <v>44890</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17638,7 +17676,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17681,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17695,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45777</v>
+        <v>45588</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17711,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17754,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17768,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45554</v>
+        <v>44531</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17784,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17827,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17841,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45369</v>
+        <v>45098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17857,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17900,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17914,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45791</v>
+        <v>45616</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17930,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17973,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -17987,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45404</v>
+        <v>44995</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18003,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18046,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18063,7 +18101,7 @@
         <v>45680</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18076,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>11.2</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18119,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18133,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45707</v>
+        <v>45198</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18149,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18192,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18206,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45586</v>
+        <v>44858</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18222,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18265,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18279,10 +18317,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45707</v>
+        <v>45777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18295,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18338,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18352,10 +18390,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45450</v>
+        <v>45777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18368,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18411,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18425,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45811</v>
+        <v>45777</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18441,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18484,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18498,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45811</v>
+        <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18514,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18557,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18571,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45811</v>
+        <v>45369</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18587,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18630,24 +18668,24 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44700</v>
+        <v>45791</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18660,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18720,7 +18758,7 @@
         <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18781,153 +18819,226 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
+          <t>S 2641-2022</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>44700</v>
+      </c>
+      <c r="E243" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="n">
+        <v>0</v>
+      </c>
+      <c r="V243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244" ht="15" customHeight="1">
+      <c r="A244" t="inlineStr">
+        <is>
           <t>S 1781-2025</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D243" s="1" t="n">
+      <c r="D244" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="E243" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I243" t="n">
+      <c r="E244" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
         <v>2.8</v>
       </c>
-      <c r="J243" t="n">
-        <v>0</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="P243" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="n">
-        <v>0</v>
-      </c>
-      <c r="T243" t="n">
-        <v>0</v>
-      </c>
-      <c r="U243" t="n">
-        <v>0</v>
-      </c>
-      <c r="V243" s="2" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0</v>
+      </c>
+      <c r="V244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>S 1773-2026</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D244" s="1" t="n">
+      <c r="D245" s="1" t="n">
         <v>46191</v>
       </c>
-      <c r="E244" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
+      <c r="E245" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I244" t="n">
+      <c r="I245" t="n">
         <v>22.3</v>
       </c>
-      <c r="J244" t="n">
-        <v>0</v>
-      </c>
-      <c r="K244" t="n">
-        <v>0</v>
-      </c>
-      <c r="L244" t="n">
-        <v>0</v>
-      </c>
-      <c r="M244" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" t="n">
-        <v>0</v>
-      </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="n">
-        <v>0</v>
-      </c>
-      <c r="T244" t="n">
-        <v>0</v>
-      </c>
-      <c r="U244" t="n">
-        <v>0</v>
-      </c>
-      <c r="V244" s="2" t="inlineStr"/>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>0</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
+      <c r="V245" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,36 +1461,36 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38064-2023</t>
+          <t>A 55118-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45159</v>
+        <v>45967</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,23 +1747,18 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1777,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1789,357 +1784,362 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31051-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38064-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Vedticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 36671-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55118-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45967</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Luddfingersvamp</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 31051-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Dunmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 70363-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44535</v>
+        <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25830-2022</t>
+          <t>A 70363-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44733</v>
+        <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 25830-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44571</v>
+        <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44494</v>
+        <v>45204</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3491,8 +3491,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3535,7 +3540,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44858</v>
+        <v>45336</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3565,7 +3570,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3608,7 +3613,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3622,10 +3627,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45534</v>
+        <v>44858</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,13 +3642,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44705</v>
+        <v>45414</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45588</v>
+        <v>44868</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44868</v>
+        <v>44494</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45560</v>
+        <v>44890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>44890</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44958</v>
+        <v>44813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45191</v>
+        <v>45050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>44749</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45204</v>
+        <v>45303</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,13 +4299,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45246</v>
+        <v>44797</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4373,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4416,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4430,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44995</v>
+        <v>45376</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4450,8 +4445,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45404</v>
+        <v>45450</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45680</v>
+        <v>44958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46007</v>
+        <v>45300</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4669,8 +4669,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4718,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4732,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45369</v>
+        <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4748,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4791,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4805,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46008</v>
+        <v>45113</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4821,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4864,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4878,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45328</v>
+        <v>45803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4932,7 +4937,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45247</v>
+        <v>45884</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4961,8 +4966,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5029,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45707</v>
+        <v>46090</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5035,7 +5045,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5078,7 +5088,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5092,10 +5102,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45707</v>
+        <v>45893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5108,7 +5118,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5151,7 +5161,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5165,10 +5175,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45586</v>
+        <v>46090</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5181,7 +5191,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5224,7 +5234,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5238,10 +5248,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45811</v>
+        <v>44575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5254,7 +5264,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5297,7 +5307,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5311,10 +5321,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45811</v>
+        <v>45660</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5327,7 +5337,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5370,7 +5380,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5380,14 +5390,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45350</v>
+        <v>45903</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5401,11 +5411,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5448,7 +5458,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5462,10 +5472,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45309</v>
+        <v>44487</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5478,7 +5488,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5521,7 +5531,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5535,10 +5545,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45811</v>
+        <v>45629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5561,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5594,7 +5604,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5608,10 +5618,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45803</v>
+        <v>45495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5634,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5667,7 +5677,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5681,10 +5691,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45450</v>
+        <v>44582</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5697,7 +5707,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5740,7 +5750,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5754,10 +5764,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45629</v>
+        <v>45140</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5770,7 +5780,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5813,7 +5823,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5827,10 +5837,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45884</v>
+        <v>45329</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5848,7 +5858,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5891,7 +5901,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5905,10 +5915,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45126</v>
+        <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5921,7 +5931,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5964,7 +5974,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5974,14 +5984,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46034</v>
+        <v>45903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5994,7 +6004,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6037,7 +6047,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6051,10 +6061,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46034</v>
+        <v>44866</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6067,7 +6077,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6110,7 +6120,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6124,10 +6134,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45893</v>
+        <v>45915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6140,7 +6150,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6183,7 +6193,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6193,14 +6203,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45819</v>
+        <v>44536</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6213,7 +6223,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6256,7 +6266,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6270,10 +6280,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44498</v>
+        <v>46108</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6285,8 +6295,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6329,7 +6344,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6343,10 +6358,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45567</v>
+        <v>45525</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6359,7 +6374,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6402,7 +6417,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6412,14 +6427,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45820</v>
+        <v>45350</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6431,8 +6446,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6475,7 +6495,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6489,10 +6509,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45660</v>
+        <v>45680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6505,7 +6525,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6548,7 +6568,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6562,10 +6582,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45109</v>
+        <v>44974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6621,7 +6641,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6635,10 +6655,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46038</v>
+        <v>45554</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6650,13 +6670,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6699,7 +6714,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6713,10 +6728,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45826</v>
+        <v>46121</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6728,8 +6743,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6772,7 +6792,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6782,14 +6802,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45903</v>
+        <v>45369</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6801,13 +6821,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6850,7 +6865,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6860,14 +6875,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45629</v>
+        <v>44879</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6880,7 +6895,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6923,7 +6938,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6937,10 +6952,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45910</v>
+        <v>44993</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6953,7 +6968,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6996,7 +7011,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7010,10 +7025,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45551</v>
+        <v>45925</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7025,8 +7040,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7069,7 +7089,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7083,10 +7103,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44897</v>
+        <v>45932</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7099,7 +7119,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7142,7 +7162,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7156,10 +7176,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45915</v>
+        <v>44917</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7172,7 +7192,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7215,7 +7235,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7229,10 +7249,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45300</v>
+        <v>45620</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,13 +7264,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7293,7 +7308,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7303,14 +7318,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45903</v>
+        <v>45588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7323,7 +7338,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7366,7 +7381,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7380,10 +7395,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44917</v>
+        <v>45939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7396,7 +7411,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7439,7 +7454,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7453,10 +7468,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44999</v>
+        <v>45229</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7469,7 +7484,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7527,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7541,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45925</v>
+        <v>45588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7541,13 +7556,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7590,7 +7600,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7604,10 +7614,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45674</v>
+        <v>45706</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7620,7 +7630,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7663,7 +7673,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7677,10 +7687,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45329</v>
+        <v>45065</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7692,13 +7702,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7741,7 +7746,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7755,10 +7760,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45082</v>
+        <v>45953</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7771,7 +7776,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7814,7 +7819,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7828,10 +7833,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45271</v>
+        <v>44999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7844,7 +7849,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7887,7 +7892,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7901,10 +7906,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45099</v>
+        <v>45113</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7917,7 +7922,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7960,7 +7965,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7974,10 +7979,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45782</v>
+        <v>44496</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7990,7 +7995,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8033,7 +8038,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8047,10 +8052,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45932</v>
+        <v>45621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8063,7 +8068,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8106,7 +8111,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8120,10 +8125,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46072</v>
+        <v>45119</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8136,7 +8141,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8179,7 +8184,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8193,10 +8198,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46072</v>
+        <v>45792</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8209,7 +8214,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8252,7 +8257,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8266,10 +8271,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46072</v>
+        <v>45960</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8282,7 +8287,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8325,7 +8330,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8339,10 +8344,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8355,7 +8360,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8398,7 +8403,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8412,10 +8417,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44603</v>
+        <v>45609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8428,7 +8433,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8471,7 +8476,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8485,10 +8490,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46090</v>
+        <v>45042</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8501,7 +8506,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8544,7 +8549,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,10 +8563,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46090</v>
+        <v>45800</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8574,7 +8579,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8617,7 +8622,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8631,10 +8636,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45751</v>
+        <v>45800</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8647,7 +8652,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8690,7 +8695,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8704,10 +8709,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45113</v>
+        <v>44858</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8720,7 +8725,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8763,7 +8768,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8777,10 +8782,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45205</v>
+        <v>45019</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8798,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8836,7 +8841,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8850,10 +8855,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44890</v>
+        <v>45918</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8866,7 +8871,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8909,7 +8914,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8923,10 +8928,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44536</v>
+        <v>45019</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8939,7 +8944,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8982,7 +8987,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8996,10 +9001,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45953</v>
+        <v>45979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9012,7 +9017,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9055,7 +9060,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9069,10 +9074,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46108</v>
+        <v>45804</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9084,13 +9089,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45960</v>
+        <v>45938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9206,7 +9206,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9220,10 +9220,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45111</v>
+        <v>45912</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9279,7 +9279,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44476</v>
+        <v>45825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9352,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9366,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46121</v>
+        <v>45554</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9381,13 +9381,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9430,7 +9425,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9444,10 +9439,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45967</v>
+        <v>45674</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9460,7 +9455,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9503,7 +9498,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9513,14 +9508,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44749</v>
+        <v>46085</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9533,7 +9528,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9576,7 +9571,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9590,10 +9585,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45918</v>
+        <v>45986</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9605,8 +9600,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>11.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45979</v>
+        <v>45986</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45582</v>
+        <v>44749</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9795,7 +9795,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45119</v>
+        <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9824,8 +9824,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9868,7 +9873,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9882,10 +9887,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44748</v>
+        <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,7 +9903,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9941,7 +9946,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9955,10 +9960,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45912</v>
+        <v>45224</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9971,7 +9976,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10014,7 +10019,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10028,10 +10033,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45986</v>
+        <v>45198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10043,13 +10048,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>11.2</v>
+        <v>2.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10092,7 +10092,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45621</v>
+        <v>46153</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45706</v>
+        <v>45013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10238,7 +10238,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45986</v>
+        <v>44995</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10311,7 +10311,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45055</v>
+        <v>45042</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10384,7 +10384,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45800</v>
+        <v>44858</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10457,7 +10457,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45792</v>
+        <v>46007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10544,10 +10544,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45800</v>
+        <v>46008</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46000</v>
+        <v>45055</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10676,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45825</v>
+        <v>44819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45280</v>
+        <v>44868</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10778,13 +10778,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10827,7 +10822,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10841,10 +10836,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45804</v>
+        <v>45791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10857,7 +10852,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10900,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10914,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45065</v>
+        <v>45594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10930,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10973,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10987,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45938</v>
+        <v>45247</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11003,7 +10998,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11046,7 +11041,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11060,10 +11055,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46085</v>
+        <v>45109</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11076,7 +11071,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11119,7 +11114,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11133,10 +11128,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44866</v>
+        <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11149,7 +11144,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11192,7 +11187,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11206,10 +11201,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44749</v>
+        <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11222,7 +11217,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11265,7 +11260,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11279,10 +11274,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11295,7 +11290,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11338,7 +11333,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11352,10 +11347,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45098</v>
+        <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11368,7 +11363,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11411,7 +11406,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11425,10 +11420,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45358</v>
+        <v>45518</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11441,7 +11436,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11484,7 +11479,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11498,10 +11493,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46141</v>
+        <v>46034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11513,13 +11508,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11562,7 +11552,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11576,10 +11566,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45303</v>
+        <v>46034</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11592,7 +11582,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11635,7 +11625,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11649,10 +11639,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45019</v>
+        <v>44531</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11665,7 +11655,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11708,7 +11698,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11722,10 +11712,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45376</v>
+        <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11743,7 +11733,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11786,7 +11776,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11800,10 +11790,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45554</v>
+        <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11816,7 +11806,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11859,7 +11849,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11873,10 +11863,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46153</v>
+        <v>44866</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11889,7 +11879,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11932,7 +11922,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11946,10 +11936,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45140</v>
+        <v>44476</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11962,7 +11952,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12005,7 +11995,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12019,10 +12009,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44749</v>
+        <v>44876</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12035,7 +12025,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12078,7 +12068,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12092,10 +12082,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44993</v>
+        <v>45771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12108,7 +12098,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12151,7 +12141,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12165,10 +12155,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45594</v>
+        <v>44603</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12181,7 +12171,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12224,7 +12214,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12238,10 +12228,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45791</v>
+        <v>46176</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12254,7 +12244,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12297,7 +12287,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12311,10 +12301,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45518</v>
+        <v>45560</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12327,7 +12317,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12370,7 +12360,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12384,10 +12374,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45588</v>
+        <v>44651</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12400,7 +12390,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12443,7 +12433,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12457,10 +12447,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46176</v>
+        <v>44749</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12473,7 +12463,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12516,7 +12506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12530,10 +12520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46170</v>
+        <v>45109</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12546,7 +12536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12589,7 +12579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12603,10 +12593,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46168</v>
+        <v>45111</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12619,7 +12609,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12662,7 +12652,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12676,10 +12666,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46239</v>
+        <v>44498</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12692,7 +12682,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12735,7 +12725,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12749,10 +12739,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45554</v>
+        <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12765,7 +12755,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12808,7 +12798,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12822,10 +12812,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45169</v>
+        <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12838,7 +12828,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12881,7 +12871,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12895,10 +12885,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46240</v>
+        <v>46072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12911,7 +12901,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12954,7 +12944,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12968,10 +12958,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46240</v>
+        <v>46072</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13027,7 +13017,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13041,10 +13031,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46240</v>
+        <v>46072</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13056,13 +13046,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13105,7 +13090,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13119,10 +13104,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45229</v>
+        <v>45575</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13135,7 +13120,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13178,7 +13163,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13192,10 +13177,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46245</v>
+        <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13208,7 +13193,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13251,7 +13236,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13265,10 +13250,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46204</v>
+        <v>45370</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13280,13 +13265,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13329,7 +13309,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13343,10 +13323,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46246</v>
+        <v>45280</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13364,7 +13344,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13407,7 +13387,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13421,10 +13401,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44536</v>
+        <v>46240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13437,7 +13417,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13480,7 +13460,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13494,10 +13474,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45414</v>
+        <v>46240</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13510,7 +13490,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13553,7 +13533,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13567,10 +13547,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45248</v>
+        <v>46240</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13582,8 +13562,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13626,7 +13611,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13640,10 +13625,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44550</v>
+        <v>46239</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13656,7 +13641,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13699,7 +13684,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13713,10 +13698,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46212</v>
+        <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13728,13 +13713,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13777,7 +13757,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13791,10 +13771,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46255</v>
+        <v>45099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13807,7 +13787,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13850,7 +13830,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13864,10 +13844,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44797</v>
+        <v>45358</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13880,7 +13860,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13923,7 +13903,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13937,10 +13917,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44858</v>
+        <v>45582</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13953,7 +13933,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13996,7 +13976,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14010,10 +13990,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44496</v>
+        <v>45044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14026,7 +14006,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14069,7 +14049,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14083,10 +14063,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45629</v>
+        <v>45567</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14099,7 +14079,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14142,7 +14122,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14152,14 +14132,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46224</v>
+        <v>46245</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14172,7 +14152,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14215,7 +14195,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14229,10 +14209,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46267</v>
+        <v>45616</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14245,7 +14225,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14288,7 +14268,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14302,10 +14282,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45113</v>
+        <v>44995</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14318,7 +14298,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14361,7 +14341,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14375,10 +14355,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45012</v>
+        <v>46246</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14390,8 +14370,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>13.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14434,7 +14419,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14448,10 +14433,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44813</v>
+        <v>44909</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14464,7 +14449,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14507,7 +14492,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14521,10 +14506,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45042</v>
+        <v>46204</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14536,8 +14521,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14580,7 +14570,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14594,10 +14584,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45616</v>
+        <v>45191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14610,7 +14600,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14653,7 +14643,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14667,10 +14657,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45588</v>
+        <v>45126</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14683,7 +14673,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14726,7 +14716,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14740,10 +14730,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45588</v>
+        <v>44550</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14756,7 +14746,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14799,7 +14789,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14813,10 +14803,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44582</v>
+        <v>44536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14829,7 +14819,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14872,7 +14862,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14886,10 +14876,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46234</v>
+        <v>45616</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14902,7 +14892,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14945,7 +14935,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14959,10 +14949,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46234</v>
+        <v>45588</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14975,7 +14965,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15018,7 +15008,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15032,10 +15022,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44487</v>
+        <v>45588</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15048,7 +15038,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15091,7 +15081,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15105,10 +15095,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45050</v>
+        <v>44705</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15121,7 +15111,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15164,7 +15154,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15178,10 +15168,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15194,7 +15184,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15237,7 +15227,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15251,10 +15241,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45113</v>
+        <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15267,7 +15257,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15310,7 +15300,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15324,10 +15314,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45336</v>
+        <v>45629</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15340,7 +15330,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15383,7 +15373,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15397,10 +15387,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44845</v>
+        <v>46212</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15412,8 +15402,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15456,7 +15451,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15470,10 +15465,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45771</v>
+        <v>45229</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15486,7 +15481,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15529,7 +15524,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15543,10 +15538,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45554</v>
+        <v>45098</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15559,7 +15554,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15602,7 +15597,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15616,10 +15611,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45013</v>
+        <v>45229</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15632,7 +15627,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15675,7 +15670,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15689,10 +15684,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44909</v>
+        <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15705,7 +15700,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15748,7 +15743,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15762,10 +15757,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44901</v>
+        <v>45248</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15778,7 +15773,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15821,7 +15816,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15831,14 +15826,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44879</v>
+        <v>45309</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15851,7 +15846,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15894,7 +15889,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15908,10 +15903,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45042</v>
+        <v>46255</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15924,7 +15919,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15967,7 +15962,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15981,10 +15976,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45044</v>
+        <v>45751</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15997,7 +15992,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16040,7 +16035,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16054,10 +16049,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45109</v>
+        <v>45554</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16070,7 +16065,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16113,7 +16108,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16127,10 +16122,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44866</v>
+        <v>44748</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16143,7 +16138,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16186,7 +16181,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16196,14 +16191,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44876</v>
+        <v>46224</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16216,7 +16211,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16259,7 +16254,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16273,10 +16268,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45140</v>
+        <v>45205</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16289,7 +16284,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16332,7 +16327,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16346,10 +16341,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45525</v>
+        <v>44897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16362,7 +16357,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16405,7 +16400,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16419,10 +16414,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44858</v>
+        <v>45534</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16434,8 +16429,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16492,10 +16492,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45450</v>
+        <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16565,10 +16565,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45019</v>
+        <v>45328</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16638,10 +16638,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45575</v>
+        <v>44858</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16711,10 +16711,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45229</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16770,7 +16770,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16784,10 +16784,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44868</v>
+        <v>45098</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16843,7 +16843,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45495</v>
+        <v>45551</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16916,7 +16916,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16930,10 +16930,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45370</v>
+        <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16989,7 +16989,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17003,10 +17003,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45098</v>
+        <v>45642</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17062,7 +17062,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44575</v>
+        <v>45777</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17135,7 +17135,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17149,10 +17149,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45236</v>
+        <v>45777</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17208,7 +17208,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44651</v>
+        <v>45777</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45224</v>
+        <v>45554</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17354,7 +17354,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17368,10 +17368,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45527</v>
+        <v>46234</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17427,7 +17427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17441,10 +17441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45609</v>
+        <v>46234</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17500,7 +17500,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44819</v>
+        <v>45369</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45620</v>
+        <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17646,7 +17646,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17660,10 +17660,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44890</v>
+        <v>45404</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45588</v>
+        <v>45680</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44531</v>
+        <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45098</v>
+        <v>45586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45616</v>
+        <v>45707</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44995</v>
+        <v>45450</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45680</v>
+        <v>45811</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45198</v>
+        <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44858</v>
+        <v>45811</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18313,14 +18313,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45777</v>
+        <v>45820</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18386,14 +18386,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45777</v>
+        <v>45819</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45777</v>
+        <v>45826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45554</v>
+        <v>45082</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45369</v>
+        <v>45782</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45791</v>
+        <v>45271</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,13 +18770,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18819,7 +18814,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18829,14 +18824,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18848,8 +18843,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,36 +1461,36 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55118-2025</t>
+          <t>A 38064-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45967</v>
+        <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,17 +1747,22 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1772,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1784,362 +1789,357 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 36671-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 55118-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Luddfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 31051-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46215</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 38064-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 36671-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45204</v>
+        <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3491,13 +3491,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3540,7 +3535,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45336</v>
+        <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3570,7 +3565,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3613,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3627,10 +3622,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44858</v>
+        <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3642,8 +3637,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45414</v>
+        <v>44705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44868</v>
+        <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44494</v>
+        <v>45560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44890</v>
+        <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44890</v>
+        <v>44958</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44813</v>
+        <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45050</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44749</v>
+        <v>45191</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45303</v>
+        <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,8 +4299,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44797</v>
+        <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45376</v>
+        <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4445,13 +4450,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45450</v>
+        <v>45328</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44958</v>
+        <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45300</v>
+        <v>45369</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4669,13 +4669,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4718,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44845</v>
+        <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4748,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4791,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4805,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45113</v>
+        <v>45126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4821,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4864,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4878,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45803</v>
+        <v>45350</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4893,8 +4888,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45884</v>
+        <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4966,13 +4966,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46090</v>
+        <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5045,7 +5040,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5088,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5102,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45893</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5118,7 +5113,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5161,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5175,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46090</v>
+        <v>45109</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5191,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5248,10 +5243,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44575</v>
+        <v>45707</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5264,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5307,7 +5302,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45660</v>
+        <v>45707</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5337,7 +5332,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5380,7 +5375,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5390,14 +5385,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45903</v>
+        <v>45586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5409,13 +5404,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5458,7 +5448,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5472,10 +5462,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44487</v>
+        <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5488,7 +5478,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5531,7 +5521,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5545,10 +5535,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45629</v>
+        <v>45811</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5561,7 +5551,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5604,7 +5594,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5618,10 +5608,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45495</v>
+        <v>45811</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5634,7 +5624,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5677,7 +5667,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5691,10 +5681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44582</v>
+        <v>46034</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5707,7 +5697,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5750,7 +5740,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5764,10 +5754,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45140</v>
+        <v>46034</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5780,7 +5770,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5823,7 +5813,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5837,10 +5827,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45329</v>
+        <v>45450</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5852,13 +5842,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5901,7 +5886,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5915,10 +5900,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45910</v>
+        <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5931,7 +5916,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5974,7 +5959,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5984,14 +5969,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45903</v>
+        <v>45884</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6003,8 +5988,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6047,7 +6037,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6061,10 +6051,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44866</v>
+        <v>45551</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6077,7 +6067,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6120,7 +6110,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6134,10 +6124,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45915</v>
+        <v>44897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6150,7 +6140,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6193,7 +6183,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6207,10 +6197,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44536</v>
+        <v>45300</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6222,8 +6212,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6266,7 +6261,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6276,14 +6271,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46108</v>
+        <v>45819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6295,13 +6290,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6344,7 +6334,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6354,14 +6344,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45525</v>
+        <v>45820</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6374,7 +6364,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6417,7 +6407,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6431,10 +6421,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45350</v>
+        <v>45893</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6446,13 +6436,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6495,7 +6480,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6509,10 +6494,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45680</v>
+        <v>44917</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6525,7 +6510,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6568,7 +6553,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6582,10 +6567,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44974</v>
+        <v>44999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6598,7 +6583,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6641,7 +6626,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6655,10 +6640,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45554</v>
+        <v>45660</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6671,7 +6656,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6714,7 +6699,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6728,10 +6713,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46121</v>
+        <v>45826</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6743,13 +6728,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6792,7 +6772,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6806,10 +6786,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45369</v>
+        <v>45674</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6822,7 +6802,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6865,7 +6845,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6875,14 +6855,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44879</v>
+        <v>45329</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6894,8 +6874,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6938,7 +6923,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6948,14 +6933,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44993</v>
+        <v>45903</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6967,8 +6952,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7011,7 +7001,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7025,10 +7015,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45925</v>
+        <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7040,13 +7030,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7089,7 +7074,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7103,10 +7088,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45932</v>
+        <v>45910</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7119,7 +7104,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7162,7 +7147,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7176,10 +7161,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44917</v>
+        <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7192,7 +7177,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7235,7 +7220,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7249,10 +7234,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45620</v>
+        <v>45915</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7265,7 +7250,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7308,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7318,14 +7303,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45588</v>
+        <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7338,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7381,7 +7366,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7395,10 +7380,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45939</v>
+        <v>44603</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7411,7 +7396,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7454,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7468,10 +7453,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45229</v>
+        <v>45082</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7484,7 +7469,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7527,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7541,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45588</v>
+        <v>45925</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7556,8 +7541,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7600,7 +7590,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7614,10 +7604,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45706</v>
+        <v>46038</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7629,8 +7619,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7673,7 +7668,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7687,10 +7682,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45065</v>
+        <v>45271</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7703,7 +7698,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7746,7 +7741,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45953</v>
+        <v>45751</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7776,7 +7771,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7819,7 +7814,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7833,10 +7828,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44999</v>
+        <v>45932</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7849,7 +7844,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7892,7 +7887,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7906,10 +7901,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45113</v>
+        <v>45782</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7922,7 +7917,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7965,7 +7960,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7979,10 +7974,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44496</v>
+        <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7995,7 +7990,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.5</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8038,7 +8033,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8052,10 +8047,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45621</v>
+        <v>44890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8068,7 +8063,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8111,7 +8106,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8125,10 +8120,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45119</v>
+        <v>45939</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8141,7 +8136,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8184,7 +8179,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8198,10 +8193,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45792</v>
+        <v>44536</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8214,7 +8209,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8257,7 +8252,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8271,10 +8266,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8287,7 +8282,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8330,7 +8325,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8344,10 +8339,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45967</v>
+        <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8360,7 +8355,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8403,7 +8398,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8417,10 +8412,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45609</v>
+        <v>45113</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8433,7 +8428,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8476,7 +8471,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8490,10 +8485,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45042</v>
+        <v>44476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8506,7 +8501,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8549,7 +8544,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8563,10 +8558,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45800</v>
+        <v>45960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8579,7 +8574,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8622,7 +8617,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8632,14 +8627,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45800</v>
+        <v>44749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8652,7 +8647,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8695,7 +8690,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8709,10 +8704,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44858</v>
+        <v>45967</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8725,7 +8720,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8768,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8782,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45019</v>
+        <v>45582</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8798,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8841,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8855,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45918</v>
+        <v>44748</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8871,7 +8866,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8914,7 +8909,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8928,10 +8923,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45019</v>
+        <v>45979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8944,7 +8939,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8987,7 +8982,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9001,10 +8996,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45979</v>
+        <v>46072</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9017,7 +9012,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9060,7 +9055,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9074,10 +9069,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45804</v>
+        <v>46072</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9090,7 +9085,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9133,7 +9128,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9147,10 +9142,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45938</v>
+        <v>46072</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9163,7 +9158,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9206,7 +9201,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9220,10 +9215,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45912</v>
+        <v>45055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9236,7 +9231,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9279,7 +9274,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9293,10 +9288,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45825</v>
+        <v>45986</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9308,8 +9303,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>11.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9352,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9366,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45554</v>
+        <v>45986</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9425,7 +9425,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45674</v>
+        <v>45280</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9454,8 +9454,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9498,7 +9503,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9512,10 +9517,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9528,7 +9533,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9571,7 +9576,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9585,10 +9590,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45986</v>
+        <v>46000</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9600,13 +9605,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45986</v>
+        <v>44866</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44749</v>
+        <v>46090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9795,7 +9795,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46141</v>
+        <v>44749</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9824,13 +9824,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9873,7 +9868,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9887,10 +9882,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9903,7 +9898,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9946,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9960,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45224</v>
+        <v>45112</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9976,7 +9971,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10019,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10033,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45198</v>
+        <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10049,7 +10044,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10092,7 +10087,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10106,10 +10101,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46153</v>
+        <v>45098</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10122,7 +10117,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10165,7 +10160,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10179,10 +10174,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45013</v>
+        <v>45358</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10195,7 +10190,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10238,7 +10233,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10252,10 +10247,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44995</v>
+        <v>45303</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10268,7 +10263,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10311,7 +10306,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10325,10 +10320,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45042</v>
+        <v>45019</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10341,7 +10336,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10384,7 +10379,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44858</v>
+        <v>45376</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10413,8 +10408,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10457,7 +10457,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46007</v>
+        <v>45554</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10530,7 +10530,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10544,10 +10544,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46008</v>
+        <v>45140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45055</v>
+        <v>44749</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10676,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44819</v>
+        <v>46108</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10705,8 +10705,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10754,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10768,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44868</v>
+        <v>44993</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10779,7 +10784,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10822,7 +10827,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10836,10 +10841,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45791</v>
+        <v>45588</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10852,7 +10857,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10895,7 +10900,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10909,10 +10914,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45594</v>
+        <v>46121</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10924,8 +10929,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>8.1</v>
+        <v>4.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10968,7 +10978,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10982,10 +10992,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45247</v>
+        <v>45554</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10998,7 +11008,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>8</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11041,7 +11051,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11055,10 +11065,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45109</v>
+        <v>45169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11071,7 +11081,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11114,7 +11124,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45246</v>
+        <v>45229</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11144,7 +11154,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11187,7 +11197,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11201,10 +11211,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45169</v>
+        <v>44536</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11217,7 +11227,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11260,7 +11270,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11274,10 +11284,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45113</v>
+        <v>45918</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11290,7 +11300,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11333,7 +11343,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11347,10 +11357,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45012</v>
+        <v>45414</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11363,7 +11373,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11406,7 +11416,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11420,10 +11430,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45518</v>
+        <v>45119</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11436,7 +11446,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11479,7 +11489,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11493,10 +11503,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46034</v>
+        <v>45248</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11509,7 +11519,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11552,7 +11562,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11566,10 +11576,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46034</v>
+        <v>44550</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11582,7 +11592,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11625,7 +11635,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11639,10 +11649,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44531</v>
+        <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11655,7 +11665,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11698,7 +11708,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11712,10 +11722,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46038</v>
+        <v>45621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11727,13 +11737,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11776,7 +11781,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11790,10 +11795,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45098</v>
+        <v>45706</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11806,7 +11811,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11849,7 +11854,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11863,10 +11868,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44866</v>
+        <v>44797</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11879,7 +11884,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11922,7 +11927,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11936,10 +11941,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44476</v>
+        <v>44858</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11952,7 +11957,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11995,7 +12000,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12009,10 +12014,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44876</v>
+        <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12025,7 +12030,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12068,7 +12073,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12082,10 +12087,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45771</v>
+        <v>45792</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12098,7 +12103,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12141,7 +12146,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12155,10 +12160,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44603</v>
+        <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12171,7 +12176,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12214,7 +12219,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12228,10 +12233,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46176</v>
+        <v>45629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12244,7 +12249,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12287,7 +12292,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12301,10 +12306,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45560</v>
+        <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12317,7 +12322,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12360,7 +12365,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12374,10 +12379,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44651</v>
+        <v>45825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12390,7 +12395,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12433,7 +12438,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12447,10 +12452,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44749</v>
+        <v>45113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12463,7 +12468,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12506,7 +12511,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12520,10 +12525,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45109</v>
+        <v>45804</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12536,7 +12541,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12579,7 +12584,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12593,10 +12598,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45111</v>
+        <v>45065</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12609,7 +12614,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12652,7 +12657,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12666,10 +12671,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44498</v>
+        <v>45938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12682,7 +12687,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12725,7 +12730,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12739,10 +12744,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44901</v>
+        <v>45012</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12755,7 +12760,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12798,7 +12803,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12812,10 +12817,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46170</v>
+        <v>46085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12828,7 +12833,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12871,7 +12876,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12885,10 +12890,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46072</v>
+        <v>44813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12901,7 +12906,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12944,7 +12949,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12958,10 +12963,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46072</v>
+        <v>45042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12974,7 +12979,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13017,7 +13022,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13031,10 +13036,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46072</v>
+        <v>45616</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13047,7 +13052,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13090,7 +13095,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13104,10 +13109,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45575</v>
+        <v>45588</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13120,7 +13125,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13163,7 +13168,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13177,10 +13182,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46168</v>
+        <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13193,7 +13198,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13236,7 +13241,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13250,10 +13255,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45370</v>
+        <v>46141</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13265,8 +13270,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13309,7 +13319,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13323,10 +13333,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45280</v>
+        <v>44582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13338,13 +13348,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13387,7 +13392,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13401,10 +13406,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46240</v>
+        <v>44487</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13417,7 +13422,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13460,7 +13465,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13474,10 +13479,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46240</v>
+        <v>46153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13490,7 +13495,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13533,7 +13538,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13547,10 +13552,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46240</v>
+        <v>45050</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13562,13 +13567,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13611,7 +13611,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13625,10 +13625,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46239</v>
+        <v>45229</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13684,7 +13684,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13698,10 +13698,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45588</v>
+        <v>45113</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13771,10 +13771,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45099</v>
+        <v>45594</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>8.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13830,7 +13830,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13844,10 +13844,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45358</v>
+        <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13903,7 +13903,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45582</v>
+        <v>45518</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13990,10 +13990,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45044</v>
+        <v>45336</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14063,10 +14063,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45567</v>
+        <v>44845</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14122,7 +14122,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14136,10 +14136,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46245</v>
+        <v>45771</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14195,7 +14195,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45616</v>
+        <v>45554</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14268,7 +14268,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14282,10 +14282,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44995</v>
+        <v>45013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14341,7 +14341,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46246</v>
+        <v>46176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14370,13 +14370,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>13.1</v>
+        <v>5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14419,7 +14414,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14433,10 +14428,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44909</v>
+        <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14449,7 +14444,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14492,7 +14487,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14506,10 +14501,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46204</v>
+        <v>44909</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14521,13 +14516,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14570,7 +14560,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14584,10 +14574,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14600,7 +14590,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14643,7 +14633,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14657,10 +14647,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45126</v>
+        <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14673,7 +14663,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14716,7 +14706,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14726,14 +14716,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44550</v>
+        <v>44879</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14746,7 +14736,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14789,7 +14779,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14803,10 +14793,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44536</v>
+        <v>45042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14819,7 +14809,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14862,7 +14852,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14876,10 +14866,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45616</v>
+        <v>45044</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14892,7 +14882,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14935,7 +14925,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14949,10 +14939,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45588</v>
+        <v>46240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14965,7 +14955,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15008,7 +14998,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15022,10 +15012,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45588</v>
+        <v>46240</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15038,7 +15028,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15081,7 +15071,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15095,10 +15085,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44705</v>
+        <v>45109</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15111,7 +15101,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15154,7 +15144,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15168,10 +15158,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45629</v>
+        <v>46240</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15183,8 +15173,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15227,7 +15222,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15241,10 +15236,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45140</v>
+        <v>46245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15257,7 +15252,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15300,7 +15295,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15314,10 +15309,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45629</v>
+        <v>46204</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15329,8 +15324,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15373,7 +15373,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15387,10 +15387,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46212</v>
+        <v>46246</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15404,11 +15404,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.7</v>
+        <v>13.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15451,7 +15451,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15465,10 +15465,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45229</v>
+        <v>44866</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45098</v>
+        <v>44876</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15611,10 +15611,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45229</v>
+        <v>45140</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15684,10 +15684,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45236</v>
+        <v>45525</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15743,7 +15743,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15757,10 +15757,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45248</v>
+        <v>44858</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45309</v>
+        <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15889,7 +15889,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46255</v>
+        <v>45019</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15962,7 +15962,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45751</v>
+        <v>45575</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45554</v>
+        <v>45229</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44748</v>
+        <v>44868</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16191,14 +16191,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46224</v>
+        <v>46212</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16210,8 +16210,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16254,7 +16259,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16268,10 +16273,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45205</v>
+        <v>46255</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16284,7 +16289,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16327,7 +16332,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16341,10 +16346,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44897</v>
+        <v>45495</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16357,7 +16362,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16400,7 +16405,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16414,10 +16419,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45534</v>
+        <v>45370</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16429,13 +16434,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>11.2</v>
+        <v>3.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16492,10 +16492,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45527</v>
+        <v>45098</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16565,10 +16565,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45328</v>
+        <v>44575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16638,10 +16638,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44858</v>
+        <v>45236</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16697,7 +16697,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16711,10 +16711,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46267</v>
+        <v>44651</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16770,7 +16770,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16784,10 +16784,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45098</v>
+        <v>45224</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16843,7 +16843,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45551</v>
+        <v>45527</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16916,7 +16916,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16926,14 +16926,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45112</v>
+        <v>46224</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16989,7 +16989,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17003,10 +17003,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45642</v>
+        <v>46267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17062,7 +17062,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45777</v>
+        <v>45609</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17135,7 +17135,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17149,10 +17149,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45777</v>
+        <v>44819</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17208,7 +17208,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45777</v>
+        <v>45620</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45554</v>
+        <v>44890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17354,7 +17354,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17368,10 +17368,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46234</v>
+        <v>45588</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17427,7 +17427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17441,10 +17441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46234</v>
+        <v>44531</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17500,7 +17500,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45369</v>
+        <v>45098</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45791</v>
+        <v>45616</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17646,7 +17646,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17660,10 +17660,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45404</v>
+        <v>44995</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45680</v>
+        <v>46234</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45707</v>
+        <v>46234</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45586</v>
+        <v>45680</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45707</v>
+        <v>45198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45450</v>
+        <v>44858</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45811</v>
+        <v>45777</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45811</v>
+        <v>45777</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45811</v>
+        <v>45777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18313,14 +18313,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45820</v>
+        <v>46239</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18386,14 +18386,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45819</v>
+        <v>45554</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45826</v>
+        <v>45369</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45082</v>
+        <v>45791</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45782</v>
+        <v>45404</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45271</v>
+        <v>45680</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.5</v>
+        <v>11.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,8 +18770,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18814,7 +18819,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18824,14 +18829,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,13 +18848,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 37754-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44999</v>
+        <v>46279</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,43 +1461,47 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Blåsippa
+Orre</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 37754-2026</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1511,10 +1515,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46279</v>
+        <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1527,13 +1531,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1567,40 +1571,36 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa
-Orre</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38064-2023</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45159</v>
+        <v>45873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,13 +1747,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1789,357 +1784,362 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55118-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 31051-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38064-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vedticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 36671-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55118-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45967</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Luddfingersvamp</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 31051-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Dunmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 64999-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44571</v>
+        <v>44514</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64999-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44514</v>
+        <v>44571</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45534</v>
+        <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,13 +3637,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3681,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44705</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3711,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3754,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3768,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45588</v>
+        <v>45204</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3788,8 +3783,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45560</v>
+        <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44868</v>
+        <v>45414</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44958</v>
+        <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44974</v>
+        <v>44890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>44890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45191</v>
+        <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45204</v>
+        <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,13 +4299,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45246</v>
+        <v>45376</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4377,8 +4372,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44995</v>
+        <v>44845</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45328</v>
+        <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45247</v>
+        <v>44487</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45369</v>
+        <v>45495</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45629</v>
+        <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45126</v>
+        <v>45329</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4815,8 +4815,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4864,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4878,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45350</v>
+        <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4888,13 +4893,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45309</v>
+        <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44498</v>
+        <v>44974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>45554</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45109</v>
+        <v>45369</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5239,14 +5239,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45707</v>
+        <v>45820</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5312,14 +5312,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45707</v>
+        <v>45819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45586</v>
+        <v>45826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5448,7 +5448,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45811</v>
+        <v>46072</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45811</v>
+        <v>46072</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45811</v>
+        <v>46072</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46034</v>
+        <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5754,10 +5754,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46034</v>
+        <v>45229</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5813,7 +5813,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5827,10 +5827,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45450</v>
+        <v>45588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5886,7 +5886,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45803</v>
+        <v>45113</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45884</v>
+        <v>46090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5988,13 +5988,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6037,7 +6032,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6051,10 +6046,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45551</v>
+        <v>44999</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6067,7 +6062,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6110,7 +6105,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6124,10 +6119,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44897</v>
+        <v>46090</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6140,7 +6135,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6183,7 +6178,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6197,10 +6192,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45300</v>
+        <v>45113</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6212,13 +6207,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6261,7 +6251,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6271,14 +6261,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45819</v>
+        <v>44496</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6291,7 +6281,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6334,7 +6324,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6344,14 +6334,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45820</v>
+        <v>45082</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6364,7 +6354,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6407,7 +6397,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6421,10 +6411,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45893</v>
+        <v>45803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6437,7 +6427,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6480,7 +6470,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6494,10 +6484,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44917</v>
+        <v>45884</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6509,8 +6499,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6553,7 +6548,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6567,10 +6562,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44999</v>
+        <v>45782</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6583,7 +6578,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6626,7 +6621,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6640,10 +6635,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45660</v>
+        <v>45271</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6656,7 +6651,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6699,7 +6694,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6713,10 +6708,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45826</v>
+        <v>45609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6729,7 +6724,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6772,7 +6767,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6786,10 +6781,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45674</v>
+        <v>46108</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6801,8 +6796,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45329</v>
+        <v>45042</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6874,13 +6874,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6923,7 +6918,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6933,14 +6928,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45903</v>
+        <v>45019</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6952,13 +6947,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7001,7 +6991,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7015,10 +7005,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45629</v>
+        <v>45019</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7031,7 +7021,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7074,7 +7064,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7088,10 +7078,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45910</v>
+        <v>45893</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7104,7 +7094,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7147,7 +7137,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7161,10 +7151,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45099</v>
+        <v>46121</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7176,8 +7166,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7220,7 +7215,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7234,10 +7229,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45915</v>
+        <v>45674</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7250,7 +7245,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7293,7 +7288,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7303,14 +7298,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45903</v>
+        <v>45660</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7323,7 +7318,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7366,7 +7361,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7380,10 +7375,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44603</v>
+        <v>44749</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7396,7 +7391,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7439,7 +7434,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7449,14 +7444,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45082</v>
+        <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7468,8 +7463,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45925</v>
+        <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7541,13 +7541,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7590,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7604,10 +7599,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46038</v>
+        <v>45910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7619,13 +7614,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7668,7 +7658,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7678,14 +7668,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45271</v>
+        <v>45903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7698,7 +7688,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7741,7 +7731,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7755,10 +7745,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45751</v>
+        <v>45915</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7771,7 +7761,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7814,7 +7804,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7828,10 +7818,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45932</v>
+        <v>45706</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7844,7 +7834,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7887,7 +7877,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7901,10 +7891,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45782</v>
+        <v>45224</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7917,7 +7907,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7960,7 +7950,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7974,10 +7964,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45205</v>
+        <v>45198</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7990,7 +7980,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8033,7 +8023,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8047,10 +8037,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44890</v>
+        <v>45065</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8063,7 +8053,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8106,7 +8096,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8120,10 +8110,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45939</v>
+        <v>45013</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8136,7 +8126,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8179,7 +8169,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8193,10 +8183,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44536</v>
+        <v>45042</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8209,7 +8199,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8252,7 +8242,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8266,10 +8256,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45953</v>
+        <v>44858</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8282,7 +8272,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8325,7 +8315,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8339,10 +8329,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45111</v>
+        <v>45621</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8355,7 +8345,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8398,7 +8388,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8412,10 +8402,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45113</v>
+        <v>45119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8428,7 +8418,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8471,7 +8461,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8485,10 +8475,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44476</v>
+        <v>45055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8501,7 +8491,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8544,7 +8534,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,10 +8548,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45960</v>
+        <v>45792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8574,7 +8564,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8617,7 +8607,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8627,14 +8617,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44749</v>
+        <v>44819</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8647,7 +8637,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8690,7 +8680,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8704,10 +8694,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45967</v>
+        <v>44868</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8720,7 +8710,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8763,7 +8753,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8777,10 +8767,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45582</v>
+        <v>45247</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8783,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8836,7 +8826,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8850,10 +8840,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44748</v>
+        <v>45246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8866,7 +8856,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8909,7 +8899,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8923,10 +8913,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45979</v>
+        <v>45169</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8939,7 +8929,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8982,7 +8972,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8996,10 +8986,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46072</v>
+        <v>45113</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9012,7 +9002,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9055,7 +9045,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9069,10 +9059,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46072</v>
+        <v>45800</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9085,7 +9075,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9128,7 +9118,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9142,10 +9132,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46072</v>
+        <v>45800</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9158,7 +9148,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9201,7 +9191,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9215,10 +9205,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45055</v>
+        <v>45012</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9231,7 +9221,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9274,7 +9264,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9288,10 +9278,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45986</v>
+        <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9303,13 +9293,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9352,7 +9337,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9366,10 +9351,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45986</v>
+        <v>45804</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9382,7 +9367,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9425,7 +9410,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9439,10 +9424,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45280</v>
+        <v>45938</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9454,13 +9439,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9503,7 +9483,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9517,10 +9497,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46090</v>
+        <v>45912</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9533,7 +9513,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9576,7 +9556,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9590,10 +9570,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46000</v>
+        <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9605,8 +9585,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9649,7 +9634,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9663,10 +9648,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44866</v>
+        <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,7 +9664,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9722,7 +9707,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9736,10 +9721,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9752,7 +9737,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9795,7 +9780,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9809,10 +9794,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44749</v>
+        <v>44531</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9825,7 +9810,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9868,7 +9853,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9882,10 +9867,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46007</v>
+        <v>45098</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,7 +9883,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9941,7 +9926,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9955,10 +9940,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45112</v>
+        <v>46141</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9970,8 +9955,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10014,7 +10004,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10028,10 +10018,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46008</v>
+        <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10044,7 +10034,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10087,7 +10077,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10101,10 +10091,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45098</v>
+        <v>44476</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10117,7 +10107,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10160,7 +10150,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10174,10 +10164,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45358</v>
+        <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10190,7 +10180,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10233,7 +10223,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10247,10 +10237,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45303</v>
+        <v>45771</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10263,7 +10253,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10306,7 +10296,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10320,10 +10310,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45019</v>
+        <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10336,7 +10326,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10379,7 +10369,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10393,10 +10383,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45376</v>
+        <v>45932</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10408,13 +10398,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10457,7 +10442,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10471,10 +10456,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45554</v>
+        <v>44651</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10487,7 +10472,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10530,7 +10515,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10544,10 +10529,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45140</v>
+        <v>46153</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10560,7 +10545,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10603,7 +10588,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10617,10 +10602,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44749</v>
+        <v>45109</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10633,7 +10618,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10676,7 +10661,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10690,10 +10675,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46108</v>
+        <v>44498</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10705,13 +10690,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10754,7 +10734,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10768,10 +10748,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44993</v>
+        <v>44901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10784,7 +10764,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10827,7 +10807,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10841,10 +10821,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45588</v>
+        <v>45791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10857,7 +10837,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10900,7 +10880,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10914,10 +10894,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46121</v>
+        <v>45594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10929,13 +10909,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10978,7 +10953,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10992,10 +10967,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45554</v>
+        <v>45575</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11008,7 +10983,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11051,7 +11026,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11065,10 +11040,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45169</v>
+        <v>45518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11081,7 +11056,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11124,7 +11099,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11138,10 +11113,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45229</v>
+        <v>45939</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11154,7 +11129,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11197,7 +11172,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11211,10 +11186,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44536</v>
+        <v>45588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11227,7 +11202,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11270,7 +11245,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11284,10 +11259,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45918</v>
+        <v>45582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11300,7 +11275,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11343,7 +11318,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11357,10 +11332,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45414</v>
+        <v>45044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11373,7 +11348,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11416,7 +11391,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11430,10 +11405,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45119</v>
+        <v>46176</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11446,7 +11421,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11489,7 +11464,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11503,10 +11478,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45248</v>
+        <v>45567</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11519,7 +11494,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11562,7 +11537,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11576,10 +11551,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44550</v>
+        <v>45616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11592,7 +11567,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11635,7 +11610,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11649,10 +11624,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45912</v>
+        <v>44995</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11665,7 +11640,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11708,7 +11683,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11722,10 +11697,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45621</v>
+        <v>45953</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11738,7 +11713,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11781,7 +11756,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11795,10 +11770,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45706</v>
+        <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11811,7 +11786,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11854,7 +11829,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11868,10 +11843,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44797</v>
+        <v>45191</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11884,7 +11859,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11927,7 +11902,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11941,10 +11916,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44858</v>
+        <v>44550</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11957,7 +11932,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12000,7 +11975,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12014,10 +11989,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45800</v>
+        <v>44536</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12030,7 +12005,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12073,7 +12048,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12087,10 +12062,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45792</v>
+        <v>46168</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12103,7 +12078,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12146,7 +12121,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12160,10 +12135,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44496</v>
+        <v>45616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12176,7 +12151,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12219,7 +12194,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12233,10 +12208,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45629</v>
+        <v>45960</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12249,7 +12224,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12292,7 +12267,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12306,10 +12281,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45800</v>
+        <v>45588</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12322,7 +12297,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12365,7 +12340,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12379,10 +12354,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45825</v>
+        <v>45588</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12395,7 +12370,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12438,7 +12413,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12452,10 +12427,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45113</v>
+        <v>45629</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12468,7 +12443,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12511,7 +12486,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12525,10 +12500,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45804</v>
+        <v>45967</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12541,7 +12516,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12584,7 +12559,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12598,10 +12573,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45065</v>
+        <v>45629</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12614,7 +12589,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12657,7 +12632,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12671,10 +12646,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45938</v>
+        <v>45229</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12687,7 +12662,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12730,7 +12705,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12744,10 +12719,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45012</v>
+        <v>45098</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12760,7 +12735,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12803,7 +12778,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12817,10 +12792,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46085</v>
+        <v>45979</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12833,7 +12808,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12876,7 +12851,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12890,10 +12865,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44813</v>
+        <v>46245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12906,7 +12881,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12949,7 +12924,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12963,10 +12938,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45042</v>
+        <v>45248</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12979,7 +12954,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13022,7 +12997,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13036,10 +13011,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45616</v>
+        <v>46246</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13051,8 +13026,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>13.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13095,7 +13075,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13109,10 +13089,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45588</v>
+        <v>45986</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13124,8 +13104,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>5.6</v>
+        <v>11.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13168,7 +13153,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13182,10 +13167,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45588</v>
+        <v>46204</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13197,8 +13182,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13241,7 +13231,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13255,10 +13245,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46141</v>
+        <v>45986</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13270,13 +13260,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13319,7 +13304,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13333,10 +13318,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44582</v>
+        <v>44748</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13349,7 +13334,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13392,7 +13377,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13406,10 +13391,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44487</v>
+        <v>45303</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13422,7 +13407,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13465,7 +13450,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13479,10 +13464,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46153</v>
+        <v>46212</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13494,8 +13479,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13538,7 +13528,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13552,10 +13542,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45050</v>
+        <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13568,7 +13558,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13611,7 +13601,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13625,10 +13615,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45229</v>
+        <v>46000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13641,7 +13631,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13684,7 +13674,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13698,10 +13688,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45113</v>
+        <v>45450</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13714,7 +13704,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13757,7 +13747,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13767,14 +13757,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45594</v>
+        <v>46224</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13787,7 +13777,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13830,7 +13820,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13844,10 +13834,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45791</v>
+        <v>44958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13860,7 +13850,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13903,7 +13893,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13917,10 +13907,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45518</v>
+        <v>45300</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13932,8 +13922,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13976,7 +13971,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13990,10 +13985,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45336</v>
+        <v>46267</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14006,7 +14001,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14049,7 +14044,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14063,10 +14058,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44845</v>
+        <v>45140</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14079,7 +14074,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14122,7 +14117,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14136,10 +14131,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45771</v>
+        <v>44866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14152,7 +14147,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14195,7 +14190,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14209,10 +14204,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45554</v>
+        <v>46007</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14225,7 +14220,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14268,7 +14263,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14282,10 +14277,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45013</v>
+        <v>46008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14298,7 +14293,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14341,7 +14336,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14355,10 +14350,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46176</v>
+        <v>45350</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14370,8 +14365,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14414,7 +14414,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46170</v>
+        <v>45680</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14487,7 +14487,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14497,14 +14497,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44909</v>
+        <v>44879</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14560,7 +14560,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44901</v>
+        <v>44993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14633,7 +14633,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46168</v>
+        <v>44917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14706,7 +14706,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14716,14 +14716,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44879</v>
+        <v>45620</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14779,7 +14779,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14793,10 +14793,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45042</v>
+        <v>44858</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14866,10 +14866,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45044</v>
+        <v>46234</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14939,10 +14939,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46240</v>
+        <v>45554</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15085,10 +15085,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45109</v>
+        <v>46240</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15161,7 +15161,7 @@
         <v>46240</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15173,13 +15173,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15222,7 +15217,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15236,10 +15231,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46245</v>
+        <v>46034</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15252,7 +15247,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15295,7 +15290,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15309,10 +15304,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15324,13 +15319,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15373,7 +15363,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15387,10 +15377,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15408,7 +15398,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>13.1</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15451,7 +15441,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15465,10 +15455,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44866</v>
+        <v>46034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15481,7 +15471,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15524,7 +15514,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15538,10 +15528,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44876</v>
+        <v>44995</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15554,7 +15544,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15597,7 +15587,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15611,10 +15601,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45140</v>
+        <v>45109</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15627,7 +15617,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15670,7 +15660,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15684,10 +15674,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45525</v>
+        <v>46038</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15699,8 +15689,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15743,7 +15738,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15757,10 +15752,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44858</v>
+        <v>45560</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15773,7 +15768,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15816,7 +15811,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15830,10 +15825,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45450</v>
+        <v>44749</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15846,7 +15841,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15889,7 +15884,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15903,10 +15898,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45019</v>
+        <v>45111</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15919,7 +15914,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15962,7 +15957,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15976,10 +15971,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45575</v>
+        <v>45370</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15992,7 +15987,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16035,7 +16030,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16049,10 +16044,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45229</v>
+        <v>45280</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16064,8 +16059,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>9</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44868</v>
+        <v>45099</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46212</v>
+        <v>45358</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16210,13 +16210,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16259,7 +16254,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16273,10 +16268,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46255</v>
+        <v>44909</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16289,7 +16284,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16332,7 +16327,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16346,10 +16341,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45495</v>
+        <v>45126</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16362,7 +16357,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16405,7 +16400,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16419,10 +16414,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45370</v>
+        <v>44705</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16435,7 +16430,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16478,7 +16473,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16492,10 +16487,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45098</v>
+        <v>45140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16508,7 +16503,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16551,7 +16546,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16565,10 +16560,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44575</v>
+        <v>45229</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16581,7 +16576,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16641,7 +16636,7 @@
         <v>45236</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16697,7 +16692,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16711,10 +16706,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44651</v>
+        <v>45309</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16727,7 +16722,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16770,7 +16765,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16784,10 +16779,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45224</v>
+        <v>45751</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16800,7 +16795,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16843,7 +16838,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16857,10 +16852,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45527</v>
+        <v>45554</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16873,7 +16868,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16916,7 +16911,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16926,14 +16921,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46224</v>
+        <v>45205</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16946,7 +16941,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>7.2</v>
+        <v>0.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16989,7 +16984,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17003,10 +16998,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46267</v>
+        <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17019,7 +17014,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17062,7 +17057,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17076,10 +17071,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45609</v>
+        <v>45534</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17091,8 +17086,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17135,7 +17135,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17149,10 +17149,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44819</v>
+        <v>45527</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17208,7 +17208,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45620</v>
+        <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17295,10 +17295,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44890</v>
+        <v>44858</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17354,7 +17354,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17368,10 +17368,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45588</v>
+        <v>45098</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17427,7 +17427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17441,10 +17441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44531</v>
+        <v>45551</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17500,7 +17500,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45098</v>
+        <v>45112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45616</v>
+        <v>45642</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17646,7 +17646,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17660,10 +17660,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44995</v>
+        <v>45777</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46234</v>
+        <v>45777</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46234</v>
+        <v>45777</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45680</v>
+        <v>45554</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45198</v>
+        <v>45369</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44858</v>
+        <v>45791</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45777</v>
+        <v>45404</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45777</v>
+        <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.7</v>
+        <v>11.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45777</v>
+        <v>45707</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46239</v>
+        <v>45586</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18390,10 +18390,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45554</v>
+        <v>45707</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45369</v>
+        <v>45450</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45791</v>
+        <v>45811</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45404</v>
+        <v>45811</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45680</v>
+        <v>45811</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,13 +18770,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18819,7 +18814,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18829,14 +18824,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18848,8 +18843,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37754-2026</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46279</v>
+        <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,149 +1461,149 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37754-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Orre</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32887-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Gulnål</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 36671-2025</t>
+          <t>A 55118-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45873</v>
+        <v>45967</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1748,17 +1748,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1788,358 +1788,358 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 31051-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 38064-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 36671-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Grönpyrola</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 55118-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45967</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Luddfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 31051-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46215</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Dunmossa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38064-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64999-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44514</v>
+        <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 64999-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44571</v>
+        <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44749</v>
+        <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,8 +3637,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3681,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3695,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>45588</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3711,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3754,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3768,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45204</v>
+        <v>45560</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3783,13 +3788,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45336</v>
+        <v>44974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45414</v>
+        <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44868</v>
+        <v>44958</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44890</v>
+        <v>45191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44890</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44813</v>
+        <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44797</v>
+        <v>44705</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45376</v>
+        <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4372,13 +4372,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4416,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4430,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44845</v>
+        <v>45204</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4450,8 +4445,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44575</v>
+        <v>45369</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44487</v>
+        <v>45328</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45495</v>
+        <v>45247</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44582</v>
+        <v>45350</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4742,8 +4742,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4791,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4805,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45329</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4815,13 +4820,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44536</v>
+        <v>45629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45525</v>
+        <v>45126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44974</v>
+        <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45554</v>
+        <v>45109</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45369</v>
+        <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5239,14 +5239,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45820</v>
+        <v>45551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5312,14 +5312,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45819</v>
+        <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45826</v>
+        <v>45300</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5404,8 +5404,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5448,7 +5453,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5462,10 +5467,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46072</v>
+        <v>44917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5478,7 +5483,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5521,7 +5526,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5535,10 +5540,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46072</v>
+        <v>44999</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5551,7 +5556,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5594,7 +5599,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5608,10 +5613,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46072</v>
+        <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5624,7 +5629,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5667,7 +5672,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5681,10 +5686,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45588</v>
+        <v>45329</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5696,8 +5701,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5740,7 +5750,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5754,10 +5764,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45229</v>
+        <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5770,7 +5780,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5813,7 +5823,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5827,10 +5837,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45588</v>
+        <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5843,7 +5853,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5886,7 +5896,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5900,10 +5910,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45113</v>
+        <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5916,7 +5926,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5959,7 +5969,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5973,10 +5983,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46090</v>
+        <v>44890</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5989,7 +5999,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6032,7 +6042,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6046,10 +6056,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44999</v>
+        <v>45751</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6062,7 +6072,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6105,7 +6115,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6119,10 +6129,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46090</v>
+        <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6135,7 +6145,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6178,7 +6188,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6192,10 +6202,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45113</v>
+        <v>45111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6208,7 +6218,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6251,7 +6261,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6261,14 +6271,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44496</v>
+        <v>44749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6281,7 +6291,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6324,7 +6334,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6338,10 +6348,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45082</v>
+        <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6354,7 +6364,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6397,7 +6407,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6411,10 +6421,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45803</v>
+        <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6470,7 +6480,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6484,10 +6494,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45884</v>
+        <v>45621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6499,13 +6509,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6548,7 +6553,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6562,10 +6567,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45782</v>
+        <v>45582</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6578,7 +6583,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6621,7 +6626,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6635,10 +6640,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45271</v>
+        <v>45706</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6651,7 +6656,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6694,7 +6699,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6708,10 +6713,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45609</v>
+        <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6724,7 +6729,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6767,7 +6772,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6781,10 +6786,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46108</v>
+        <v>45803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6796,13 +6801,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45042</v>
+        <v>45800</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6918,7 +6918,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45019</v>
+        <v>45055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6991,7 +6991,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45019</v>
+        <v>45792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7064,7 +7064,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45893</v>
+        <v>45884</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7093,8 +7093,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7137,7 +7142,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7151,10 +7156,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46121</v>
+        <v>45113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7166,13 +7171,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45674</v>
+        <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,8 +7244,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7288,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7302,10 +7307,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45660</v>
+        <v>45800</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7318,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7361,7 +7366,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7375,10 +7380,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44749</v>
+        <v>45893</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7391,7 +7396,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7434,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7444,14 +7449,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45903</v>
+        <v>45825</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7463,13 +7468,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45629</v>
+        <v>45804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45910</v>
+        <v>45660</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7658,7 +7658,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7668,14 +7668,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45903</v>
+        <v>44866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45915</v>
+        <v>45065</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7804,7 +7804,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45706</v>
+        <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7877,7 +7877,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45224</v>
+        <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7906,8 +7906,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7950,7 +7955,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7964,10 +7969,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45198</v>
+        <v>46085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7980,7 +7985,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8023,7 +8028,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8037,10 +8042,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45065</v>
+        <v>44749</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8053,7 +8058,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8096,7 +8101,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8110,10 +8115,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45013</v>
+        <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8126,7 +8131,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8169,7 +8174,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8183,10 +8188,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45042</v>
+        <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8199,7 +8204,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8242,7 +8247,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8256,10 +8261,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44858</v>
+        <v>45910</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8272,7 +8277,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8315,7 +8320,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8329,10 +8334,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45621</v>
+        <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8345,7 +8350,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8388,7 +8393,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8398,14 +8403,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45119</v>
+        <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8418,7 +8423,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8461,7 +8466,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8475,10 +8480,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45055</v>
+        <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8490,8 +8495,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8534,7 +8544,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8548,10 +8558,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45792</v>
+        <v>45098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8564,7 +8574,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8607,7 +8617,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8621,10 +8631,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44819</v>
+        <v>45358</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8637,7 +8647,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8680,7 +8690,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8694,10 +8704,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44868</v>
+        <v>45303</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8710,7 +8720,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8753,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8767,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45247</v>
+        <v>45019</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8783,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8826,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8840,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45246</v>
+        <v>45925</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8855,8 +8865,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8899,7 +8914,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8913,10 +8928,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45169</v>
+        <v>45376</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8928,8 +8943,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8972,7 +8992,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8986,10 +9006,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45113</v>
+        <v>45554</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9002,7 +9022,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9045,7 +9065,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9059,10 +9079,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45800</v>
+        <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9075,7 +9095,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9118,7 +9138,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9132,10 +9152,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45800</v>
+        <v>45140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9148,7 +9168,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9191,7 +9211,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9205,10 +9225,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45012</v>
+        <v>44749</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9221,7 +9241,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9264,7 +9284,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9278,10 +9298,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45918</v>
+        <v>44993</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9294,7 +9314,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9337,7 +9357,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9351,10 +9371,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45804</v>
+        <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9367,7 +9387,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9410,7 +9430,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9424,10 +9444,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45938</v>
+        <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9440,7 +9460,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9483,7 +9503,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9497,10 +9517,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45912</v>
+        <v>45554</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9513,7 +9533,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9556,7 +9576,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9570,10 +9590,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45925</v>
+        <v>45169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9585,13 +9605,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9634,7 +9649,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9648,10 +9663,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45825</v>
+        <v>45953</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9664,7 +9679,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9707,7 +9722,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9721,10 +9736,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46085</v>
+        <v>46153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9737,7 +9752,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9780,7 +9795,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9794,10 +9809,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44531</v>
+        <v>45229</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9810,7 +9825,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9853,7 +9868,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9867,10 +9882,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45098</v>
+        <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9883,7 +9898,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9926,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9940,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46141</v>
+        <v>45960</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9955,13 +9970,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10004,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10018,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44866</v>
+        <v>45414</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10034,7 +10044,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10077,7 +10087,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10091,10 +10101,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44476</v>
+        <v>45967</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10107,7 +10117,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10150,7 +10160,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10164,10 +10174,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44876</v>
+        <v>45248</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10180,7 +10190,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10223,7 +10233,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10237,10 +10247,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45771</v>
+        <v>44550</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10253,7 +10263,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10296,7 +10306,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10310,10 +10320,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44603</v>
+        <v>44797</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10326,7 +10336,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10369,7 +10379,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10383,10 +10393,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45932</v>
+        <v>45979</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10399,7 +10409,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10442,7 +10452,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10456,10 +10466,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44651</v>
+        <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10472,7 +10482,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10515,7 +10525,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10529,10 +10539,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46153</v>
+        <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10545,7 +10555,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10588,7 +10598,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10602,10 +10612,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45109</v>
+        <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10618,7 +10628,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10661,7 +10671,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10675,10 +10685,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44498</v>
+        <v>45113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10734,7 +10744,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10748,10 +10758,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44901</v>
+        <v>45594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10764,7 +10774,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10807,7 +10817,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10821,10 +10831,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45791</v>
+        <v>45986</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10836,8 +10846,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10880,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10894,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45594</v>
+        <v>45986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10910,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10953,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10967,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45575</v>
+        <v>45791</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10983,7 +10998,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11026,7 +11041,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11040,10 +11055,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45518</v>
+        <v>45012</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11099,7 +11114,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11113,10 +11128,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45939</v>
+        <v>44813</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11129,7 +11144,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11172,7 +11187,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11186,10 +11201,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45588</v>
+        <v>45042</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11202,7 +11217,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11245,7 +11260,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11259,10 +11274,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45582</v>
+        <v>45616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11275,7 +11290,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11318,7 +11333,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11332,10 +11347,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45044</v>
+        <v>45588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11348,7 +11363,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11391,7 +11406,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11405,10 +11420,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46176</v>
+        <v>45588</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11421,7 +11436,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11464,7 +11479,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11478,10 +11493,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45567</v>
+        <v>45518</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11494,7 +11509,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11537,7 +11552,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11551,10 +11566,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45616</v>
+        <v>44582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11567,7 +11582,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11610,7 +11625,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11624,10 +11639,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44995</v>
+        <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11640,7 +11655,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11683,7 +11698,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11697,10 +11712,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45953</v>
+        <v>44487</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11713,7 +11728,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11756,7 +11771,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11770,10 +11785,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46170</v>
+        <v>46007</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11786,7 +11801,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11829,7 +11844,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11843,10 +11858,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45191</v>
+        <v>46008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11859,7 +11874,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11902,7 +11917,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11916,10 +11931,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44550</v>
+        <v>45050</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11932,7 +11947,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11975,7 +11990,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11989,10 +12004,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44536</v>
+        <v>45229</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12005,7 +12020,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12048,7 +12063,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12062,10 +12077,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46168</v>
+        <v>45113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12078,7 +12093,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12121,7 +12136,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12135,10 +12150,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45616</v>
+        <v>46034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12151,7 +12166,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12194,7 +12209,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12208,10 +12223,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45960</v>
+        <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12224,7 +12239,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12267,7 +12282,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12281,10 +12296,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45588</v>
+        <v>46038</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12296,8 +12311,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12340,7 +12360,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12354,10 +12374,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45588</v>
+        <v>45336</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12370,7 +12390,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12413,7 +12433,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12427,10 +12447,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45629</v>
+        <v>44845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12443,7 +12463,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12486,7 +12506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12500,10 +12520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45967</v>
+        <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12516,7 +12536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12559,7 +12579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12573,10 +12593,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45629</v>
+        <v>46176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12589,7 +12609,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12632,7 +12652,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12646,10 +12666,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45229</v>
+        <v>45554</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12662,7 +12682,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12705,7 +12725,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12719,10 +12739,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45098</v>
+        <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12735,7 +12755,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12778,7 +12798,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12792,10 +12812,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45979</v>
+        <v>46072</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12808,7 +12828,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12851,7 +12871,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12865,10 +12885,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46245</v>
+        <v>46072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12881,7 +12901,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12924,7 +12944,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12938,10 +12958,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45248</v>
+        <v>46072</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12954,7 +12974,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12997,7 +13017,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13011,10 +13031,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46246</v>
+        <v>46170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13026,13 +13046,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>13.1</v>
+        <v>6.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13075,7 +13090,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13089,10 +13104,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45986</v>
+        <v>46090</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13104,13 +13119,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13153,7 +13163,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13167,10 +13177,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46204</v>
+        <v>44909</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13182,13 +13192,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13231,7 +13236,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13245,10 +13250,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45986</v>
+        <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13261,7 +13266,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13304,7 +13309,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13318,10 +13323,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44748</v>
+        <v>46090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13334,7 +13339,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13377,7 +13382,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13391,10 +13396,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45303</v>
+        <v>46168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13407,7 +13412,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13450,7 +13455,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13460,14 +13465,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46212</v>
+        <v>44879</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13479,13 +13484,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13528,7 +13528,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46255</v>
+        <v>45042</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13601,7 +13601,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46000</v>
+        <v>45044</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45450</v>
+        <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13703,8 +13703,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13747,7 +13752,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13757,14 +13762,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46224</v>
+        <v>45109</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13777,7 +13782,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13820,7 +13825,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13834,10 +13839,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44958</v>
+        <v>46121</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13849,8 +13854,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13893,7 +13903,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13907,10 +13917,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45300</v>
+        <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13922,13 +13932,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13971,7 +13976,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13985,10 +13990,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46267</v>
+        <v>44866</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14001,7 +14006,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14044,7 +14049,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14058,10 +14063,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45140</v>
+        <v>44876</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14074,7 +14079,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14117,7 +14122,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14131,10 +14136,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44866</v>
+        <v>45140</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14147,7 +14152,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14190,7 +14195,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14204,10 +14209,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46007</v>
+        <v>45525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14220,7 +14225,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14263,7 +14268,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14277,10 +14282,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46008</v>
+        <v>44858</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14293,7 +14298,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14336,7 +14341,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14350,10 +14355,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45350</v>
+        <v>45918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14365,13 +14370,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14414,7 +14414,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45680</v>
+        <v>45450</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14487,7 +14487,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14497,14 +14497,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44879</v>
+        <v>45019</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14560,7 +14560,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44993</v>
+        <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14633,7 +14633,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44917</v>
+        <v>45229</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14706,7 +14706,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14720,10 +14720,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45620</v>
+        <v>45119</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14779,7 +14779,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14793,10 +14793,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44858</v>
+        <v>44868</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14852,7 +14852,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14866,10 +14866,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14881,8 +14881,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14925,7 +14930,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14939,10 +14944,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45554</v>
+        <v>46246</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14954,8 +14959,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>13.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14998,7 +15008,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15012,10 +15022,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46234</v>
+        <v>45495</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15028,7 +15038,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15071,7 +15081,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15085,10 +15095,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46240</v>
+        <v>45370</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15101,7 +15111,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15144,7 +15154,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15158,10 +15168,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46240</v>
+        <v>45098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15174,7 +15184,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15217,7 +15227,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15231,10 +15241,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46034</v>
+        <v>44575</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15247,7 +15257,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15290,7 +15300,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15304,10 +15314,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46239</v>
+        <v>45236</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15320,7 +15330,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15363,7 +15373,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15377,10 +15387,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46240</v>
+        <v>44651</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15392,13 +15402,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15441,7 +15446,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15455,10 +15460,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46034</v>
+        <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15471,7 +15476,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15514,7 +15519,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15528,10 +15533,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44995</v>
+        <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15544,7 +15549,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15587,7 +15592,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15601,10 +15606,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45109</v>
+        <v>46212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15616,8 +15621,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15660,7 +15670,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15674,10 +15684,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46038</v>
+        <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15689,13 +15699,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15738,7 +15743,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15752,10 +15757,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45560</v>
+        <v>46255</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15768,7 +15773,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15811,7 +15816,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15825,10 +15830,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44749</v>
+        <v>44819</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15841,7 +15846,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15884,7 +15889,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15898,10 +15903,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45111</v>
+        <v>45620</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15914,7 +15919,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15957,7 +15962,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15971,10 +15976,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45370</v>
+        <v>44890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15987,7 +15992,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16030,7 +16035,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16044,10 +16049,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45280</v>
+        <v>45588</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16059,13 +16064,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45099</v>
+        <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45358</v>
+        <v>45098</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16254,7 +16254,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16268,10 +16268,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44909</v>
+        <v>45616</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45126</v>
+        <v>44995</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16410,14 +16410,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44705</v>
+        <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16473,7 +16473,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45140</v>
+        <v>46267</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16546,7 +16546,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45229</v>
+        <v>45680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16633,10 +16633,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45236</v>
+        <v>45198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16692,7 +16692,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45309</v>
+        <v>44858</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16765,7 +16765,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16779,10 +16779,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45751</v>
+        <v>45777</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16838,7 +16838,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16852,10 +16852,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45554</v>
+        <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45205</v>
+        <v>45777</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.1</v>
+        <v>6.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16984,7 +16984,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16998,10 +16998,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44897</v>
+        <v>45554</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17057,7 +17057,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17071,10 +17071,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45534</v>
+        <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17086,13 +17086,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>11.2</v>
+        <v>5.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17135,7 +17130,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17149,10 +17144,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45527</v>
+        <v>46234</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17165,7 +17160,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17208,7 +17203,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17222,10 +17217,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45328</v>
+        <v>46234</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17238,7 +17233,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17281,7 +17276,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17295,10 +17290,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44858</v>
+        <v>45791</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17311,7 +17306,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17354,7 +17349,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17368,10 +17363,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45098</v>
+        <v>46240</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17384,7 +17379,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17427,7 +17422,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17441,10 +17436,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45551</v>
+        <v>46240</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17457,7 +17452,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17500,7 +17495,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17514,10 +17509,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45112</v>
+        <v>45404</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17530,7 +17525,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17573,7 +17568,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17587,10 +17582,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45642</v>
+        <v>45680</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17603,7 +17598,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>11.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17646,7 +17641,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17660,10 +17655,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45777</v>
+        <v>46240</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17675,8 +17670,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45777</v>
+        <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45777</v>
+        <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45554</v>
+        <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45369</v>
+        <v>45586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45791</v>
+        <v>45811</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45404</v>
+        <v>45811</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45680</v>
+        <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45707</v>
+        <v>45450</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18313,14 +18313,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45586</v>
+        <v>45819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18386,14 +18386,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45707</v>
+        <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45450</v>
+        <v>45826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45811</v>
+        <v>45082</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45811</v>
+        <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45811</v>
+        <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,8 +18770,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18814,7 +18819,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18824,14 +18829,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,13 +18848,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45967</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>46215</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45159</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>45873</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45588</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45560</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>44958</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44705</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45204</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45369</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45328</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45247</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45350</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>45109</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45300</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44999</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45329</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>44890</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45751</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45111</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>44749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45582</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>45706</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>45800</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>45884</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45113</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45800</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45893</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45825</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45804</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>45660</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45065</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>44749</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45910</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45358</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45303</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45019</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45925</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45376</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45554</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>45140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44749</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>44993</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45939</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45554</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45953</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45229</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45960</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45414</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45967</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45248</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44550</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44797</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45979</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44858</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45986</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45791</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45012</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44813</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45042</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45588</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45518</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44487</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>46007</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>46008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45050</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45229</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>46034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>46038</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45336</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45771</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>46176</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45554</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>46072</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>46072</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>46170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>46090</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44909</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>46090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>46168</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>44879</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45042</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45044</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45109</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>46121</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>46245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44866</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44876</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45140</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44858</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45450</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45019</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45575</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45229</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45119</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44868</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46204</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46246</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45495</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45370</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>44575</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45236</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44651</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>46255</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44819</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45620</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>44890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45588</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45098</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45616</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44995</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>46267</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44858</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45777</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45777</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45554</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46234</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46234</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45791</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46240</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46240</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45404</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45680</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46240</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45811</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45811</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45450</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45082</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55118-2025</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45967</v>
+        <v>45873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1788,358 +1788,358 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 55118-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Luddfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31051-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>46215</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>2.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 38064-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45159</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>3.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Vedticka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 36671-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45588</v>
+        <v>44705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45560</v>
+        <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44974</v>
+        <v>45560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44868</v>
+        <v>44958</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44958</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45191</v>
+        <v>44868</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45191</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45246</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44705</v>
+        <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,8 +4299,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44995</v>
+        <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4373,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4416,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45204</v>
+        <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4445,13 +4450,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4511,7 +4511,7 @@
         <v>45369</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45328</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45247</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45350</v>
+        <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4742,13 +4742,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4791,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4805,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>45350</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4820,8 +4815,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45629</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>45126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45109</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45567</v>
+        <v>45551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45551</v>
+        <v>44897</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44897</v>
+        <v>45300</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5331,8 +5331,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5375,7 +5380,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5389,10 +5394,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45300</v>
+        <v>44917</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5402,11 +5407,6 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -5453,7 +5453,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44917</v>
+        <v>44999</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44999</v>
+        <v>45109</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5616,7 +5616,7 @@
         <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45329</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44890</v>
+        <v>45751</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6042,7 +6042,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45751</v>
+        <v>44890</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45111</v>
+        <v>45918</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44749</v>
+        <v>45111</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6348,10 +6348,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44476</v>
+        <v>45803</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45912</v>
+        <v>44476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6480,7 +6480,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45621</v>
+        <v>45119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6567,10 +6567,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45582</v>
+        <v>45884</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6582,8 +6582,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6626,7 +6631,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6636,14 +6641,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45706</v>
+        <v>44749</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6656,7 +6661,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6699,7 +6704,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6713,10 +6718,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44748</v>
+        <v>45912</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6729,7 +6734,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6772,7 +6777,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6786,10 +6791,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45803</v>
+        <v>45621</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6802,7 +6807,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6845,7 +6850,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6859,10 +6864,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45800</v>
+        <v>45893</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6875,7 +6880,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6918,7 +6923,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6932,10 +6937,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45055</v>
+        <v>45706</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6948,7 +6953,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6991,7 +6996,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7005,10 +7010,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45792</v>
+        <v>45113</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7021,7 +7026,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7064,7 +7069,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7078,10 +7083,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45884</v>
+        <v>45800</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7093,13 +7098,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45113</v>
+        <v>45660</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45280</v>
+        <v>45582</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7244,13 +7244,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7293,7 +7288,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7307,10 +7302,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45800</v>
+        <v>45792</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7323,7 +7318,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7366,7 +7361,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7380,10 +7375,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45893</v>
+        <v>45800</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7396,7 +7391,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7439,7 +7434,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7449,14 +7444,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45825</v>
+        <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7468,8 +7463,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45804</v>
+        <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45660</v>
+        <v>45825</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7658,7 +7658,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44866</v>
+        <v>44748</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45065</v>
+        <v>45804</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7804,7 +7804,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45938</v>
+        <v>45910</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7877,7 +7877,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7906,13 +7906,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7955,7 +7950,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7965,14 +7960,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46085</v>
+        <v>45903</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7985,7 +7980,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8028,7 +8023,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8042,10 +8037,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44749</v>
+        <v>45065</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8058,7 +8053,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8101,7 +8096,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8115,10 +8110,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45629</v>
+        <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8131,7 +8126,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8174,7 +8169,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8188,10 +8183,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45112</v>
+        <v>46085</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8204,7 +8199,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8247,7 +8242,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8261,10 +8256,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45910</v>
+        <v>45055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8277,7 +8272,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8320,7 +8315,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8334,10 +8329,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8349,8 +8344,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8403,14 +8403,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45903</v>
+        <v>45280</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8422,8 +8422,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8466,7 +8471,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8480,10 +8485,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46141</v>
+        <v>45932</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8495,13 +8500,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45098</v>
+        <v>46141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8573,8 +8573,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8617,7 +8622,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8631,10 +8636,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45358</v>
+        <v>44866</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8647,7 +8652,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8690,7 +8695,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8704,10 +8709,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45303</v>
+        <v>44749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8720,7 +8725,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8763,7 +8768,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8777,10 +8782,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45019</v>
+        <v>46153</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8798,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8836,7 +8841,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8850,10 +8855,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45925</v>
+        <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8865,13 +8870,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8914,7 +8914,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45376</v>
+        <v>45939</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8943,13 +8943,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8992,7 +8987,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9006,10 +9001,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45554</v>
+        <v>45098</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9065,7 +9060,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9079,10 +9074,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45932</v>
+        <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9095,7 +9090,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9138,7 +9133,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9152,10 +9147,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45140</v>
+        <v>45594</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9211,7 +9206,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9225,10 +9220,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44749</v>
+        <v>45953</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9241,7 +9236,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9284,7 +9279,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9298,10 +9293,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44993</v>
+        <v>45303</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9357,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9371,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45939</v>
+        <v>45019</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9387,7 +9382,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9430,7 +9425,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9444,10 +9439,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45588</v>
+        <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9460,7 +9455,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9503,7 +9498,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9517,10 +9512,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45554</v>
+        <v>45376</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9532,8 +9527,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9576,7 +9576,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9590,10 +9590,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45169</v>
+        <v>45960</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45953</v>
+        <v>45554</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9736,10 +9736,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46153</v>
+        <v>45967</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9795,7 +9795,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45229</v>
+        <v>45518</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9868,7 +9868,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9882,10 +9882,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44536</v>
+        <v>45140</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9941,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45960</v>
+        <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10014,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45414</v>
+        <v>44993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10087,7 +10087,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10101,10 +10101,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10160,7 +10160,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45248</v>
+        <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10233,7 +10233,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44550</v>
+        <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10262,8 +10262,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>11.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10306,7 +10311,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10320,10 +10325,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44797</v>
+        <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10336,7 +10341,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10379,7 +10384,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10393,10 +10398,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45979</v>
+        <v>45554</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10409,7 +10414,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10452,7 +10457,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10466,10 +10471,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44858</v>
+        <v>45169</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10482,7 +10487,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10525,7 +10530,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10539,10 +10544,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44496</v>
+        <v>45229</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10555,7 +10560,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10598,7 +10603,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10612,10 +10617,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45629</v>
+        <v>44536</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10628,7 +10633,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10671,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10685,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45113</v>
+        <v>46000</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10701,7 +10706,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10744,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10758,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45594</v>
+        <v>45414</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10774,7 +10779,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10817,7 +10822,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10831,10 +10836,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45986</v>
+        <v>46176</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10846,13 +10851,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>11.2</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10895,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10909,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45986</v>
+        <v>46007</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10968,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10982,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45791</v>
+        <v>45248</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45012</v>
+        <v>44550</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11114,7 +11114,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44813</v>
+        <v>46008</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11187,7 +11187,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45042</v>
+        <v>44797</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11260,7 +11260,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45616</v>
+        <v>44858</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11347,10 +11347,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45588</v>
+        <v>44496</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11406,7 +11406,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11420,10 +11420,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45588</v>
+        <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11479,7 +11479,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45518</v>
+        <v>46170</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44582</v>
+        <v>45113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46000</v>
+        <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11698,7 +11698,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44487</v>
+        <v>46034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11785,10 +11785,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46007</v>
+        <v>45012</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11844,7 +11844,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11858,10 +11858,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46008</v>
+        <v>46038</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11873,8 +11873,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11917,7 +11922,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11931,10 +11936,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45050</v>
+        <v>44813</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11947,7 +11952,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11990,7 +11995,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12004,10 +12009,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45229</v>
+        <v>46168</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12020,7 +12025,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12063,7 +12068,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12077,10 +12082,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45113</v>
+        <v>45042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12093,7 +12098,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12136,7 +12141,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12150,10 +12155,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46034</v>
+        <v>45616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12166,7 +12171,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12209,7 +12214,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12223,10 +12228,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46034</v>
+        <v>45588</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12239,7 +12244,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12282,7 +12287,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12296,10 +12301,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46038</v>
+        <v>45588</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12311,13 +12316,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12360,7 +12360,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12374,10 +12374,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45336</v>
+        <v>44582</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44845</v>
+        <v>44487</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12506,7 +12506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45771</v>
+        <v>46072</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12579,7 +12579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12593,10 +12593,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46176</v>
+        <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45554</v>
+        <v>46072</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12725,7 +12725,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45013</v>
+        <v>45050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12798,7 +12798,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46072</v>
+        <v>45229</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12871,7 +12871,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12885,10 +12885,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46072</v>
+        <v>46090</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12958,10 +12958,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46072</v>
+        <v>45113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13090,7 +13090,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13104,10 +13104,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46090</v>
+        <v>45336</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13163,7 +13163,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 16153-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44909</v>
+        <v>46108</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13192,8 +13192,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13236,7 +13241,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13250,10 +13255,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44901</v>
+        <v>46204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13265,8 +13270,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13309,7 +13319,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13323,10 +13333,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46090</v>
+        <v>44845</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13339,7 +13349,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13382,7 +13392,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13396,10 +13406,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46168</v>
+        <v>46246</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13411,8 +13421,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>13.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13455,7 +13470,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13465,14 +13480,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44879</v>
+        <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13485,7 +13500,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13528,7 +13543,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13542,10 +13557,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45042</v>
+        <v>46121</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13557,8 +13572,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13601,7 +13621,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13615,10 +13635,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45044</v>
+        <v>45554</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13631,7 +13651,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13674,7 +13694,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13688,10 +13708,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46108</v>
+        <v>45013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13703,13 +13723,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13752,7 +13767,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13766,10 +13781,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45109</v>
+        <v>44909</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13782,7 +13797,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13825,7 +13840,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13839,10 +13854,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46121</v>
+        <v>44901</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13854,13 +13869,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13903,7 +13913,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13917,10 +13927,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46245</v>
+        <v>46212</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13932,8 +13942,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13976,7 +13991,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13986,14 +14001,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44866</v>
+        <v>44879</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14006,7 +14021,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14049,7 +14064,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14063,10 +14078,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44876</v>
+        <v>45042</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14079,7 +14094,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14122,7 +14137,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14136,10 +14151,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45140</v>
+        <v>46255</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14152,7 +14167,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14195,7 +14210,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14209,10 +14224,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45525</v>
+        <v>45044</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14225,7 +14240,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14268,7 +14283,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14282,10 +14297,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44858</v>
+        <v>45109</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14298,7 +14313,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14341,7 +14356,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14355,10 +14370,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45918</v>
+        <v>44866</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14371,7 +14386,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14414,7 +14429,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14428,10 +14443,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45450</v>
+        <v>44876</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14444,7 +14459,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14487,7 +14502,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14497,14 +14512,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45019</v>
+        <v>46224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14517,7 +14532,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.6</v>
+        <v>7.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14560,7 +14575,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14574,10 +14589,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45575</v>
+        <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14590,7 +14605,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14633,7 +14648,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14647,10 +14662,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45229</v>
+        <v>45140</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14663,7 +14678,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14706,7 +14721,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14720,10 +14735,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45119</v>
+        <v>45525</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14736,7 +14751,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14779,7 +14794,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14793,10 +14808,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44868</v>
+        <v>44858</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14809,7 +14824,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14852,7 +14867,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14866,10 +14881,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46204</v>
+        <v>45450</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14881,13 +14896,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14930,7 +14940,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14944,10 +14954,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46246</v>
+        <v>45019</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14959,13 +14969,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>13.1</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15008,7 +15013,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15022,10 +15027,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45495</v>
+        <v>45575</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15038,7 +15043,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15081,7 +15086,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15095,10 +15100,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45370</v>
+        <v>45229</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15111,7 +15116,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15154,7 +15159,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15168,10 +15173,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45098</v>
+        <v>44868</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15184,7 +15189,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15227,7 +15232,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15241,10 +15246,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44575</v>
+        <v>45495</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15257,7 +15262,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15300,7 +15305,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15314,10 +15319,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45236</v>
+        <v>45370</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15330,7 +15335,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15373,7 +15378,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15387,10 +15392,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44651</v>
+        <v>45098</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15403,7 +15408,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15446,7 +15451,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15460,10 +15465,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45224</v>
+        <v>46234</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15476,7 +15481,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15519,7 +15524,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15533,10 +15538,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45527</v>
+        <v>46234</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15549,7 +15554,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15592,7 +15597,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15606,10 +15611,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46212</v>
+        <v>44575</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15621,13 +15626,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15684,10 +15684,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45609</v>
+        <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15743,7 +15743,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15757,10 +15757,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46255</v>
+        <v>44651</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44819</v>
+        <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15889,7 +15889,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45620</v>
+        <v>45527</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15962,7 +15962,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44890</v>
+        <v>46240</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45588</v>
+        <v>46240</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44531</v>
+        <v>46240</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16137,8 +16137,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16181,7 +16186,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16195,10 +16200,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45098</v>
+        <v>45609</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16211,7 +16216,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16254,7 +16259,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16268,10 +16273,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45616</v>
+        <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16284,7 +16289,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16327,7 +16332,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16341,10 +16346,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44995</v>
+        <v>44819</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16357,7 +16362,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16400,7 +16405,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16410,14 +16415,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46224</v>
+        <v>45620</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16430,7 +16435,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16473,7 +16478,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16487,10 +16492,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46267</v>
+        <v>44890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16503,7 +16508,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16546,7 +16551,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16560,10 +16565,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45680</v>
+        <v>45588</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16576,7 +16581,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16619,7 +16624,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16633,10 +16638,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45198</v>
+        <v>44531</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16649,7 +16654,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16692,7 +16697,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16706,10 +16711,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44858</v>
+        <v>45098</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16722,7 +16727,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16765,7 +16770,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16779,10 +16784,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45777</v>
+        <v>45616</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16795,7 +16800,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16838,7 +16843,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16852,10 +16857,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45777</v>
+        <v>46245</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16868,7 +16873,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16911,7 +16916,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16925,10 +16930,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45777</v>
+        <v>44995</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16941,7 +16946,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16984,7 +16989,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16998,10 +17003,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45554</v>
+        <v>45680</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17014,7 +17019,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17057,7 +17062,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17071,10 +17076,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45369</v>
+        <v>45198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17087,7 +17092,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17130,7 +17135,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17144,10 +17149,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46234</v>
+        <v>44858</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17160,7 +17165,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17203,7 +17208,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17217,10 +17222,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46234</v>
+        <v>45777</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17233,7 +17238,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17276,7 +17281,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17290,10 +17295,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45791</v>
+        <v>45777</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17306,7 +17311,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17349,7 +17354,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17363,10 +17368,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46240</v>
+        <v>45777</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17379,7 +17384,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17422,7 +17427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17436,10 +17441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46240</v>
+        <v>45554</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17452,7 +17457,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17495,7 +17500,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17509,10 +17514,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45404</v>
+        <v>45369</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17525,7 +17530,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17568,7 +17573,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17582,10 +17587,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45680</v>
+        <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17598,7 +17603,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>11.2</v>
+        <v>4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17641,7 +17646,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17655,10 +17660,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46240</v>
+        <v>45404</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17670,13 +17675,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17719,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17733,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46239</v>
+        <v>45680</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>7.2</v>
+        <v>11.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17809,7 +17809,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45811</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45811</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45450</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45082</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,36 +1461,36 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 36671-2025</t>
+          <t>A 38064-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45873</v>
+        <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,8 +1747,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1784,39 +1789,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
@@ -1840,7 +1845,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1933,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31051-2026</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1947,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46215</v>
+        <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1963,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,148 +2003,143 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 31051-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38064-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44494</v>
+        <v>44858</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44858</v>
+        <v>45369</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45534</v>
+        <v>44494</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,13 +3637,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3681,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44705</v>
+        <v>45224</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3716,7 +3711,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3754,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3768,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45588</v>
+        <v>45198</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3827,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3841,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45560</v>
+        <v>45013</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3857,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3900,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3914,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44958</v>
+        <v>45050</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3930,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3973,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3987,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>45042</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4003,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4046,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4060,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44868</v>
+        <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4076,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4119,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4134,14 +4129,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45191</v>
+        <v>44749</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4149,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4192,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4206,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>45055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4222,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4265,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4279,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45204</v>
+        <v>44819</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,13 +4294,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4338,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4352,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45246</v>
+        <v>44868</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4378,7 +4368,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4411,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4425,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44995</v>
+        <v>45247</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4441,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4484,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4498,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45369</v>
+        <v>45204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4523,8 +4513,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4562,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45328</v>
+        <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4592,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4635,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4649,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45247</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4665,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4708,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45629</v>
+        <v>45791</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4781,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4795,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45350</v>
+        <v>45336</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4813,11 +4808,6 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4864,7 +4854,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4878,10 +4868,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>45113</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4894,7 +4884,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4937,7 +4927,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,10 +4941,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45126</v>
+        <v>45012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4967,7 +4957,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5010,7 +5000,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5024,10 +5014,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44498</v>
+        <v>45414</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5040,7 +5030,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5083,7 +5073,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5087,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5113,7 +5103,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5156,7 +5146,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5170,10 +5160,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45551</v>
+        <v>45404</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5186,7 +5176,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5229,7 +5219,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5243,10 +5233,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44897</v>
+        <v>44531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5249,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5302,7 +5292,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5316,10 +5306,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45300</v>
+        <v>44890</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5331,13 +5321,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5380,7 +5365,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5394,10 +5379,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44917</v>
+        <v>44890</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5410,7 +5395,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5453,7 +5438,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5467,10 +5452,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44999</v>
+        <v>44813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5483,7 +5468,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5526,7 +5511,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5540,10 +5525,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45109</v>
+        <v>45098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5556,7 +5541,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5599,7 +5584,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5613,10 +5598,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45674</v>
+        <v>44866</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5629,7 +5614,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5672,7 +5657,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5686,10 +5671,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45329</v>
+        <v>44476</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5701,13 +5686,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5750,7 +5730,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5764,10 +5744,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45099</v>
+        <v>44876</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5780,7 +5760,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5823,7 +5803,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5837,10 +5817,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44603</v>
+        <v>45680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5853,7 +5833,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5896,7 +5876,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5910,10 +5890,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45205</v>
+        <v>45771</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5926,7 +5906,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.1</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5969,7 +5949,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,10 +5963,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45751</v>
+        <v>44603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5999,7 +5979,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6042,7 +6022,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6056,10 +6036,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44890</v>
+        <v>44797</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6115,7 +6095,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6129,10 +6109,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44536</v>
+        <v>45113</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6145,7 +6125,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6188,7 +6168,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6202,10 +6182,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45918</v>
+        <v>44651</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6218,7 +6198,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6261,7 +6241,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6275,10 +6255,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45111</v>
+        <v>45803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6291,7 +6271,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6334,7 +6314,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6348,10 +6328,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45803</v>
+        <v>45884</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6363,8 +6343,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6407,7 +6392,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6421,10 +6406,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44476</v>
+        <v>45376</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6436,8 +6421,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6480,7 +6470,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6494,10 +6484,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45119</v>
+        <v>45109</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6510,7 +6500,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6553,7 +6543,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6567,10 +6557,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45884</v>
+        <v>45893</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6582,13 +6572,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6631,7 +6616,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6641,14 +6626,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44749</v>
+        <v>44498</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6661,7 +6646,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6704,7 +6689,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6718,10 +6703,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45912</v>
+        <v>44901</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6734,7 +6719,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6777,7 +6762,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6791,10 +6776,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45621</v>
+        <v>45660</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6807,7 +6792,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6850,7 +6835,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6860,14 +6845,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45893</v>
+        <v>45903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6879,8 +6864,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6923,7 +6913,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6937,10 +6927,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45706</v>
+        <v>44845</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6953,7 +6943,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6996,7 +6986,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7010,10 +7000,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45113</v>
+        <v>45629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7026,7 +7016,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7069,7 +7059,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7083,10 +7073,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45800</v>
+        <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7099,7 +7089,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7142,7 +7132,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7156,10 +7146,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45660</v>
+        <v>45910</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7172,7 +7162,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7215,7 +7205,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7225,14 +7215,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45582</v>
+        <v>45903</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7245,7 +7235,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7288,7 +7278,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7302,10 +7292,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45792</v>
+        <v>44575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7318,7 +7308,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7361,7 +7351,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7375,10 +7365,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45800</v>
+        <v>45915</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7391,7 +7381,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7434,7 +7424,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7444,14 +7434,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45903</v>
+        <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7463,13 +7453,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7497,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7511,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45629</v>
+        <v>45588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7542,7 +7527,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7585,7 +7570,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7599,10 +7584,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45825</v>
+        <v>45495</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,7 +7600,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7658,7 +7643,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7672,10 +7657,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44748</v>
+        <v>44582</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7688,7 +7673,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7731,7 +7716,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,10 +7730,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45804</v>
+        <v>45582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7761,7 +7746,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7804,7 +7789,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7818,10 +7803,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45910</v>
+        <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7833,8 +7818,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7877,7 +7867,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7891,10 +7881,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7906,8 +7896,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7950,7 +7945,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7960,14 +7955,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45903</v>
+        <v>45707</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7980,7 +7975,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8023,7 +8018,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8037,10 +8032,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45065</v>
+        <v>45044</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8053,7 +8048,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8096,7 +8091,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8110,10 +8105,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45938</v>
+        <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8126,7 +8121,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8169,7 +8164,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8183,10 +8178,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46085</v>
+        <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8199,7 +8194,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8242,7 +8237,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45055</v>
+        <v>45586</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8272,7 +8267,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8315,7 +8310,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8329,10 +8324,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45925</v>
+        <v>45707</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8344,13 +8339,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8393,7 +8383,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8407,10 +8397,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45280</v>
+        <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8422,13 +8412,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8471,7 +8456,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8485,10 +8470,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45932</v>
+        <v>45450</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8501,7 +8486,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8544,7 +8529,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,10 +8543,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46141</v>
+        <v>45811</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8573,13 +8558,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8622,7 +8602,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8636,10 +8616,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44866</v>
+        <v>45811</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8652,7 +8632,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8695,7 +8675,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8709,10 +8689,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44749</v>
+        <v>45811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8725,7 +8705,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8768,7 +8748,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8782,10 +8762,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46153</v>
+        <v>45616</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8798,7 +8778,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8841,7 +8821,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8855,10 +8835,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45112</v>
+        <v>45525</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8871,7 +8851,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8914,7 +8894,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8928,10 +8908,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45939</v>
+        <v>44995</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8944,7 +8924,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8987,7 +8967,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9001,10 +8981,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45098</v>
+        <v>44974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9017,7 +8997,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9060,7 +9040,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9074,10 +9054,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45358</v>
+        <v>45191</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9090,7 +9070,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9133,7 +9113,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9147,10 +9127,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45594</v>
+        <v>45554</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9163,7 +9143,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9206,7 +9186,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9220,10 +9200,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45953</v>
+        <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9236,7 +9216,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9279,7 +9259,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9293,10 +9273,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45303</v>
+        <v>45369</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9309,7 +9289,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9352,7 +9332,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9366,10 +9346,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45019</v>
+        <v>44550</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9382,7 +9362,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9425,7 +9405,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9439,10 +9419,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45791</v>
+        <v>44536</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9455,7 +9435,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9498,7 +9478,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9512,10 +9492,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45376</v>
+        <v>45616</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9527,13 +9507,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9576,7 +9551,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9590,10 +9565,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45960</v>
+        <v>45588</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9606,7 +9581,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9649,7 +9624,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9663,10 +9638,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45554</v>
+        <v>45588</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9679,7 +9654,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9722,7 +9697,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9736,10 +9711,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45967</v>
+        <v>45629</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9795,7 +9770,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9809,10 +9784,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45518</v>
+        <v>45588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9825,7 +9800,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9868,7 +9843,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9882,10 +9857,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45140</v>
+        <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,7 +9873,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9941,7 +9916,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9955,10 +9930,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44749</v>
+        <v>45588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9971,7 +9946,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10014,7 +9989,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10028,10 +10003,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44993</v>
+        <v>45953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10044,7 +10019,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10087,7 +10062,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10097,14 +10072,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45979</v>
+        <v>45820</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10117,7 +10092,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10160,7 +10135,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10174,10 +10149,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45588</v>
+        <v>45960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10190,7 +10165,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10233,7 +10208,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10247,10 +10222,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45986</v>
+        <v>45629</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10262,13 +10237,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10311,7 +10281,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10325,10 +10295,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45986</v>
+        <v>44999</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10341,7 +10311,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10384,7 +10354,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10398,10 +10368,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45554</v>
+        <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10414,7 +10384,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10457,7 +10427,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10467,14 +10437,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45169</v>
+        <v>45819</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10487,7 +10457,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10530,7 +10500,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10544,10 +10514,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45229</v>
+        <v>45113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10560,7 +10530,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10603,7 +10573,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10617,10 +10587,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44536</v>
+        <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10633,7 +10603,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10676,7 +10646,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10690,10 +10660,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46000</v>
+        <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10706,7 +10676,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10719,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10733,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45414</v>
+        <v>45967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10779,7 +10749,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10822,7 +10792,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10836,10 +10806,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46176</v>
+        <v>45248</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10852,7 +10822,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10895,7 +10865,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10909,10 +10879,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46007</v>
+        <v>45979</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10925,7 +10895,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10968,7 +10938,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10982,10 +10952,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45248</v>
+        <v>45609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10998,7 +10968,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11041,7 +11011,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11055,10 +11025,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44550</v>
+        <v>45042</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11071,7 +11041,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11114,7 +11084,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11128,10 +11098,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46008</v>
+        <v>44748</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11144,7 +11114,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11187,7 +11157,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11201,10 +11171,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44797</v>
+        <v>45019</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11260,7 +11230,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11274,10 +11244,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44858</v>
+        <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11290,7 +11260,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11333,7 +11303,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11347,10 +11317,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44496</v>
+        <v>45986</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11362,8 +11332,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>6.5</v>
+        <v>11.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11406,7 +11381,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11420,10 +11395,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45629</v>
+        <v>45986</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11436,7 +11411,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11479,7 +11454,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11493,10 +11468,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46170</v>
+        <v>45674</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11509,7 +11484,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11552,7 +11527,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11566,10 +11541,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45113</v>
+        <v>45826</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11582,7 +11557,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11625,7 +11600,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11639,10 +11614,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46034</v>
+        <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11655,7 +11630,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11698,7 +11673,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11712,10 +11687,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46034</v>
+        <v>45303</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11728,7 +11703,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11771,7 +11746,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11785,10 +11760,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45012</v>
+        <v>46000</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11801,7 +11776,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11844,7 +11819,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11858,10 +11833,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11873,13 +11848,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11922,7 +11892,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11936,10 +11906,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44813</v>
+        <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11952,7 +11922,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11995,7 +11965,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12009,10 +11979,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46168</v>
+        <v>46007</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12025,7 +11995,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12068,7 +12038,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12082,10 +12052,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45042</v>
+        <v>46038</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12097,8 +12067,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12141,7 +12116,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12155,10 +12130,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45616</v>
+        <v>46008</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12171,7 +12146,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12214,7 +12189,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12228,10 +12203,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45588</v>
+        <v>45450</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12244,7 +12219,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12287,7 +12262,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12301,10 +12276,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45588</v>
+        <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12317,7 +12292,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12360,7 +12335,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12374,10 +12349,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44582</v>
+        <v>45300</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12389,8 +12364,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12433,7 +12413,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12447,10 +12427,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44487</v>
+        <v>45140</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12463,7 +12443,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12506,7 +12486,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12520,10 +12500,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46072</v>
+        <v>44866</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12536,7 +12516,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12579,7 +12559,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12593,10 +12573,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46072</v>
+        <v>45350</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12608,8 +12588,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12652,7 +12637,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12666,10 +12651,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46072</v>
+        <v>46240</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12682,7 +12667,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12725,7 +12710,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12739,10 +12724,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45050</v>
+        <v>46240</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12755,7 +12740,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12798,7 +12783,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12812,10 +12797,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45229</v>
+        <v>45680</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12828,7 +12813,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12871,7 +12856,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12881,14 +12866,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46090</v>
+        <v>44879</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12901,7 +12886,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12944,7 +12929,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12958,10 +12943,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45113</v>
+        <v>44993</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12974,7 +12959,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13017,7 +13002,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13031,10 +13016,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46090</v>
+        <v>44917</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13047,7 +13032,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13090,7 +13075,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13104,10 +13089,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45336</v>
+        <v>45620</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13120,7 +13105,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13163,7 +13148,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16153-2026</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13177,10 +13162,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46108</v>
+        <v>46245</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13192,13 +13177,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13241,7 +13221,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13255,10 +13235,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46204</v>
+        <v>46072</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13270,13 +13250,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13319,7 +13294,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13333,10 +13308,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44845</v>
+        <v>46072</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13349,7 +13324,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13392,7 +13367,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13406,10 +13381,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46246</v>
+        <v>46072</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13421,13 +13396,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13470,7 +13440,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 39411-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13484,10 +13454,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45771</v>
+        <v>46288</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13499,8 +13469,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13543,7 +13518,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13557,10 +13532,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46121</v>
+        <v>44858</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13572,13 +13547,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13621,7 +13591,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13635,10 +13605,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45554</v>
+        <v>46246</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13650,8 +13620,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>13.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13694,7 +13669,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13708,10 +13683,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45013</v>
+        <v>45554</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13724,7 +13699,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13767,7 +13742,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13781,10 +13756,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44909</v>
+        <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13797,7 +13772,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13840,7 +13815,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13854,10 +13829,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44901</v>
+        <v>46090</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13870,7 +13845,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13913,7 +13888,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13927,10 +13902,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46212</v>
+        <v>45082</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13942,13 +13917,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13991,7 +13961,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14001,14 +13971,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44879</v>
+        <v>44995</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14021,7 +13991,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14064,7 +14034,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14078,10 +14048,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45042</v>
+        <v>45109</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14137,7 +14107,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14151,10 +14121,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46255</v>
+        <v>45560</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14167,7 +14137,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14210,7 +14180,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14224,10 +14194,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45044</v>
+        <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14240,7 +14210,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14283,7 +14253,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14297,10 +14267,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45109</v>
+        <v>45111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14313,7 +14283,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14356,7 +14326,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14370,10 +14340,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44866</v>
+        <v>45782</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14386,7 +14356,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14429,7 +14399,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14443,10 +14413,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44876</v>
+        <v>45271</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14459,7 +14429,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14502,7 +14472,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14512,14 +14482,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46224</v>
+        <v>46121</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14531,8 +14501,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14575,7 +14550,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14589,10 +14564,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46267</v>
+        <v>45370</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14605,7 +14580,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14648,7 +14623,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14662,10 +14637,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45140</v>
+        <v>45280</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14677,8 +14652,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14721,7 +14701,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14735,10 +14715,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45525</v>
+        <v>45099</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14751,7 +14731,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14794,7 +14774,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14808,10 +14788,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44858</v>
+        <v>45358</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14824,7 +14804,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14867,7 +14847,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14881,10 +14861,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45450</v>
+        <v>44909</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14897,7 +14877,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14940,7 +14920,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14954,10 +14934,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45019</v>
+        <v>45706</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14970,7 +14950,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15013,7 +14993,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15027,10 +15007,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45575</v>
+        <v>45126</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15043,7 +15023,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15086,7 +15066,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15100,10 +15080,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45229</v>
+        <v>44705</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15116,7 +15096,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15159,7 +15139,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15173,10 +15153,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44868</v>
+        <v>45065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15189,7 +15169,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15232,7 +15212,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15246,10 +15226,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45495</v>
+        <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15262,7 +15242,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15305,7 +15285,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15319,10 +15299,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45370</v>
+        <v>45621</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15335,7 +15315,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15378,7 +15358,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15392,10 +15372,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45098</v>
+        <v>45119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15408,7 +15388,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15451,7 +15431,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15465,10 +15445,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46234</v>
+        <v>45229</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15481,7 +15461,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15524,7 +15504,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15538,10 +15518,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46234</v>
+        <v>45236</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15554,7 +15534,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15597,7 +15577,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15611,10 +15591,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44575</v>
+        <v>45309</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15627,7 +15607,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15670,7 +15650,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15684,10 +15664,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45236</v>
+        <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15700,7 +15680,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15743,7 +15723,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15757,10 +15737,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44651</v>
+        <v>45751</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15773,7 +15753,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15816,7 +15796,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15830,10 +15810,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45224</v>
+        <v>45554</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15846,7 +15826,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15889,7 +15869,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15903,10 +15883,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45527</v>
+        <v>45205</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15919,7 +15899,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15962,7 +15942,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15976,10 +15956,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46240</v>
+        <v>44897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15992,7 +15972,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16035,7 +16015,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16049,10 +16029,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46240</v>
+        <v>45534</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16064,8 +16044,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>11.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16108,7 +16093,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16122,10 +16107,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46240</v>
+        <v>45527</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16137,13 +16122,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16186,7 +16166,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16200,10 +16180,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45609</v>
+        <v>45328</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16216,7 +16196,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16259,7 +16239,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16273,10 +16253,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46239</v>
+        <v>44858</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16289,7 +16269,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16332,7 +16312,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16346,10 +16326,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44819</v>
+        <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16362,7 +16342,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16405,7 +16385,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16419,10 +16399,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45620</v>
+        <v>45800</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16435,7 +16415,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16478,7 +16458,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16492,10 +16472,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44890</v>
+        <v>45918</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16508,7 +16488,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16551,7 +16531,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16565,10 +16545,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45588</v>
+        <v>45098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16581,7 +16561,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16624,7 +16604,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16638,10 +16618,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44531</v>
+        <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16654,7 +16634,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16697,7 +16677,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16711,10 +16691,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45098</v>
+        <v>45938</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16727,7 +16707,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16770,7 +16750,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16784,10 +16764,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45616</v>
+        <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16800,7 +16780,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16843,7 +16823,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16857,10 +16837,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46245</v>
+        <v>45825</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16873,7 +16853,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16916,7 +16896,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16930,10 +16910,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44995</v>
+        <v>46085</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16946,7 +16926,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16989,7 +16969,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17003,10 +16983,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45680</v>
+        <v>45551</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17019,7 +16999,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17062,7 +17042,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17076,10 +17056,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45198</v>
+        <v>46141</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17089,6 +17069,11 @@
       <c r="G219" t="inlineStr">
         <is>
           <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -17135,7 +17120,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17149,10 +17134,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44858</v>
+        <v>45112</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17165,7 +17150,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17208,7 +17193,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17222,10 +17207,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45777</v>
+        <v>45642</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17238,7 +17223,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17281,7 +17266,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17298,7 +17283,7 @@
         <v>45777</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17311,7 +17296,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17354,7 +17339,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17371,7 +17356,7 @@
         <v>45777</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17384,7 +17369,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17427,7 +17412,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17441,10 +17426,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45554</v>
+        <v>45777</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17457,7 +17442,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17500,7 +17485,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17514,10 +17499,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45369</v>
+        <v>46153</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17530,7 +17515,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17573,7 +17558,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17587,10 +17572,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45791</v>
+        <v>45554</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17603,7 +17588,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17646,7 +17631,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17660,10 +17645,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45404</v>
+        <v>45791</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17676,7 +17661,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17719,7 +17704,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17733,10 +17718,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45680</v>
+        <v>45594</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17734,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>11.2</v>
+        <v>8.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17777,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17791,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45707</v>
+        <v>45518</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17807,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17850,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17864,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45707</v>
+        <v>46176</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17880,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17923,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17937,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45586</v>
+        <v>46170</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17953,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +17996,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18010,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45811</v>
+        <v>46168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18026,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18069,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18083,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45811</v>
+        <v>46204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18113,8 +18098,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18147,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18161,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45811</v>
+        <v>46212</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18186,8 +18176,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18225,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18239,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45450</v>
+        <v>46255</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18255,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18298,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18317,10 +18312,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45819</v>
+        <v>46224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18328,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18371,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18386,14 +18381,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45820</v>
+        <v>46267</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18406,7 +18401,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18444,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18458,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45826</v>
+        <v>46234</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18474,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18517,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18531,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45082</v>
+        <v>46234</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18547,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18590,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18604,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45271</v>
+        <v>46239</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18620,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18663,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18677,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45782</v>
+        <v>46240</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18697,8 +18692,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,13 +18770,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18819,7 +18814,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18829,14 +18824,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18848,8 +18843,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,36 +1461,36 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38064-2023</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45159</v>
+        <v>45873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,13 +1747,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1789,39 +1784,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
     </row>
@@ -1845,7 +1840,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1933,7 +1928,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 36671-2025</t>
+          <t>A 31051-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1947,10 +1942,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45873</v>
+        <v>46215</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1963,17 +1958,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1987,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2003,42 +1998,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31051-2026</t>
+          <t>A 38064-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46215</v>
+        <v>45159</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,17 +2062,22 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2104,39 +2104,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 69666-2021</t>
+          <t>A 55581-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44532</v>
+        <v>44475</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55581-2021</t>
+          <t>A 69666-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44475</v>
+        <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44858</v>
+        <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45369</v>
+        <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44494</v>
+        <v>45534</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,8 +3637,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3681,7 +3686,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3695,10 +3700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45224</v>
+        <v>44705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3711,7 +3716,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3754,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3768,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45198</v>
+        <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3784,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3827,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3841,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45013</v>
+        <v>45560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3857,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3900,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3914,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45050</v>
+        <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3930,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3973,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3987,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45042</v>
+        <v>44958</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4003,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4046,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4060,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44858</v>
+        <v>44868</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4076,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4119,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4129,14 +4134,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44749</v>
+        <v>45191</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4149,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4192,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4206,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45055</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4222,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4265,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4279,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44819</v>
+        <v>45204</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4294,8 +4299,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4338,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4352,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44868</v>
+        <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4368,7 +4378,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4411,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4425,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45247</v>
+        <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4441,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4484,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45204</v>
+        <v>45328</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4513,13 +4523,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4592,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4635,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4649,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45169</v>
+        <v>45369</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4665,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45791</v>
+        <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4738,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4781,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45336</v>
+        <v>45350</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4808,6 +4813,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4854,7 +4864,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4868,10 +4878,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45113</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4884,7 +4894,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4927,7 +4937,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4941,10 +4951,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45012</v>
+        <v>45126</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4957,7 +4967,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5000,7 +5010,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5014,10 +5024,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45414</v>
+        <v>44498</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5030,7 +5040,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5073,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5087,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44868</v>
+        <v>45567</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5103,7 +5113,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5146,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5160,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45404</v>
+        <v>45109</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5176,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5219,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5233,10 +5243,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44531</v>
+        <v>45551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5292,7 +5302,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5306,10 +5316,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44890</v>
+        <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5322,7 +5332,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5365,7 +5375,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5379,10 +5389,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44890</v>
+        <v>45300</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5394,8 +5404,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5438,7 +5453,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5452,10 +5467,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44813</v>
+        <v>44917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5468,7 +5483,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5511,7 +5526,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5525,10 +5540,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45098</v>
+        <v>44999</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5541,7 +5556,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5584,7 +5599,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5598,10 +5613,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44866</v>
+        <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5614,7 +5629,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5657,7 +5672,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5671,10 +5686,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44476</v>
+        <v>45329</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5686,8 +5701,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5730,7 +5750,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5744,10 +5764,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44876</v>
+        <v>45099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5760,7 +5780,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5803,7 +5823,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5817,10 +5837,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45680</v>
+        <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5833,7 +5853,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5876,7 +5896,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5890,10 +5910,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45771</v>
+        <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5906,7 +5926,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5949,7 +5969,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5963,10 +5983,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44603</v>
+        <v>44890</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5979,7 +5999,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6022,7 +6042,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6036,10 +6056,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44797</v>
+        <v>45751</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6052,7 +6072,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6095,7 +6115,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6109,10 +6129,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45113</v>
+        <v>44536</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6125,7 +6145,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6168,7 +6188,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6182,10 +6202,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44651</v>
+        <v>45918</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6198,7 +6218,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6258,7 +6278,7 @@
         <v>45803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6314,7 +6334,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6328,10 +6348,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45884</v>
+        <v>45111</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6343,13 +6363,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6392,7 +6407,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6406,10 +6421,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45376</v>
+        <v>44476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6421,13 +6436,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6470,7 +6480,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6484,10 +6494,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45109</v>
+        <v>45884</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6499,8 +6509,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6543,7 +6558,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6557,10 +6572,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45893</v>
+        <v>45119</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6573,7 +6588,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6616,7 +6631,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6626,14 +6641,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44498</v>
+        <v>44749</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6646,7 +6661,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6689,7 +6704,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6703,10 +6718,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44901</v>
+        <v>45893</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6719,7 +6734,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6779,7 +6794,7 @@
         <v>45660</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6835,7 +6850,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6845,14 +6860,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45903</v>
+        <v>45912</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6864,13 +6879,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6913,7 +6923,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6927,10 +6937,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44845</v>
+        <v>45621</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6943,7 +6953,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6986,7 +6996,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7000,10 +7010,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45629</v>
+        <v>45582</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7016,7 +7026,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7059,7 +7069,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7073,10 +7083,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45575</v>
+        <v>45706</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7089,7 +7099,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7132,7 +7142,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7142,14 +7152,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7161,8 +7171,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7205,7 +7220,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7215,14 +7230,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45903</v>
+        <v>45113</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7235,7 +7250,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7278,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7292,10 +7307,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44575</v>
+        <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7308,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7351,7 +7366,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7365,10 +7380,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45915</v>
+        <v>44748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7381,7 +7396,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7424,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7438,10 +7453,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44487</v>
+        <v>45910</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7454,7 +7469,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7497,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7511,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45588</v>
+        <v>45915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7527,7 +7542,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7570,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7580,14 +7595,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45495</v>
+        <v>45903</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7600,7 +7615,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7643,7 +7658,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7657,10 +7672,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44582</v>
+        <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7673,7 +7688,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7716,7 +7731,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7730,10 +7745,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45582</v>
+        <v>45925</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7745,8 +7760,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7789,7 +7809,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7803,10 +7823,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45329</v>
+        <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7824,7 +7844,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7867,7 +7887,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7881,10 +7901,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45925</v>
+        <v>45800</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7896,13 +7916,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7945,7 +7960,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7959,10 +7974,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45707</v>
+        <v>45792</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7975,7 +7990,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8018,7 +8033,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8032,10 +8047,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45044</v>
+        <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8048,7 +8063,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8091,7 +8106,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8105,10 +8120,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44536</v>
+        <v>45932</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8121,7 +8136,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8164,7 +8179,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8178,10 +8193,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45567</v>
+        <v>44749</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8194,7 +8209,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8237,7 +8252,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8251,10 +8266,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45586</v>
+        <v>45112</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8267,7 +8282,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8310,7 +8325,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8324,10 +8339,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45707</v>
+        <v>45800</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8340,7 +8355,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8383,7 +8398,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8397,10 +8412,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45932</v>
+        <v>45825</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8413,7 +8428,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8456,7 +8471,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8470,10 +8485,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45450</v>
+        <v>45939</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8486,7 +8501,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8529,7 +8544,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8543,10 +8558,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45811</v>
+        <v>45098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8559,7 +8574,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8602,7 +8617,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8616,10 +8631,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45811</v>
+        <v>45358</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8632,7 +8647,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8675,7 +8690,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8689,10 +8704,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45811</v>
+        <v>45804</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8705,7 +8720,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8748,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8762,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45616</v>
+        <v>45303</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8778,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8821,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8835,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45525</v>
+        <v>45019</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8851,7 +8866,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8894,7 +8909,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8908,10 +8923,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44995</v>
+        <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8924,7 +8939,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8967,7 +8982,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8981,10 +8996,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44974</v>
+        <v>45376</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8996,8 +9011,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9040,7 +9060,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9054,10 +9074,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45191</v>
+        <v>45065</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9070,7 +9090,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9113,7 +9133,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9127,10 +9147,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45554</v>
+        <v>45938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9143,7 +9163,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9186,7 +9206,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9200,10 +9220,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45939</v>
+        <v>46085</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9216,7 +9236,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9259,7 +9279,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9273,10 +9293,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45369</v>
+        <v>45554</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9289,7 +9309,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>9</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9332,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9346,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44550</v>
+        <v>45960</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9362,7 +9382,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9405,7 +9425,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9419,10 +9439,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44536</v>
+        <v>45140</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9435,7 +9455,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9478,7 +9498,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9492,10 +9512,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45616</v>
+        <v>44749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9508,7 +9528,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9551,7 +9571,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9565,10 +9585,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45588</v>
+        <v>44993</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9581,7 +9601,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9624,7 +9644,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9638,10 +9658,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45588</v>
+        <v>45967</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9654,7 +9674,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9697,7 +9717,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9711,10 +9731,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45629</v>
+        <v>45588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9727,7 +9747,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9770,7 +9790,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9784,10 +9804,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45588</v>
+        <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9799,8 +9819,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9843,7 +9868,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9857,10 +9882,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45229</v>
+        <v>45979</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9873,7 +9898,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9916,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9930,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45588</v>
+        <v>45554</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9946,7 +9971,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9989,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10003,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45953</v>
+        <v>45169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10019,7 +10044,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10062,7 +10087,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10072,14 +10097,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45820</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10091,8 +10116,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.3</v>
+        <v>11.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10135,7 +10165,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10149,10 +10179,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45960</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10165,7 +10195,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10208,7 +10238,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10222,10 +10252,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10238,7 +10268,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10281,7 +10311,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10295,10 +10325,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44999</v>
+        <v>44536</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10311,7 +10341,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10354,7 +10384,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10368,10 +10398,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45229</v>
+        <v>45414</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10384,7 +10414,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10427,7 +10457,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10437,14 +10467,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45819</v>
+        <v>46153</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10457,7 +10487,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10500,7 +10530,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10514,10 +10544,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45113</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10530,7 +10560,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10573,7 +10603,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10587,10 +10617,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44496</v>
+        <v>45248</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10603,7 +10633,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10646,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10660,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45098</v>
+        <v>44550</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10676,7 +10706,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10719,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10733,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45967</v>
+        <v>45594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10749,7 +10779,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10792,7 +10822,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10806,10 +10836,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45248</v>
+        <v>46007</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10822,7 +10852,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10865,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10879,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45979</v>
+        <v>46008</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10895,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10938,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10952,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45609</v>
+        <v>44797</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10968,7 +10998,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11011,7 +11041,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11025,10 +11055,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45042</v>
+        <v>44858</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11041,7 +11071,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11084,7 +11114,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11098,10 +11128,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44748</v>
+        <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11114,7 +11144,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11157,7 +11187,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11171,10 +11201,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45019</v>
+        <v>45629</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11187,7 +11217,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11230,7 +11260,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11244,10 +11274,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45019</v>
+        <v>45791</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11260,7 +11290,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11303,7 +11333,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11317,10 +11347,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45986</v>
+        <v>45113</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11332,13 +11362,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>11.2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11381,7 +11406,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11395,10 +11420,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45986</v>
+        <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11411,7 +11436,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11454,7 +11479,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11468,10 +11493,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45674</v>
+        <v>46034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11484,7 +11509,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11527,7 +11552,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11541,10 +11566,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45826</v>
+        <v>46034</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11557,7 +11582,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11600,7 +11625,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11614,10 +11639,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44749</v>
+        <v>45518</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11630,7 +11655,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11673,7 +11698,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11687,10 +11712,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45303</v>
+        <v>44813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11703,7 +11728,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11746,7 +11771,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11760,10 +11785,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46000</v>
+        <v>45042</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11776,7 +11801,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11819,7 +11844,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11833,10 +11858,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46034</v>
+        <v>45616</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11849,7 +11874,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11892,7 +11917,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11906,10 +11931,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46034</v>
+        <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11922,7 +11947,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11965,7 +11990,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11979,10 +12004,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46007</v>
+        <v>45588</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11995,7 +12020,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12055,7 +12080,7 @@
         <v>46038</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12116,7 +12141,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12130,10 +12155,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46008</v>
+        <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12189,7 +12214,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12203,10 +12228,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45450</v>
+        <v>44487</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12219,7 +12244,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12262,7 +12287,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12276,10 +12301,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44958</v>
+        <v>45050</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12292,7 +12317,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12335,7 +12360,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12349,10 +12374,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45300</v>
+        <v>45229</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12364,13 +12389,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12413,7 +12433,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12427,10 +12447,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45140</v>
+        <v>45113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12443,7 +12463,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12486,7 +12506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12500,10 +12520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44866</v>
+        <v>46072</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12516,7 +12536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12559,7 +12579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12573,10 +12593,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45350</v>
+        <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12588,13 +12608,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12637,7 +12652,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12651,10 +12666,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46240</v>
+        <v>46072</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12667,7 +12682,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12710,7 +12725,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12724,10 +12739,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46240</v>
+        <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12740,7 +12755,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12783,7 +12798,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12797,10 +12812,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45680</v>
+        <v>46090</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12813,7 +12828,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12856,7 +12871,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12866,14 +12881,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44879</v>
+        <v>46176</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12886,7 +12901,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12929,7 +12944,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12943,10 +12958,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44993</v>
+        <v>45336</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12959,7 +12974,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13002,7 +13017,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13016,10 +13031,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44917</v>
+        <v>44845</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13032,7 +13047,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13075,7 +13090,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13089,10 +13104,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45620</v>
+        <v>46170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13105,7 +13120,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13148,7 +13163,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13162,10 +13177,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46245</v>
+        <v>45771</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13178,7 +13193,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13221,7 +13236,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13235,10 +13250,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46072</v>
+        <v>46168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13251,7 +13266,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13294,7 +13309,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13308,10 +13323,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46072</v>
+        <v>45554</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13324,7 +13339,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13367,7 +13382,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13381,10 +13396,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46072</v>
+        <v>45013</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13397,7 +13412,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13440,7 +13455,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39411-2026</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13454,10 +13469,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46288</v>
+        <v>46121</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13475,7 +13490,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13518,7 +13533,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13532,10 +13547,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44858</v>
+        <v>44909</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13548,7 +13563,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13591,7 +13606,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13605,10 +13620,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46246</v>
+        <v>44901</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13620,13 +13635,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>13.1</v>
+        <v>4.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13669,7 +13679,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13679,14 +13689,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45554</v>
+        <v>44879</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13699,7 +13709,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13742,7 +13752,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13756,10 +13766,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46090</v>
+        <v>45042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13772,7 +13782,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13815,7 +13825,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13829,10 +13839,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46090</v>
+        <v>46204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13844,8 +13854,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13888,7 +13903,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13902,10 +13917,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45082</v>
+        <v>45044</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13918,7 +13933,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13961,7 +13976,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13975,10 +13990,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44995</v>
+        <v>45109</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13991,7 +14006,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14034,7 +14049,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14048,10 +14063,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45109</v>
+        <v>44866</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14064,7 +14079,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14107,7 +14122,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14121,10 +14136,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45560</v>
+        <v>44876</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14137,7 +14152,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14180,7 +14195,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14194,10 +14209,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44749</v>
+        <v>45140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14210,7 +14225,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14253,7 +14268,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14267,10 +14282,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45111</v>
+        <v>45525</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14283,7 +14298,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14326,7 +14341,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14340,10 +14355,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45782</v>
+        <v>46212</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14355,8 +14370,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14399,7 +14419,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14413,10 +14433,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45271</v>
+        <v>44858</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14429,7 +14449,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14472,7 +14492,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14486,10 +14506,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46121</v>
+        <v>45450</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14501,13 +14521,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14550,7 +14565,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14564,10 +14579,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45370</v>
+        <v>45019</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14580,7 +14595,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14623,7 +14638,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14637,10 +14652,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45280</v>
+        <v>45575</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14652,13 +14667,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14701,7 +14711,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14715,10 +14725,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45099</v>
+        <v>46255</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14731,7 +14741,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14774,7 +14784,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14788,10 +14798,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45358</v>
+        <v>45229</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14804,7 +14814,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.1</v>
+        <v>9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14847,7 +14857,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14861,10 +14871,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44909</v>
+        <v>44868</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14877,7 +14887,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14920,7 +14930,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14934,10 +14944,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45706</v>
+        <v>45495</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14950,7 +14960,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14993,7 +15003,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15007,10 +15017,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45126</v>
+        <v>45370</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15023,7 +15033,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15066,7 +15076,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15080,10 +15090,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44705</v>
+        <v>45098</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15096,7 +15106,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15139,7 +15149,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15153,10 +15163,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45065</v>
+        <v>44575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15169,7 +15179,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15212,7 +15222,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15222,14 +15232,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45140</v>
+        <v>46224</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15242,7 +15252,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15285,7 +15295,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15299,10 +15309,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45621</v>
+        <v>46267</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15315,7 +15325,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15358,7 +15368,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15372,10 +15382,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45119</v>
+        <v>45236</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15388,7 +15398,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15431,7 +15441,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15445,10 +15455,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45229</v>
+        <v>44651</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15461,7 +15471,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15504,7 +15514,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15518,10 +15528,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45236</v>
+        <v>45224</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15534,7 +15544,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15577,7 +15587,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15591,10 +15601,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45309</v>
+        <v>45527</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15607,7 +15617,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15650,7 +15660,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15664,10 +15674,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45792</v>
+        <v>45609</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15680,7 +15690,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15723,7 +15733,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15737,10 +15747,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45751</v>
+        <v>44819</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15753,7 +15763,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15796,7 +15806,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15810,10 +15820,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45554</v>
+        <v>45620</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15826,7 +15836,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15869,7 +15879,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15883,10 +15893,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45205</v>
+        <v>44890</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15899,7 +15909,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15942,7 +15952,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15956,10 +15966,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44897</v>
+        <v>45588</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15972,7 +15982,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16015,7 +16025,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16029,10 +16039,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45534</v>
+        <v>46234</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16044,13 +16054,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16093,7 +16098,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16107,10 +16112,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45527</v>
+        <v>46234</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16123,7 +16128,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16166,7 +16171,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16180,10 +16185,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45328</v>
+        <v>44531</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16196,7 +16201,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16239,7 +16244,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16253,10 +16258,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44858</v>
+        <v>45098</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16269,7 +16274,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16312,7 +16317,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16326,10 +16331,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45800</v>
+        <v>45616</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16342,7 +16347,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16385,7 +16390,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16399,10 +16404,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45800</v>
+        <v>44995</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16415,7 +16420,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16458,7 +16463,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16472,10 +16477,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45918</v>
+        <v>46240</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16488,7 +16493,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16531,7 +16536,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16545,10 +16550,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45098</v>
+        <v>46240</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16561,7 +16566,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16604,7 +16609,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16618,10 +16623,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45804</v>
+        <v>45680</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16634,7 +16639,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16677,7 +16682,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16691,10 +16696,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45938</v>
+        <v>45198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16707,7 +16712,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16750,7 +16755,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16764,10 +16769,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45912</v>
+        <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16780,7 +16785,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16823,7 +16828,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16837,10 +16842,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45825</v>
+        <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16853,7 +16858,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16896,7 +16901,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16910,10 +16915,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46085</v>
+        <v>46240</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16925,8 +16930,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16969,7 +16979,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16983,10 +16993,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45551</v>
+        <v>45777</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16999,7 +17009,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17042,7 +17052,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17056,10 +17066,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46141</v>
+        <v>45777</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17071,13 +17081,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17120,7 +17125,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17134,10 +17139,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45112</v>
+        <v>46239</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17150,7 +17155,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17193,7 +17198,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17207,10 +17212,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45642</v>
+        <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17223,7 +17228,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17266,7 +17271,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17280,10 +17285,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45777</v>
+        <v>45369</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17296,7 +17301,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17339,7 +17344,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17353,10 +17358,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45777</v>
+        <v>45791</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17369,7 +17374,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17412,7 +17417,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 39411-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17426,10 +17431,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45777</v>
+        <v>46288</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17441,8 +17446,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17485,7 +17495,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17499,10 +17509,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46153</v>
+        <v>46245</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17515,7 +17525,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17558,7 +17568,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17572,10 +17582,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45554</v>
+        <v>45404</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17588,7 +17598,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17631,7 +17641,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17645,10 +17655,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45791</v>
+        <v>45680</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17661,7 +17671,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17704,7 +17714,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17718,10 +17728,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45594</v>
+        <v>46246</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17733,8 +17743,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>8.1</v>
+        <v>13.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17777,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17791,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45518</v>
+        <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17807,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17850,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17864,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46176</v>
+        <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17880,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17923,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17937,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46170</v>
+        <v>45586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17953,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -17996,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18010,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46168</v>
+        <v>45811</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18026,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18069,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18083,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46204</v>
+        <v>45811</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18098,13 +18113,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18147,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18161,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46212</v>
+        <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18176,13 +18186,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18225,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18239,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46255</v>
+        <v>45450</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18255,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18298,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18312,10 +18317,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46224</v>
+        <v>45819</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18328,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18371,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18381,14 +18386,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46267</v>
+        <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18401,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18444,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18458,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46234</v>
+        <v>45826</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18474,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18517,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18531,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46234</v>
+        <v>45082</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18547,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18590,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18604,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46239</v>
+        <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18620,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18663,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18677,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46240</v>
+        <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18692,13 +18697,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,8 +18770,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18814,7 +18819,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18824,14 +18829,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,13 +18848,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32887-2023</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Dvärghäxört
-Gulnål</t>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 37754-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44999</v>
+        <v>46279</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,43 +1461,47 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Blåsippa
+Orre</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 37754-2026</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1511,10 +1515,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46279</v>
+        <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1527,13 +1531,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1567,40 +1571,36 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa
-Orre</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 36671-2025</t>
+          <t>A 38064-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45873</v>
+        <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,8 +1747,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1784,39 +1789,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
@@ -1840,7 +1845,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1928,7 +1933,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31051-2026</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,10 +1947,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46215</v>
+        <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1958,16 +1963,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1982,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1998,148 +2003,143 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 31051-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38064-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45159</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 70363-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44571</v>
+        <v>44535</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 70363-2021</t>
+          <t>A 25830-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44535</v>
+        <v>44733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25830-2022</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44733</v>
+        <v>44571</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55581-2021</t>
+          <t>A 69666-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44475</v>
+        <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 69666-2021</t>
+          <t>A 55581-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44532</v>
+        <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45534</v>
+        <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3637,13 +3637,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3686,7 +3681,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44705</v>
+        <v>45204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3715,8 +3710,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45588</v>
+        <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45560</v>
+        <v>45414</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44974</v>
+        <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44958</v>
+        <v>45336</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44868</v>
+        <v>44890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45191</v>
+        <v>44890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45204</v>
+        <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4299,13 +4299,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4343,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4357,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45246</v>
+        <v>45376</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4377,8 +4372,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44995</v>
+        <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45328</v>
+        <v>44845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45247</v>
+        <v>45680</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45369</v>
+        <v>46034</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45629</v>
+        <v>46034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45350</v>
+        <v>44575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4815,13 +4815,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4864,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4878,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>45113</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4894,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4937,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45126</v>
+        <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4967,7 +4962,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5010,7 +5005,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44498</v>
+        <v>45884</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5039,8 +5034,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45567</v>
+        <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5112,8 +5112,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>8.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5156,7 +5161,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5170,10 +5175,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45109</v>
+        <v>45893</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5186,7 +5191,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5229,7 +5234,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5243,10 +5248,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45551</v>
+        <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5259,7 +5264,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5302,7 +5307,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 335-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5316,10 +5321,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44897</v>
+        <v>45660</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5332,7 +5337,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5375,7 +5380,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5389,10 +5394,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45300</v>
+        <v>45495</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5404,13 +5409,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44917</v>
+        <v>44582</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12322-2023</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44999</v>
+        <v>45903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5555,8 +5555,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5599,7 +5604,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45674</v>
+        <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5628,8 +5633,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5672,7 +5682,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5686,10 +5696,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45329</v>
+        <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5701,13 +5711,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5750,7 +5755,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5764,10 +5769,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45099</v>
+        <v>44536</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5780,7 +5785,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5823,7 +5828,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5837,10 +5842,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44603</v>
+        <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5853,7 +5858,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5896,7 +5901,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5906,14 +5911,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45205</v>
+        <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5926,7 +5931,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.1</v>
+        <v>7.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5969,7 +5974,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5983,10 +5988,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44890</v>
+        <v>45915</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6042,7 +6047,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45751</v>
+        <v>45525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6072,7 +6077,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6115,7 +6120,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6129,10 +6134,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44536</v>
+        <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6145,7 +6150,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6188,7 +6193,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6202,10 +6207,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45918</v>
+        <v>46072</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6218,7 +6223,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6261,7 +6266,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6275,10 +6280,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45803</v>
+        <v>46072</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6291,7 +6296,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6334,7 +6339,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6348,10 +6353,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45111</v>
+        <v>46072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6364,7 +6369,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6407,7 +6412,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6421,10 +6426,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44476</v>
+        <v>45554</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6437,7 +6442,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6480,7 +6485,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6494,10 +6499,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45884</v>
+        <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6509,13 +6514,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45119</v>
+        <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6587,8 +6587,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6631,7 +6636,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6641,14 +6646,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44749</v>
+        <v>45932</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6661,7 +6666,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6704,7 +6709,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6718,10 +6723,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45893</v>
+        <v>45707</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6734,7 +6739,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6777,7 +6782,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 335-2025</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6791,10 +6796,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45660</v>
+        <v>45586</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6807,7 +6812,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6850,7 +6855,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6864,10 +6869,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45912</v>
+        <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6880,7 +6885,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6923,7 +6928,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6937,10 +6942,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45621</v>
+        <v>45588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6953,7 +6958,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6996,7 +7001,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7010,10 +7015,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45582</v>
+        <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7026,7 +7031,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7069,7 +7074,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7083,10 +7088,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7099,7 +7104,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7142,7 +7147,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7152,14 +7157,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45903</v>
+        <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7171,13 +7176,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7220,7 +7220,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45113</v>
+        <v>45588</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45629</v>
+        <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 12322-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44748</v>
+        <v>44999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7439,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45910</v>
+        <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45915</v>
+        <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7595,14 +7595,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45903</v>
+        <v>44496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7658,7 +7658,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45055</v>
+        <v>45811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45925</v>
+        <v>45811</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7760,13 +7760,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>9.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7809,7 +7804,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7823,10 +7818,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45280</v>
+        <v>45953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7838,13 +7833,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7887,7 +7877,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7901,10 +7891,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45800</v>
+        <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7917,7 +7907,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7960,7 +7950,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7974,10 +7964,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45792</v>
+        <v>45811</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7990,7 +7980,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8033,7 +8023,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8047,10 +8037,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44866</v>
+        <v>46121</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8062,8 +8052,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8106,7 +8101,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8120,10 +8115,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45932</v>
+        <v>45609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8136,7 +8131,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8179,7 +8174,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8193,10 +8188,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44749</v>
+        <v>45967</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8209,7 +8204,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8252,7 +8247,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8266,10 +8261,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45112</v>
+        <v>45042</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8282,7 +8277,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8325,7 +8320,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8339,10 +8334,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45800</v>
+        <v>45019</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8355,7 +8350,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8398,7 +8393,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8412,10 +8407,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45825</v>
+        <v>45019</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8428,7 +8423,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8471,7 +8466,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8485,10 +8480,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45939</v>
+        <v>45979</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8501,7 +8496,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8544,7 +8539,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8558,10 +8553,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45098</v>
+        <v>45674</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8574,7 +8569,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8617,7 +8612,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8631,10 +8626,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45358</v>
+        <v>45986</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8646,8 +8641,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>11.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45804</v>
+        <v>44749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45303</v>
+        <v>45986</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8836,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45019</v>
+        <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45953</v>
+        <v>45065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45376</v>
+        <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9011,13 +9011,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9060,7 +9055,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9074,10 +9069,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45065</v>
+        <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9090,7 +9085,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9133,7 +9128,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9147,10 +9142,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45938</v>
+        <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9163,7 +9158,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9206,7 +9201,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9220,10 +9215,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46085</v>
+        <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9236,7 +9231,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9279,7 +9274,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9293,10 +9288,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45554</v>
+        <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9309,7 +9304,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9352,7 +9347,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9366,10 +9361,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45960</v>
+        <v>45792</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9382,7 +9377,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9425,7 +9420,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9439,10 +9434,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45140</v>
+        <v>45013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9455,7 +9450,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9498,7 +9493,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9508,14 +9503,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44749</v>
+        <v>45820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9528,7 +9523,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9571,7 +9566,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9585,10 +9580,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44993</v>
+        <v>46007</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9601,7 +9596,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9644,7 +9639,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9658,10 +9653,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45967</v>
+        <v>45042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9674,7 +9669,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9717,7 +9712,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9731,10 +9726,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45588</v>
+        <v>46008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9747,7 +9742,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9790,7 +9785,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9800,14 +9795,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46141</v>
+        <v>45819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9819,13 +9814,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9868,7 +9858,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9882,10 +9872,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45979</v>
+        <v>44858</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9898,7 +9888,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9941,7 +9931,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9955,10 +9945,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45554</v>
+        <v>45055</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9971,7 +9961,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10014,7 +10004,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10028,10 +10018,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45169</v>
+        <v>44819</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10044,7 +10034,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10087,7 +10077,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10101,10 +10091,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45986</v>
+        <v>44868</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10116,13 +10106,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>11.2</v>
+        <v>0.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10165,7 +10150,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10179,10 +10164,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45986</v>
+        <v>45800</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10195,7 +10180,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10238,7 +10223,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10252,10 +10237,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45229</v>
+        <v>45800</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10268,7 +10253,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10311,7 +10296,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10325,10 +10310,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44536</v>
+        <v>45918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10341,7 +10326,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10384,7 +10369,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10398,10 +10383,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45414</v>
+        <v>45247</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10414,7 +10399,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10457,7 +10442,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10471,10 +10456,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46153</v>
+        <v>45804</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10487,7 +10472,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10530,7 +10515,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10544,10 +10529,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10560,7 +10545,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10603,7 +10588,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10617,10 +10602,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45248</v>
+        <v>45912</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10633,7 +10618,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10676,7 +10661,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10690,10 +10675,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44550</v>
+        <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10706,7 +10691,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10749,7 +10734,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10763,10 +10748,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45594</v>
+        <v>45246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10779,7 +10764,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10822,7 +10807,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10836,10 +10821,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46007</v>
+        <v>45826</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10852,7 +10837,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10895,7 +10880,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10909,10 +10894,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46008</v>
+        <v>46085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10925,7 +10910,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10968,7 +10953,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10982,10 +10967,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44797</v>
+        <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10998,7 +10983,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11041,7 +11026,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11055,10 +11040,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44858</v>
+        <v>45113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11071,7 +11056,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11114,7 +11099,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11128,10 +11113,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44496</v>
+        <v>45012</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11144,7 +11129,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11187,7 +11172,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11201,10 +11186,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45629</v>
+        <v>46141</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11216,8 +11201,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11260,7 +11250,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11274,10 +11264,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45791</v>
+        <v>44531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11290,7 +11280,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11333,7 +11323,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11347,10 +11337,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45113</v>
+        <v>45098</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11363,7 +11353,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11406,7 +11396,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11420,10 +11410,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45012</v>
+        <v>44866</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11436,7 +11426,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11479,7 +11469,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11493,10 +11483,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46034</v>
+        <v>44476</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11509,7 +11499,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11552,7 +11542,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11566,10 +11556,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46034</v>
+        <v>44876</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11582,7 +11572,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11625,7 +11615,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11639,10 +11629,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45518</v>
+        <v>46153</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11655,7 +11645,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11698,7 +11688,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11712,10 +11702,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44813</v>
+        <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11728,7 +11718,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11771,7 +11761,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11785,10 +11775,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45042</v>
+        <v>44603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11801,7 +11791,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11844,7 +11834,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11858,10 +11848,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45616</v>
+        <v>45791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11874,7 +11864,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11917,7 +11907,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11931,10 +11921,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45588</v>
+        <v>45594</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11947,7 +11937,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11990,7 +11980,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12004,10 +11994,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45588</v>
+        <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12020,7 +12010,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12063,7 +12053,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12077,10 +12067,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46038</v>
+        <v>45109</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12092,13 +12082,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12141,7 +12126,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12155,10 +12140,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44582</v>
+        <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12171,7 +12156,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12214,7 +12199,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12228,10 +12213,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44487</v>
+        <v>44901</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12244,7 +12229,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12287,7 +12272,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12301,10 +12286,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45050</v>
+        <v>45518</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12317,7 +12302,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12360,7 +12345,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12374,10 +12359,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45229</v>
+        <v>45082</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12390,7 +12375,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12433,7 +12418,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12447,10 +12432,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45113</v>
+        <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12506,7 +12491,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12520,10 +12505,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46072</v>
+        <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12536,7 +12521,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12579,7 +12564,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12593,10 +12578,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46072</v>
+        <v>45271</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12609,7 +12594,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12652,7 +12637,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12666,10 +12651,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46072</v>
+        <v>46176</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12682,7 +12667,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12725,7 +12710,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12739,10 +12724,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46090</v>
+        <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12755,7 +12740,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12798,7 +12783,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12812,10 +12797,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46090</v>
+        <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12828,7 +12813,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12871,7 +12856,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12885,10 +12870,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46176</v>
+        <v>45044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12901,7 +12886,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12944,7 +12929,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12958,10 +12943,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45336</v>
+        <v>46170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12974,7 +12959,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13017,7 +13002,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13031,10 +13016,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44845</v>
+        <v>45567</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13047,7 +13032,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13090,7 +13075,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13104,10 +13089,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46170</v>
+        <v>45616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13120,7 +13105,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13163,7 +13148,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13177,10 +13162,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45771</v>
+        <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13193,7 +13178,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13236,7 +13221,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13250,10 +13235,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46168</v>
+        <v>44995</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13266,7 +13251,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13309,7 +13294,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13323,10 +13308,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45554</v>
+        <v>45191</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13339,7 +13324,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13382,7 +13367,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13396,10 +13381,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45013</v>
+        <v>44550</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13412,7 +13397,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13455,7 +13440,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13469,10 +13454,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46121</v>
+        <v>44536</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13484,13 +13469,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13533,7 +13513,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13547,10 +13527,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44909</v>
+        <v>45616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13563,7 +13543,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13606,7 +13586,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13620,10 +13600,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44901</v>
+        <v>45588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13636,7 +13616,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13679,7 +13659,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13689,14 +13669,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44879</v>
+        <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13709,7 +13689,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13752,7 +13732,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13766,10 +13746,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45042</v>
+        <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13782,7 +13762,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13842,7 +13822,7 @@
         <v>46204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13903,7 +13883,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13917,10 +13897,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45044</v>
+        <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13976,7 +13956,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13990,10 +13970,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45109</v>
+        <v>45229</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14006,7 +13986,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14049,7 +14029,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14063,10 +14043,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44866</v>
+        <v>45098</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14122,7 +14102,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14136,10 +14116,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44876</v>
+        <v>45248</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14152,7 +14132,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14195,7 +14175,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14209,10 +14189,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45140</v>
+        <v>46212</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14224,8 +14204,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14268,7 +14253,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14282,10 +14267,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45525</v>
+        <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14298,7 +14283,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14341,7 +14326,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14355,10 +14340,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46212</v>
+        <v>46255</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14370,13 +14355,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14419,7 +14399,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14433,10 +14413,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44858</v>
+        <v>45303</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14449,7 +14429,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14492,7 +14472,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14502,14 +14482,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45450</v>
+        <v>46224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14522,7 +14502,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14565,7 +14545,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14579,10 +14559,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45019</v>
+        <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14595,7 +14575,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14638,7 +14618,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14652,10 +14632,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45575</v>
+        <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14668,7 +14648,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14711,7 +14691,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14725,10 +14705,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46255</v>
+        <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14741,7 +14721,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14784,7 +14764,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14798,10 +14778,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45229</v>
+        <v>45300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14813,8 +14793,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14857,7 +14842,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14871,10 +14856,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44868</v>
+        <v>45140</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14887,7 +14872,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14930,7 +14915,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14944,10 +14929,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45495</v>
+        <v>44866</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14960,7 +14945,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15003,7 +14988,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15017,10 +15002,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45370</v>
+        <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15032,8 +15017,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15076,7 +15066,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15090,10 +15080,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45098</v>
+        <v>46234</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15149,7 +15139,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15163,10 +15153,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44575</v>
+        <v>46234</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15179,7 +15169,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15222,7 +15212,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15232,14 +15222,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46224</v>
+        <v>45680</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15252,7 +15242,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15295,7 +15285,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15305,14 +15295,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46267</v>
+        <v>44879</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15325,7 +15315,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15368,7 +15358,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15382,10 +15372,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45236</v>
+        <v>46239</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15398,7 +15388,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15441,7 +15431,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15455,10 +15445,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44651</v>
+        <v>46240</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15470,8 +15460,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15514,7 +15509,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15528,10 +15523,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45224</v>
+        <v>44993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15587,7 +15582,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15601,10 +15596,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45527</v>
+        <v>44917</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15617,7 +15612,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15660,7 +15655,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15674,10 +15669,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45609</v>
+        <v>45620</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15690,7 +15685,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15733,7 +15728,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15747,10 +15742,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44819</v>
+        <v>46240</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15763,7 +15758,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15806,7 +15801,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15820,10 +15815,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45620</v>
+        <v>46240</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15836,7 +15831,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15879,7 +15874,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15893,10 +15888,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44890</v>
+        <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15909,7 +15904,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15952,7 +15947,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15966,10 +15961,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45588</v>
+        <v>44858</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16025,7 +16020,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 39411-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16039,10 +16034,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46234</v>
+        <v>46288</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16054,8 +16049,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16098,7 +16098,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16112,10 +16112,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46234</v>
+        <v>46246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16127,8 +16127,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>4.5</v>
+        <v>13.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16171,7 +16176,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16185,10 +16190,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44531</v>
+        <v>45554</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16201,7 +16206,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16244,7 +16249,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16258,10 +16263,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45098</v>
+        <v>44995</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16274,7 +16279,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16317,7 +16322,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16331,10 +16336,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45616</v>
+        <v>45109</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16347,7 +16352,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16390,7 +16395,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16404,10 +16409,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44995</v>
+        <v>45560</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16420,7 +16425,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16463,7 +16468,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16477,10 +16482,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46240</v>
+        <v>44749</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16493,7 +16498,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16536,7 +16541,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16550,10 +16555,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46240</v>
+        <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16566,7 +16571,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16609,7 +16614,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16623,10 +16628,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45680</v>
+        <v>45370</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16639,7 +16644,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16682,7 +16687,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16696,10 +16701,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45198</v>
+        <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16711,8 +16716,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16755,7 +16765,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16769,10 +16779,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44858</v>
+        <v>45099</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16785,7 +16795,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16828,7 +16838,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16842,10 +16852,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45777</v>
+        <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16858,7 +16868,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16901,7 +16911,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16915,10 +16925,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46240</v>
+        <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16930,13 +16940,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16979,7 +16984,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16993,10 +16998,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45777</v>
+        <v>45126</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17009,7 +17014,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17052,7 +17057,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17066,10 +17071,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45777</v>
+        <v>44705</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17082,7 +17087,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17125,7 +17130,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17139,10 +17144,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46239</v>
+        <v>45140</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17155,7 +17160,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17198,7 +17203,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17212,10 +17217,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45554</v>
+        <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17228,7 +17233,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17271,7 +17276,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17285,10 +17290,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45369</v>
+        <v>45236</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17301,7 +17306,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17344,7 +17349,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17358,10 +17363,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45791</v>
+        <v>45309</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17374,7 +17379,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17417,7 +17422,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 39411-2026</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17431,10 +17436,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46288</v>
+        <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17446,13 +17451,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17495,7 +17495,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17509,10 +17509,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46245</v>
+        <v>45554</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17568,7 +17568,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17582,10 +17582,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45404</v>
+        <v>45205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17641,7 +17641,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17655,10 +17655,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45680</v>
+        <v>44897</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17714,7 +17714,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17728,10 +17728,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46246</v>
+        <v>45534</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45707</v>
+        <v>45527</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45707</v>
+        <v>45328</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45586</v>
+        <v>44858</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45811</v>
+        <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18084,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18098,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45811</v>
+        <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18157,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18171,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45811</v>
+        <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18230,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45450</v>
+        <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18303,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18313,14 +18313,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45819</v>
+        <v>45777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18386,14 +18386,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45820</v>
+        <v>45777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45826</v>
+        <v>45777</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45082</v>
+        <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18609,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45271</v>
+        <v>45369</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45782</v>
+        <v>45791</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,13 +18770,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18819,7 +18814,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18829,14 +18824,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18848,8 +18843,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46279</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>46215</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44535</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44571</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45414</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45336</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45376</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>44845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45680</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46034</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>46034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45113</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45884</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45893</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45660</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45495</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44582</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44536</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45915</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>46072</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>46072</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>46072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45554</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45932</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45707</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45586</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45588</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>45811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45811</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45811</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>46121</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45967</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45042</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45019</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45019</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45979</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45674</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45986</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45986</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45792</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>46007</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>46008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44858</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45055</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44819</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>44868</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45800</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45800</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45247</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45804</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45912</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45826</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45012</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46141</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45098</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44866</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44476</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44876</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46153</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45594</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45109</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44901</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45518</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45082</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45271</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46176</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>46170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45567</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44995</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45191</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44550</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>44536</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>46204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45229</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45098</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45248</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46212</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46255</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45303</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45140</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44866</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>46234</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46234</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45680</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44879</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>46239</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46240</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44917</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45620</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46240</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46240</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44858</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46288</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45554</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>44995</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45109</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45560</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44749</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45370</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45099</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45126</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44705</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45140</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45236</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45309</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45554</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44897</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45534</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45527</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45328</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44858</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45777</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45369</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45791</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46279</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45873</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>46215</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44535</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>44514</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>44571</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45050</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45414</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45336</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>44890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45376</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>44845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45680</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46034</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>46034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45113</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45884</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45893</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45660</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45495</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44582</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45903</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45329</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44536</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45915</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>46072</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>46072</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>46072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45554</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45369</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45932</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45707</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45586</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>46090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45588</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45939</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44496</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>45811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45811</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45811</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>46121</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45967</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45042</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45019</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45019</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45979</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45674</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45986</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44749</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45986</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>46000</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45224</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45792</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>46007</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>46008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44858</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45055</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>44819</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>44868</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45800</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45800</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45247</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45804</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45912</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45246</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45826</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45012</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46141</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45098</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44866</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44476</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44876</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46153</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45594</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45109</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44901</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45518</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45082</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45271</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46176</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>46170</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45567</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44995</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45191</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44550</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>44536</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>46204</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45229</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45098</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45248</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46212</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46255</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45303</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>46224</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>46267</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45140</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44866</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>46234</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46234</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45680</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44879</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>46239</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46240</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44917</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45620</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46240</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46240</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44858</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46288</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45554</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>44995</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45109</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45560</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44749</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45370</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45099</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45358</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44909</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45126</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44705</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45140</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45236</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45309</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45751</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45554</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45205</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44897</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45534</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45527</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45328</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44858</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45098</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45777</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45369</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45791</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45351</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>45415</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 12413-2023</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1249,36 +1249,36 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
+          <t>Dvärghäxört
+Gulnål</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37754-2026</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46279</v>
+        <v>44999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,149 +1461,149 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 37754-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Orre</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 37754-2026 artfynd.xlsx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 37754-2026 karta.png", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 37754-2026 georefererad karta.tif", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 37754-2026 FSC-klagomål.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 37754-2026 FSC-klagomål mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 37754-2026 tillsynsbegäran.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 37754-2026 tillsynsbegäran mail.docx", "A 37754-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 37754-2026 prioriterade fågelarter.docx", "A 37754-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32887-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Gulnål</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45351</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45159</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55118-2025</t>
+          <t>A 36671-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45967</v>
+        <v>45873</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1882,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1898,143 +1898,143 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 55118-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Luddfingersvamp</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 36671-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45873</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>46215</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 70363-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44535</v>
+        <v>44571</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64999-2021</t>
+          <t>A 70363-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44514</v>
+        <v>44535</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25830-2022</t>
+          <t>A 64999-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44733</v>
+        <v>44514</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 25830-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44571</v>
+        <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>44470</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44809</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44600</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44526</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44498</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44494</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44858</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28880-2022</t>
+          <t>A 21324-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44749</v>
+        <v>44705</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 41726-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45204</v>
+        <v>45560</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3710,13 +3710,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3759,7 +3754,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19471-2023</t>
+          <t>A 36289-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3773,10 +3768,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45050</v>
+        <v>45534</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3788,8 +3783,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17391-2024</t>
+          <t>A 4976-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45414</v>
+        <v>44958</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5966-2024</t>
+          <t>A 45313-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45336</v>
+        <v>45191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56210-2022</t>
+          <t>A 47702-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44890</v>
+        <v>45588</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56218-2022</t>
+          <t>A 59998-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44890</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38526-2022</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44813</v>
+        <v>45204</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4226,8 +4226,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35154-2022</t>
+          <t>A 8176-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44797</v>
+        <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11916-2024</t>
+          <t>A 57720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45376</v>
+        <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4372,13 +4377,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15691-2024</t>
+          <t>A 23125-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45404</v>
+        <v>45791</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45667-2022</t>
+          <t>A 62440-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44845</v>
+        <v>46007</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3571-2025</t>
+          <t>A 62844-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45680</v>
+        <v>46008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.2</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1695-2026</t>
+          <t>A 25693-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46034</v>
+        <v>45803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1689-2026</t>
+          <t>A 15691-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46034</v>
+        <v>45404</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2027-2022</t>
+          <t>A 3571-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44575</v>
+        <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30990-2023</t>
+          <t>A 11916-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45113</v>
+        <v>44995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25693-2025</t>
+          <t>A 38878-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45803</v>
+        <v>45884</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4961,8 +4961,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5005,7 +5010,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38878-2025</t>
+          <t>A 10837-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5019,10 +5024,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45884</v>
+        <v>45369</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5034,13 +5039,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2981-2026</t>
+          <t>A 4696-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46038</v>
+        <v>45328</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5112,13 +5112,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5161,7 +5156,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40043-2025</t>
+          <t>A 57957-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5175,10 +5170,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45893</v>
+        <v>45247</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5191,7 +5186,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58225-2021</t>
+          <t>A 40043-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5248,10 +5243,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44487</v>
+        <v>45893</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5264,7 +5259,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5324,7 +5319,7 @@
         <v>45660</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5380,7 +5375,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30616-2024</t>
+          <t>A 8307-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5394,10 +5389,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45495</v>
+        <v>45350</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5409,8 +5404,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3141-2022</t>
+          <t>A 2199-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44582</v>
+        <v>45309</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42098-2025</t>
+          <t>A 57296-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45903</v>
+        <v>45629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5555,13 +5555,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5604,7 +5599,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4862-2024</t>
+          <t>A 8092-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45329</v>
+        <v>45707</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5633,13 +5628,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5682,7 +5672,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57305-2024</t>
+          <t>A 8089-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5696,10 +5686,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45629</v>
+        <v>45707</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5712,7 +5702,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5755,7 +5745,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 70345-2021</t>
+          <t>A 47026-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5769,10 +5759,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44536</v>
+        <v>45586</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5785,7 +5775,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5828,7 +5818,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43343-2025</t>
+          <t>A 26911-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5842,10 +5832,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45910</v>
+        <v>45811</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5858,7 +5848,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5901,7 +5891,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42026-2025</t>
+          <t>A 26912-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5911,14 +5901,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45903</v>
+        <v>45811</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5931,7 +5921,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5974,7 +5964,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44046-2025</t>
+          <t>A 42098-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5984,14 +5974,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45915</v>
+        <v>45903</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6003,8 +5993,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6047,7 +6042,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34417-2024</t>
+          <t>A 26914-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6061,10 +6056,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45525</v>
+        <v>45811</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6077,7 +6072,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6120,7 +6115,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 34112-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6134,10 +6129,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44974</v>
+        <v>45126</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6150,7 +6145,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6193,7 +6188,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9810-2026</t>
+          <t>A 57305-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6207,10 +6202,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46072</v>
+        <v>45629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6223,7 +6218,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6266,7 +6261,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9811-2026</t>
+          <t>A 23186-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6280,10 +6275,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46072</v>
+        <v>45450</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6296,7 +6291,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6339,7 +6334,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9821-2026</t>
+          <t>A 43343-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6353,10 +6348,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46072</v>
+        <v>45910</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6369,7 +6364,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6412,7 +6407,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40261-2024</t>
+          <t>A 61092-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6426,10 +6421,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45554</v>
+        <v>44498</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6442,7 +6437,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6485,7 +6480,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10837-2024</t>
+          <t>A 43113-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6499,10 +6494,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45369</v>
+        <v>45567</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6515,7 +6510,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6558,7 +6553,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46312-2025</t>
+          <t>A 44046-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6572,10 +6567,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45925</v>
+        <v>45915</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6587,13 +6582,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6636,7 +6626,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48085-2025</t>
+          <t>A 42026-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6646,14 +6636,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45932</v>
+        <v>45903</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6666,7 +6656,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6709,7 +6699,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8092-2025</t>
+          <t>A 29995-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6723,10 +6713,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45707</v>
+        <v>45109</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6739,7 +6729,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6782,7 +6772,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47026-2024</t>
+          <t>A 28647-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6792,14 +6782,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45586</v>
+        <v>45819</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6812,7 +6802,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6855,7 +6845,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12567-2026</t>
+          <t>A 28786-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6865,14 +6855,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46090</v>
+        <v>45820</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6885,7 +6875,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6928,7 +6918,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47699-2024</t>
+          <t>A 46312-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6942,10 +6932,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45588</v>
+        <v>45925</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6957,8 +6947,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7001,7 +6996,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12517-2026</t>
+          <t>A 30054-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7015,10 +7010,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46090</v>
+        <v>45826</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7031,7 +7026,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7074,7 +7069,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8089-2025</t>
+          <t>A 39534-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7088,10 +7083,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45707</v>
+        <v>45551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7104,7 +7099,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7147,7 +7142,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54877-2023</t>
+          <t>A 57710-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7161,10 +7156,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45229</v>
+        <v>44897</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7177,7 +7172,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7220,7 +7215,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47697-2024</t>
+          <t>A 705-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7234,10 +7229,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45588</v>
+        <v>45300</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7249,8 +7244,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49500-2025</t>
+          <t>A 61814-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45939</v>
+        <v>44917</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>44999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30980-2023</t>
+          <t>A 48085-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45113</v>
+        <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23186-2024</t>
+          <t>A 2457-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45450</v>
+        <v>45674</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60382-2021</t>
+          <t>A 4862-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44496</v>
+        <v>45329</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7614,8 +7614,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7658,7 +7663,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26911-2025</t>
+          <t>A 49500-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7672,10 +7677,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45811</v>
+        <v>45939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7688,7 +7693,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7731,7 +7736,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26912-2025</t>
+          <t>A 24424-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7745,10 +7750,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45811</v>
+        <v>45082</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7761,7 +7766,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7804,7 +7809,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52216-2025</t>
+          <t>A 28143-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7818,10 +7823,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45953</v>
+        <v>45099</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7834,7 +7839,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7877,7 +7882,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53536-2025</t>
+          <t>A 52216-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7891,10 +7896,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7907,7 +7912,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7950,7 +7955,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26914-2025</t>
+          <t>A 62705-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7964,10 +7969,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45811</v>
+        <v>45271</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7980,7 +7985,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8023,7 +8028,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17686-2026</t>
+          <t>A 21425-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8037,10 +8042,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46121</v>
+        <v>45782</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8052,13 +8057,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52384-2024</t>
+          <t>A 7086-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45609</v>
+        <v>44603</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8174,7 +8174,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 55119-2025</t>
+          <t>A 53536-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45967</v>
+        <v>45960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8247,7 +8247,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18529-2023</t>
+          <t>A 1689-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45042</v>
+        <v>46034</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8320,7 +8320,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15463-2023</t>
+          <t>A 1695-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45019</v>
+        <v>46034</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15466-2023</t>
+          <t>A 55119-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8407,10 +8407,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45019</v>
+        <v>45967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8466,7 +8466,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 57088-2025</t>
+          <t>A 16359-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8480,10 +8480,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45979</v>
+        <v>45751</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8539,7 +8539,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2457-2025</t>
+          <t>A 48365-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45674</v>
+        <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8612,7 +8612,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58707-2025</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45986</v>
+        <v>44890</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8641,13 +8641,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>11.2</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8690,7 +8685,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28862-2022</t>
+          <t>A 2981-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8704,10 +8699,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44749</v>
+        <v>46038</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8719,8 +8714,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8763,7 +8763,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58628-2025</t>
+          <t>A 57088-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45986</v>
+        <v>45979</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8836,7 +8836,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7764-2025</t>
+          <t>A 70328-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45706</v>
+        <v>44536</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22168-2023</t>
+          <t>A 30990-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45065</v>
+        <v>45113</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61122-2025</t>
+          <t>A 58707-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46000</v>
+        <v>45986</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9011,8 +9011,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9055,7 +9060,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52321-2023</t>
+          <t>A 58628-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9069,10 +9074,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45224</v>
+        <v>45986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9085,7 +9090,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9128,7 +9133,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55317-2024</t>
+          <t>A 30573-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9142,10 +9147,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45621</v>
+        <v>45111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9158,7 +9163,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9201,7 +9206,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32037-2023</t>
+          <t>A 55660-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9215,10 +9220,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45119</v>
+        <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9231,7 +9236,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9274,7 +9279,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46753-2023</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9284,14 +9289,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45198</v>
+        <v>44749</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9304,7 +9309,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9347,7 +9352,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23670-2025</t>
+          <t>A 61122-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9361,10 +9366,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45792</v>
+        <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9377,7 +9382,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9420,7 +9425,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14660-2023</t>
+          <t>A 46518-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9434,10 +9439,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45013</v>
+        <v>45582</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9450,7 +9455,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9493,7 +9498,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28786-2025</t>
+          <t>A 28703-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9503,14 +9508,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45820</v>
+        <v>44748</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9523,7 +9528,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9566,7 +9571,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62440-2025</t>
+          <t>A 20141-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9580,10 +9585,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46007</v>
+        <v>45055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9596,7 +9601,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9639,7 +9644,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18528-2023</t>
+          <t>A 9811-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9653,10 +9658,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45042</v>
+        <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9669,7 +9674,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9712,7 +9717,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 62844-2025</t>
+          <t>A 9810-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9726,10 +9731,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46008</v>
+        <v>46072</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9742,7 +9747,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9785,7 +9790,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28647-2025</t>
+          <t>A 9821-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9795,14 +9800,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45819</v>
+        <v>46072</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9815,7 +9820,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9858,7 +9863,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48426-2022</t>
+          <t>A 64859-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9872,10 +9877,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44858</v>
+        <v>45280</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9887,8 +9892,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9931,7 +9941,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20141-2023</t>
+          <t>A 50428-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9945,10 +9955,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45055</v>
+        <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9961,7 +9971,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10004,7 +10014,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 40493-2022</t>
+          <t>A 12517-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10018,10 +10028,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44819</v>
+        <v>46090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10034,7 +10044,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10077,7 +10087,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 51056-2022</t>
+          <t>A 12567-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10091,10 +10101,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44868</v>
+        <v>46090</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10107,7 +10117,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10150,7 +10160,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25748-2025</t>
+          <t>A 28862-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10164,10 +10174,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45800</v>
+        <v>44749</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10180,7 +10190,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10223,7 +10233,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25751-2025</t>
+          <t>A 32889-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10237,10 +10247,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45800</v>
+        <v>45112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10253,7 +10263,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10296,7 +10306,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 45019-2025</t>
+          <t>A 27853-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10310,10 +10320,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45918</v>
+        <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10326,7 +10336,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10369,7 +10379,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 57957-2023</t>
+          <t>A 9259-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10383,10 +10393,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45247</v>
+        <v>45358</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10399,7 +10409,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10442,7 +10452,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25822-2025</t>
+          <t>A 1282-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10456,10 +10466,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45804</v>
+        <v>45303</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10472,7 +10482,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10515,7 +10525,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 49373-2025</t>
+          <t>A 15463-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10529,10 +10539,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45938</v>
+        <v>45019</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10545,7 +10555,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10588,7 +10598,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43833-2025</t>
+          <t>A 11916-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10602,10 +10612,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45912</v>
+        <v>45376</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10617,8 +10627,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10661,7 +10676,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29509-2025</t>
+          <t>A 40251-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10675,10 +10690,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45825</v>
+        <v>45554</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10691,7 +10706,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10734,7 +10749,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 34525-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10748,10 +10763,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45246</v>
+        <v>45140</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10764,7 +10779,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10807,7 +10822,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30054-2025</t>
+          <t>A 28866-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10821,10 +10836,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45826</v>
+        <v>44749</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10837,7 +10852,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10880,7 +10895,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 11963-2026</t>
+          <t>A 11402-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10894,10 +10909,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46085</v>
+        <v>44993</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10910,7 +10925,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10953,7 +10968,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 41013-2023</t>
+          <t>A 17686-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10967,10 +10982,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45169</v>
+        <v>46121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10982,8 +10997,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11026,7 +11046,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 30981-2023</t>
+          <t>A 47699-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11040,10 +11060,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45113</v>
+        <v>45588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11056,7 +11076,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11099,7 +11119,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14470-2023</t>
+          <t>A 40189-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11113,10 +11133,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45012</v>
+        <v>45554</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11129,7 +11149,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11172,7 +11192,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20630-2026</t>
+          <t>A 41013-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11186,10 +11206,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46141</v>
+        <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11201,13 +11221,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11250,7 +11265,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 69487-2021</t>
+          <t>A 45019-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11264,10 +11279,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44531</v>
+        <v>45918</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11280,7 +11295,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11323,7 +11338,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27836-2023</t>
+          <t>A 54870-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11337,10 +11352,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45098</v>
+        <v>45229</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11353,7 +11368,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11396,7 +11411,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50428-2022</t>
+          <t>A 70345-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11410,10 +11425,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44866</v>
+        <v>44536</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11426,7 +11441,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11469,7 +11484,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 55660-2021</t>
+          <t>A 32037-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11483,10 +11498,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44476</v>
+        <v>45119</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11499,7 +11514,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11542,7 +11557,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 53885-2022</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11556,10 +11571,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44876</v>
+        <v>45414</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11572,7 +11587,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11615,7 +11630,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22126-2026</t>
+          <t>A 43833-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11629,10 +11644,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46153</v>
+        <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11645,7 +11660,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11688,7 +11703,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19914-2025</t>
+          <t>A 55317-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11702,10 +11717,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45771</v>
+        <v>45621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11718,7 +11733,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11761,7 +11776,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7086-2022</t>
+          <t>A 7764-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11775,10 +11790,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44603</v>
+        <v>45706</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11791,7 +11806,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11834,7 +11849,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 23133-2025</t>
+          <t>A 58097-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11848,10 +11863,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45791</v>
+        <v>45248</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11864,7 +11879,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11907,7 +11922,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 49146-2024</t>
+          <t>A 73273-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11921,10 +11936,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45594</v>
+        <v>44550</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11937,7 +11952,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11980,7 +11995,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 14225-2022</t>
+          <t>A 25748-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11994,10 +12009,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44651</v>
+        <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12010,7 +12025,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12053,7 +12068,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29995-2023</t>
+          <t>A 23670-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12067,10 +12082,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45109</v>
+        <v>45792</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12083,7 +12098,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12126,7 +12141,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61092-2021</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12140,10 +12155,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44498</v>
+        <v>44797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12156,7 +12171,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12199,7 +12214,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 58266-2022</t>
+          <t>A 48447-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12213,10 +12228,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44901</v>
+        <v>44858</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12229,7 +12244,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12272,7 +12287,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33221-2024</t>
+          <t>A 25751-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12286,10 +12301,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45518</v>
+        <v>45800</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12302,7 +12317,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12345,7 +12360,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24424-2023</t>
+          <t>A 29509-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12359,10 +12374,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45082</v>
+        <v>45825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12375,7 +12390,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12418,7 +12433,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 45086-2024</t>
+          <t>A 60382-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12432,10 +12447,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45575</v>
+        <v>44496</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12448,7 +12463,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12491,7 +12506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21425-2025</t>
+          <t>A 25822-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12505,10 +12520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45782</v>
+        <v>45804</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12521,7 +12536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12564,7 +12579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 62705-2023</t>
+          <t>A 57298-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12578,10 +12593,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45271</v>
+        <v>45629</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12594,7 +12609,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12637,7 +12652,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25304-2026</t>
+          <t>A 22168-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12651,10 +12666,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46176</v>
+        <v>45065</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12667,7 +12682,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12710,7 +12725,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 47690-2024</t>
+          <t>A 49373-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12724,10 +12739,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45588</v>
+        <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12740,7 +12755,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12783,7 +12798,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 46518-2024</t>
+          <t>A 30981-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12797,10 +12812,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45582</v>
+        <v>45113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12813,7 +12828,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12856,7 +12871,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 18970-2023</t>
+          <t>A 11963-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12870,10 +12885,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45044</v>
+        <v>46085</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12886,7 +12901,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12929,7 +12944,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24527-2026</t>
+          <t>A 14470-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12943,10 +12958,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46170</v>
+        <v>45012</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12959,7 +12974,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13002,7 +13017,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 43113-2024</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13016,10 +13031,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45567</v>
+        <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13032,7 +13047,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13075,7 +13090,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 54176-2024</t>
+          <t>A 18529-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13089,10 +13104,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45616</v>
+        <v>45042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13105,7 +13120,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13148,7 +13163,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 24096-2026</t>
+          <t>A 54181-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13162,10 +13177,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46168</v>
+        <v>45616</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13178,7 +13193,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13221,7 +13236,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 11910-2023</t>
+          <t>A 20630-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13235,10 +13250,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44995</v>
+        <v>46141</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13250,8 +13265,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13294,7 +13314,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 47690-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13308,10 +13328,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45191</v>
+        <v>45588</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13324,7 +13344,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13367,7 +13387,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 73273-2021</t>
+          <t>A 47697-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13381,10 +13401,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44550</v>
+        <v>45588</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13397,7 +13417,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13440,7 +13460,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 70328-2021</t>
+          <t>A 3141-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13454,10 +13474,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44536</v>
+        <v>44582</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13470,7 +13490,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13513,7 +13533,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54181-2024</t>
+          <t>A 58225-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13527,10 +13547,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45616</v>
+        <v>44487</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13543,7 +13563,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13586,7 +13606,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 47692-2024</t>
+          <t>A 22126-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13600,10 +13620,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45588</v>
+        <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13616,7 +13636,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13659,7 +13679,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13673,10 +13693,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45588</v>
+        <v>45050</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13689,7 +13709,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13732,7 +13752,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 57296-2024</t>
+          <t>A 49146-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13746,10 +13766,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45629</v>
+        <v>45594</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13762,7 +13782,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13805,7 +13825,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 29615-2026</t>
+          <t>A 54867-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13819,10 +13839,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46204</v>
+        <v>45229</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13834,13 +13854,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13883,7 +13898,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57298-2024</t>
+          <t>A 23133-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13897,10 +13912,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45629</v>
+        <v>45791</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13913,7 +13928,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13956,7 +13971,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 54867-2023</t>
+          <t>A 30980-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13970,10 +13985,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45229</v>
+        <v>45113</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13986,7 +14001,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14029,7 +14044,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27831-2023</t>
+          <t>A 33221-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14043,10 +14058,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45098</v>
+        <v>45518</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14059,7 +14074,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14102,7 +14117,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 58097-2023</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14116,10 +14131,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45248</v>
+        <v>45336</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14132,7 +14147,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14175,7 +14190,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 30767-2026</t>
+          <t>A 45667-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14189,10 +14204,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46212</v>
+        <v>44845</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14204,13 +14219,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14253,7 +14263,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28703-2022</t>
+          <t>A 19914-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14267,10 +14277,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44748</v>
+        <v>45771</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14283,7 +14293,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14326,7 +14336,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34910-2026</t>
+          <t>A 40261-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14340,10 +14350,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46255</v>
+        <v>45554</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14356,7 +14366,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14399,7 +14409,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 1282-2024</t>
+          <t>A 14660-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14413,10 +14423,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45303</v>
+        <v>45013</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14429,7 +14439,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14472,7 +14482,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31605-2026</t>
+          <t>A 25304-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14482,14 +14492,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46224</v>
+        <v>46176</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14502,7 +14512,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14545,7 +14555,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36179-2026</t>
+          <t>A 24527-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14559,10 +14569,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46267</v>
+        <v>46170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14575,7 +14585,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14618,7 +14628,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 23185-2024</t>
+          <t>A 60148-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14632,10 +14642,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45450</v>
+        <v>44909</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14648,7 +14658,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14691,7 +14701,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 24096-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14705,10 +14715,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44958</v>
+        <v>46168</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14721,7 +14731,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14764,7 +14774,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 705-2024</t>
+          <t>A 58266-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14778,10 +14788,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45300</v>
+        <v>44901</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14793,13 +14803,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14842,7 +14847,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34532-2023</t>
+          <t>A 53617-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14852,14 +14857,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45140</v>
+        <v>44879</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14872,7 +14877,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14915,7 +14920,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 51257-2022</t>
+          <t>A 18528-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14929,10 +14934,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44866</v>
+        <v>45042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14945,7 +14950,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14988,7 +14993,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 8307-2024</t>
+          <t>A 18970-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15002,10 +15007,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45350</v>
+        <v>45044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15017,13 +15022,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15066,7 +15066,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32110-2026</t>
+          <t>A 29996-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15080,10 +15080,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46234</v>
+        <v>45109</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15139,7 +15139,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32108-2026</t>
+          <t>A 29615-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15153,10 +15153,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15168,8 +15168,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15212,7 +15217,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3570-2025</t>
+          <t>A 51257-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15226,10 +15231,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45680</v>
+        <v>44866</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15242,7 +15247,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15285,7 +15290,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 53617-2022</t>
+          <t>A 53885-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15295,14 +15300,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44879</v>
+        <v>44876</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15315,7 +15320,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15358,7 +15363,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32519-2026</t>
+          <t>A 34532-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15372,10 +15377,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46239</v>
+        <v>45140</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15388,7 +15393,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15431,7 +15436,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 32675-2026</t>
+          <t>A 34417-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15445,10 +15450,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46240</v>
+        <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15460,13 +15465,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15509,7 +15509,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11402-2023</t>
+          <t>A 48276-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44993</v>
+        <v>44858</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15582,7 +15582,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 61814-2022</t>
+          <t>A 23185-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15596,10 +15596,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44917</v>
+        <v>45450</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15655,7 +15655,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 55256-2024</t>
+          <t>A 15466-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15669,10 +15669,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45620</v>
+        <v>45019</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15728,7 +15728,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32629-2026</t>
+          <t>A 45086-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15742,10 +15742,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46240</v>
+        <v>45575</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15801,7 +15801,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32634-2026</t>
+          <t>A 54877-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15815,10 +15815,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46240</v>
+        <v>45229</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -15874,7 +15874,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33168-2026</t>
+          <t>A 51056-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46245</v>
+        <v>44868</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 48276-2022</t>
+          <t>A 30767-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -15961,10 +15961,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44858</v>
+        <v>46212</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15976,8 +15976,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16020,7 +16025,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 39411-2026</t>
+          <t>A 34910-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16034,10 +16039,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46288</v>
+        <v>46255</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16049,13 +16054,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16098,7 +16098,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 33465-2026</t>
+          <t>A 30616-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16112,10 +16112,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46246</v>
+        <v>45495</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16127,13 +16127,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16176,7 +16171,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 40251-2024</t>
+          <t>A 10951-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16190,10 +16185,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45554</v>
+        <v>45370</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16206,7 +16201,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16249,7 +16244,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11916-2023</t>
+          <t>A 27836-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16263,10 +16258,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44995</v>
+        <v>45098</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16279,7 +16274,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16322,7 +16317,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 29996-2023</t>
+          <t>A 2027-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16336,10 +16331,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45109</v>
+        <v>44575</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16352,7 +16347,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16395,7 +16390,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 54943-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16409,10 +16404,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45560</v>
+        <v>45236</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16425,7 +16420,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16468,7 +16463,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28866-2022</t>
+          <t>A 14225-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16482,10 +16477,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44749</v>
+        <v>44651</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16498,7 +16493,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16541,7 +16536,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 30573-2023</t>
+          <t>A 52321-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16555,10 +16550,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45111</v>
+        <v>45224</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16571,7 +16566,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16614,7 +16609,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 10951-2024</t>
+          <t>A 34979-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16628,10 +16623,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45370</v>
+        <v>45527</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16644,7 +16639,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16687,7 +16682,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 64859-2023</t>
+          <t>A 31605-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16697,14 +16692,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45280</v>
+        <v>46224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16716,13 +16711,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16765,7 +16755,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 28143-2023</t>
+          <t>A 36179-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16779,10 +16769,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45099</v>
+        <v>46267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16795,7 +16785,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -16838,7 +16828,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 9259-2024</t>
+          <t>A 52384-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -16852,10 +16842,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45358</v>
+        <v>45609</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16868,7 +16858,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -16911,7 +16901,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 60148-2022</t>
+          <t>A 40493-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -16925,10 +16915,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44909</v>
+        <v>44819</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16941,7 +16931,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -16984,7 +16974,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34112-2023</t>
+          <t>A 55256-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -16998,10 +16988,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45126</v>
+        <v>45620</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17014,7 +17004,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17057,7 +17047,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17071,10 +17061,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44705</v>
+        <v>44890</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17087,7 +17077,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17130,7 +17120,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34525-2023</t>
+          <t>A 47692-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17144,10 +17134,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45140</v>
+        <v>45588</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17160,7 +17150,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17203,7 +17193,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 54870-2023</t>
+          <t>A 69487-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17217,10 +17207,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45229</v>
+        <v>44531</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17233,7 +17223,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17276,7 +17266,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 54943-2023</t>
+          <t>A 27831-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17290,10 +17280,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45236</v>
+        <v>45098</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17306,7 +17296,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17349,7 +17339,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 2199-2024</t>
+          <t>A 54176-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17363,10 +17353,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45309</v>
+        <v>45616</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17379,7 +17369,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17422,7 +17412,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 16359-2025</t>
+          <t>A 11910-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17436,10 +17426,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45751</v>
+        <v>44995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17452,7 +17442,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17495,7 +17485,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 40189-2024</t>
+          <t>A 32110-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17509,10 +17499,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45554</v>
+        <v>46234</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17525,7 +17515,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17568,7 +17558,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 48365-2023</t>
+          <t>A 32108-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17582,10 +17572,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45205</v>
+        <v>46234</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17598,7 +17588,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17641,7 +17631,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 57710-2022</t>
+          <t>A 3570-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17655,10 +17645,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44897</v>
+        <v>45680</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17671,7 +17661,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17714,7 +17704,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 46753-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17728,10 +17718,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45534</v>
+        <v>45198</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17743,13 +17733,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>11.2</v>
+        <v>2.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17792,7 +17777,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 34979-2024</t>
+          <t>A 48426-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17806,10 +17791,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45527</v>
+        <v>44858</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17822,7 +17807,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -17865,7 +17850,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 4696-2024</t>
+          <t>A 21024-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -17879,10 +17864,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45328</v>
+        <v>45777</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -17895,7 +17880,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -17938,7 +17923,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 48447-2022</t>
+          <t>A 21028-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -17952,10 +17937,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44858</v>
+        <v>45777</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -17968,7 +17953,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18011,7 +17996,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 27853-2023</t>
+          <t>A 21032-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18025,10 +18010,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45098</v>
+        <v>45777</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18041,7 +18026,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18084,7 +18069,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 39534-2024</t>
+          <t>A 40278-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18098,10 +18083,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45551</v>
+        <v>45554</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18114,7 +18099,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18157,7 +18142,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 32889-2023</t>
+          <t>A 32629-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18171,10 +18156,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45112</v>
+        <v>46240</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18187,7 +18172,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18230,7 +18215,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 32634-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18244,10 +18229,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45642</v>
+        <v>46240</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18260,7 +18245,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18303,7 +18288,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21024-2025</t>
+          <t>A 10800-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18317,10 +18302,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45777</v>
+        <v>45369</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18333,7 +18318,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18376,7 +18361,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21028-2025</t>
+          <t>A 32675-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18390,10 +18375,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45777</v>
+        <v>46240</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18405,8 +18390,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18449,7 +18439,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21032-2025</t>
+          <t>A 32519-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18463,10 +18453,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45777</v>
+        <v>46239</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18479,7 +18469,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18522,7 +18512,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 40278-2024</t>
+          <t>A 39411-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18536,10 +18526,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45554</v>
+        <v>46288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18551,8 +18541,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18595,7 +18590,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 10800-2024</t>
+          <t>A 33168-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18609,10 +18604,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45369</v>
+        <v>46245</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18625,7 +18620,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18668,7 +18663,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 23125-2025</t>
+          <t>A 33465-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18682,10 +18677,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45791</v>
+        <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18697,8 +18692,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>4</v>
+        <v>13.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 2641-2022</t>
+          <t>S 599-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18751,14 +18751,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44700</v>
+        <v>45351</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18770,8 +18770,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.8</v>
+        <v>36.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18814,7 +18819,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 599-2024</t>
+          <t>S 2641-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -18824,14 +18829,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45351</v>
+        <v>44700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18843,13 +18848,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>36.3</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -18909,7 +18909,7 @@
         <v>45813</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt ÅMÅL.xlsx
+++ b/Översikt ÅMÅL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE245"/>
+  <dimension ref="A1:AE247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45414</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>46066</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 17535-2024</t>
+          <t>A 40425-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45415</v>
+        <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>20.9</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -903,21 +903,138 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Kattfotslav
+Vedtrappmossa
+Bronshjon
+Stubbspretmossa
+Thomsons trägnagare
+Västlig hakmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 40425-2026 artfynd.xlsx", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 40425-2026 karta.png", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 40425-2026 georefererad karta.tif", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 40425-2026 FSC-klagomål.docx", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 40425-2026 FSC-klagomål mail.docx", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 40425-2026 tillsynsbegäran.docx", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 40425-2026 tillsynsbegäran mail.docx", "A 40425-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/fåglar/A 40425-2026 prioriterade fågelarter.docx", "A 40425-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 17535-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Trollsmultron
 Bergjohannesört
@@ -928,112 +1045,112 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 17535-2024 artfynd.xlsx", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 17535-2024 karta.png", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 17535-2024 georefererad karta.tif", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 17535-2024 FSC-klagomål.docx", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 17535-2024 FSC-klagomål mail.docx", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 17535-2024 tillsynsbegäran.docx", "A 17535-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 17535-2024 tillsynsbegäran mail.docx", "A 17535-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 63804-2023</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>45278</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>0.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Svinrot
@@ -1041,251 +1158,145 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 63804-2023 artfynd.xlsx", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 63804-2023 karta.png", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 63804-2023 georefererad karta.tif", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 63804-2023 FSC-klagomål.docx", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 63804-2023 FSC-klagomål mail.docx", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 63804-2023 tillsynsbegäran.docx", "A 63804-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 63804-2023 tillsynsbegäran mail.docx", "A 63804-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 58632-2024</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>1.9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsklocka
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 58632-2024 artfynd.xlsx", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 58632-2024 karta.png", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 58632-2024 georefererad karta.tif", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 58632-2024 FSC-klagomål.docx", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 58632-2024 FSC-klagomål mail.docx", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 58632-2024 tillsynsbegäran.docx", "A 58632-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 58632-2024 tillsynsbegäran mail.docx", "A 58632-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 32887-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Dvärghäxört
-Gulnål</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50546-2024</t>
+          <t>A 12413-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1295,14 +1306,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>44999</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1315,7 +1326,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1355,145 +1366,145 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Kortskaftad ärgspik
+Bronshjon</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 50546-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Dofttaggsvamp
 Platt fjädermossa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 50546-2024 artfynd.xlsx", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 50546-2024 karta.png", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 50546-2024 georefererad karta.tif", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 50546-2024 FSC-klagomål.docx", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 50546-2024 FSC-klagomål mail.docx", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 50546-2024 tillsynsbegäran.docx", "A 50546-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 50546-2024 tillsynsbegäran mail.docx", "A 50546-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 12413-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44999</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik
-Bronshjon</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 12413-2023 artfynd.xlsx", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 12413-2023 karta.png", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 12413-2023 georefererad karta.tif", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 12413-2023 FSC-klagomål.docx", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 12413-2023 FSC-klagomål mail.docx", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 12413-2023 tillsynsbegäran.docx", "A 12413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 12413-2023 tillsynsbegäran mail.docx", "A 12413-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1514,7 +1525,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,24 +1618,24 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S 602-2024</t>
+          <t>A 32887-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45351</v>
+        <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,22 +1647,17 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>68.40000000000001</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1666,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1675,548 +1681,586 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Dvärghäxört
+Gulnål</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 32887-2023 artfynd.xlsx", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 32887-2023 karta.png", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 32887-2023 georefererad karta.tif", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 32887-2023 FSC-klagomål.docx", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 32887-2023 FSC-klagomål mail.docx", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 32887-2023 tillsynsbegäran.docx", "A 32887-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 32887-2023 tillsynsbegäran mail.docx", "A 32887-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 602-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Skogsklocka
 Strandlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/S 602-2024 artfynd.xlsx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/S 602-2024 karta.png", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/S 602-2024 georefererad karta.tif", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/S 602-2024 FSC-klagomål.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/S 602-2024 FSC-klagomål mail.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/S 602-2024 tillsynsbegäran.docx", "S 602-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/S 602-2024 tillsynsbegäran mail.docx", "S 602-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 38064-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45159</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>3.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Vedticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 38064-2023 artfynd.xlsx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 38064-2023 karta.png", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 38064-2023 georefererad karta.tif", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 38064-2023 FSC-klagomål.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 38064-2023 FSC-klagomål mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 38064-2023 tillsynsbegäran.docx", "A 38064-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 38064-2023 tillsynsbegäran mail.docx", "A 38064-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 36671-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 36671-2025 artfynd.xlsx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 36671-2025 karta.png", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 36671-2025 georefererad karta.tif", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 36671-2025 FSC-klagomål.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 36671-2025 FSC-klagomål mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 36671-2025 tillsynsbegäran.docx", "A 36671-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 36671-2025 tillsynsbegäran mail.docx", "A 36671-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 55118-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>45967</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Luddfingersvamp</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 55118-2025 artfynd.xlsx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 55118-2025 karta.png", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 55118-2025 georefererad karta.tif", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 55118-2025 FSC-klagomål.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 55118-2025 FSC-klagomål mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 55118-2025 tillsynsbegäran.docx", "A 55118-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 55118-2025 tillsynsbegäran mail.docx", "A 55118-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 31051-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46215</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÅMÅL</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2.3</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Dunmossa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/artfynd/A 31051-2026 artfynd.xlsx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor/A 31051-2026 karta.png", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/kartor_geotiff/A 31051-2026 georefererad karta.tif", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomål/A 31051-2026 FSC-klagomål.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/klagomålsmail/A 31051-2026 FSC-klagomål mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsyn/A 31051-2026 tillsynsbegäran.docx", "A 31051-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1492/tillsynsmail/A 31051-2026 tillsynsbegäran mail.docx", "A 31051-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 42774-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÅMÅL</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr"/>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58883-2021</t>
+          <t>A 42774-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2230,10 +2274,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44489</v>
+        <v>44832</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2246,7 +2290,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2289,7 +2333,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64067-2021</t>
+          <t>A 58883-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2303,10 +2347,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44509</v>
+        <v>44489</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2318,13 +2362,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2367,7 +2406,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 909-2022</t>
+          <t>A 64067-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2381,10 +2420,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44571</v>
+        <v>44509</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2396,8 +2435,13 @@
           <t>ÅMÅL</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2440,7 +2484,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 70363-2021</t>
+          <t>A 909-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,10 +2498,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44535</v>
+        <v>44571</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2470,7 +2514,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2513,7 +2557,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64999-2021</t>
+          <t>A 70363-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2527,10 +2571,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44514</v>
+        <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2543,7 +2587,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2586,7 +2630,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25830-2022</t>
+          <t>A 64999-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2600,10 +2644,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44733</v>
+        <v>44514</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2616,7 +2660,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2659,7 +2703,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54077-2021</t>
+          <t>A 25830-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2673,10 +2717,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44470</v>
+        <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2689,7 +2733,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2732,7 +2776,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37425-2022</t>
+          <t>A 54077-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2746,10 +2790,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44809</v>
+        <v>44470</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2805,7 +2849,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45804-2022</t>
+          <t>A 37425-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2819,10 +2863,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>44809</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2835,7 +2879,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2878,7 +2922,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25845-2022</t>
+          <t>A 45804-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2892,10 +2936,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44733</v>
+        <v>44846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2908,7 +2952,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2951,7 +2995,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6190-2022</t>
+          <t>A 25845-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2965,10 +3009,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44600</v>
+        <v>44733</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2981,7 +3025,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3024,7 +3068,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44061-2022</t>
+          <t>A 6190-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3038,10 +3082,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44839</v>
+        <v>44600</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3054,7 +3098,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3097,7 +3141,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 68194-2021</t>
+          <t>A 44061-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3111,10 +3155,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44526</v>
+        <v>44839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3127,7 +3171,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3170,7 +3214,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 69666-2021</t>
+          <t>A 68194-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3184,10 +3228,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44532</v>
+        <v>44526</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3200,7 +3244,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3243,7 +3287,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55581-2021</t>
+          <t>A 69666-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3257,10 +3301,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44475</v>
+        <v>44532</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3273,7 +3317,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3316,7 +3360,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61207-2021</t>
+          <t>A 55581-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3326,14 +3370,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44498</v>
+        <v>44475</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3346,7 +3390,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3406,7 +3450,7 @@
         <v>44505</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3462,7 +3506,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59809-2021</t>
+          <t>A 61207-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3472,14 +3516,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44494</v>
+        <v>44498</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3492,7 +3536,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3535,7 +3579,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48433-2022</t>
+          <t>A 59809-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3549,10 +3593,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44858</v>
+        <v>44494</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3565,7 +3609,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3608,7 +3652,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21324-2022</t>
+          <t>A 48433-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3622,10 +3666,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44705</v>
+        <v>44858</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3638,7 +3682,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3681,7 +3725,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41726-2024</t>
+          <t>A 28880-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3691,14 +3735,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45560</v>
+        <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3711,7 +3755,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3754,7 +3798,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36289-2024</t>
+          <t>A 49090-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3768,10 +3812,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45534</v>
+        <v>45204</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3789,7 +3833,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>11.2</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3832,7 +3876,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4976-2023</t>
+          <t>A 5966-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3846,10 +3890,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44958</v>
+        <v>45336</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3862,7 +3906,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3905,7 +3949,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51067-2022</t>
+          <t>A 17391-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3919,10 +3963,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44868</v>
+        <v>45414</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3935,7 +3979,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3978,7 +4022,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45313-2023</t>
+          <t>A 51067-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3992,10 +4036,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45191</v>
+        <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4008,7 +4052,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4051,7 +4095,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47702-2024</t>
+          <t>A 56210-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4065,10 +4109,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45588</v>
+        <v>44890</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4081,7 +4125,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4124,7 +4168,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59998-2024</t>
+          <t>A 56218-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4138,10 +4182,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>44890</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4154,7 +4198,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4197,7 +4241,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49090-2023</t>
+          <t>A 38526-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4211,10 +4255,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45204</v>
+        <v>44813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4226,13 +4270,8 @@
           <t>ÅMÅL</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4275,7 +4314,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8176-2023</t>
+          <t>A 19471-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4289,10 +4328,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44974</v>
+        <v>45050</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4305,7 +4344,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4348,7 +4387,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57720-2023</t>
+          <t>A 35154-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4362,10 +4401,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45246</v>
+        <v>44797</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
    